--- a/secciones/valuacion/modelos/Mallplaza_Sensibilidad_Tasas_Inflacion.xlsx
+++ b/secciones/valuacion/modelos/Mallplaza_Sensibilidad_Tasas_Inflacion.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="133">
   <si>
     <t xml:space="preserve">Sensibilidad del valor por acción a tasas largas e inflación (NUEVO)</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t xml:space="preserve">Lectura: el DCF dice que una alza de 100 pb de tasa real baja el valor ~17%, mientras que la inflación casi no lo mueve; en el dato histórico la sensibilidad es mucho menor y poco significativa porque la acción se re-valorizó con tasas casi planas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E. Precio objetivo (80% DCF + 20% múltiplos, múltiplos fijos): filas = inflación esperada, columnas = tasa real a 10 años (BCU10, base 30-09-26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasa real / inflación</t>
   </si>
   <si>
     <t xml:space="preserve">Sensibilidad a tasas largas e inflación — insumos</t>
@@ -422,9 +428,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -512,7 +519,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -525,11 +532,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -537,7 +548,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -733,7 +744,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1545,6 +1556,166 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <f aca="false">2.82/100+-100/10000</f>
+        <v>0.0182</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <f aca="false">2.82/100+-50/10000</f>
+        <v>0.0232</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <f aca="false">2.82/100+0/10000</f>
+        <v>0.0282</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <f aca="false">2.82/100+50/10000</f>
+        <v>0.0332</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <f aca="false">2.82/100+100/10000</f>
+        <v>0.0382</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <f aca="false">Supuestos!$B$4+100/10000</f>
+        <v>0.04</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI35+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2396.37158617503</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI36+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2221.47215684732</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI37+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2069.99520538708</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI38+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1937.58878276197</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI39+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1820.9138255286</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <f aca="false">Supuestos!$B$4+50/10000</f>
+        <v>0.035</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI28+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2398.52282169555</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI29+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2224.00504632591</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI30+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2072.77343294611</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI31+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1940.51691298762</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI32+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1823.92435425508</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <f aca="false">Supuestos!$B$4+0/10000</f>
+        <v>0.03</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI21+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2400.87840988789</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI22+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2226.72643573829</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI23+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2075.72669191032</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI24+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1943.60840185851</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI25+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1827.08796807026</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <f aca="false">Supuestos!$B$4+-50/10000</f>
+        <v>0.025</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI14+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2403.44603891151</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI15+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2229.64351386822</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI16+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2078.86171657788</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI17+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1946.86957007491</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI18+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1830.41061070193</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <f aca="false">Supuestos!$B$4+-100/10000</f>
+        <v>0.02</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI7+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2406.23370717642</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI8+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2232.76376155139</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI9+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>2082.18551649992</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI10+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1950.30699807294</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <f aca="false">Supuestos!$B$12*Calculo!AI11+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
+        <v>1833.8984712684</v>
       </c>
     </row>
   </sheetData>
@@ -1568,160 +1739,160 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>0.03</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>0.03</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>0.27</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>1285740</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>50841</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>2190</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>3555</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>2951.38547083101</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>0.85</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B15" s="5" t="n">
         <v>100</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">Calculo!AI107</f>
@@ -1730,7 +1901,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">B19/Calculo!AI5-1</f>
@@ -1739,199 +1910,199 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="C23" s="5" t="n">
         <v>113425.715768245</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="5" t="n">
         <v>199440.442268561</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="5" t="n">
         <v>259687.719258378</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="5" t="n">
         <v>375320.615932717</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="5" t="n">
         <v>377068.219372121</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="5" t="n">
         <v>398715.503513791</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="5" t="n">
         <v>528835.311960595</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="C24" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="C25" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="C26" s="5" t="n">
         <v>0.117033041180547</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="5" t="n">
         <v>0.117479013178444</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="5" t="n">
         <v>0.11792498517634</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="5" t="n">
         <v>0.118370957174237</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="5" t="n">
         <v>0.118816929172134</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="5" t="n">
         <v>0.119262901170031</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="5" t="n">
         <v>0.119262901170031</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C27" s="5" t="n">
         <v>0.0362592187808888</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0.0367776563426664</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>0.037296093904444</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="5" t="n">
         <v>0.0378145314662216</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="5" t="n">
         <v>0.0383329690279992</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="5" t="n">
         <v>0.0388514065897768</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" s="5" t="n">
         <v>0.0388514065897768</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="C28" s="5" t="n">
         <v>0.171864958306498</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="5" t="n">
         <v>0.182384862157361</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="5" t="n">
         <v>0.192640847271158</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="5" t="n">
         <v>0.202642722227619</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="5" t="n">
         <v>0.212399815504365</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="5" t="n">
         <v>0.221921004496352</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="5" t="n">
         <v>0.221921004496352</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1955,122 +2126,122 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="T4" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V4" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="W4" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X4" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Y4" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Z4" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AA4" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AB4" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AC4" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AD4" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AE4" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AF4" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG4" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AH4" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AI4" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AJ4" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2085,7 +2256,7 @@
         <v>0.85</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E5" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A5/10000))*(1+Supuestos!$B$4+$B5/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A5/10000)*(1+Supuestos!$B$4+$B5/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -2228,7 +2399,7 @@
         <v>0.85</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A6/10000))*(1+Supuestos!$B$4+$B6/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A6/10000)*(1+Supuestos!$B$4+$B6/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -2371,7 +2542,7 @@
         <v>0.85</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E7" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A7/10000))*(1+Supuestos!$B$4+$B7/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A7/10000)*(1+Supuestos!$B$4+$B7/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -2514,7 +2685,7 @@
         <v>0.85</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A8/10000))*(1+Supuestos!$B$4+$B8/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A8/10000)*(1+Supuestos!$B$4+$B8/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -2657,7 +2828,7 @@
         <v>0.85</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E9" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A9/10000))*(1+Supuestos!$B$4+$B9/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A9/10000)*(1+Supuestos!$B$4+$B9/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -2800,7 +2971,7 @@
         <v>0.85</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E10" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A10/10000))*(1+Supuestos!$B$4+$B10/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A10/10000)*(1+Supuestos!$B$4+$B10/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -2943,7 +3114,7 @@
         <v>0.85</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A11/10000))*(1+Supuestos!$B$4+$B11/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A11/10000)*(1+Supuestos!$B$4+$B11/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -3086,7 +3257,7 @@
         <v>0.85</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E12" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A12/10000))*(1+Supuestos!$B$4+$B12/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A12/10000)*(1+Supuestos!$B$4+$B12/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -3229,7 +3400,7 @@
         <v>0.85</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A13/10000))*(1+Supuestos!$B$4+$B13/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A13/10000)*(1+Supuestos!$B$4+$B13/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -3372,7 +3543,7 @@
         <v>0.85</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E14" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A14/10000))*(1+Supuestos!$B$4+$B14/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A14/10000)*(1+Supuestos!$B$4+$B14/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -3515,7 +3686,7 @@
         <v>0.85</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E15" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A15/10000))*(1+Supuestos!$B$4+$B15/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A15/10000)*(1+Supuestos!$B$4+$B15/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -3658,7 +3829,7 @@
         <v>0.85</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E16" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A16/10000))*(1+Supuestos!$B$4+$B16/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A16/10000)*(1+Supuestos!$B$4+$B16/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -3801,7 +3972,7 @@
         <v>0.85</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E17" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A17/10000))*(1+Supuestos!$B$4+$B17/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A17/10000)*(1+Supuestos!$B$4+$B17/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -3944,7 +4115,7 @@
         <v>0.85</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E18" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A18/10000))*(1+Supuestos!$B$4+$B18/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A18/10000)*(1+Supuestos!$B$4+$B18/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -4087,7 +4258,7 @@
         <v>0.85</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E19" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A19/10000))*(1+Supuestos!$B$4+$B19/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A19/10000)*(1+Supuestos!$B$4+$B19/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -4230,7 +4401,7 @@
         <v>0.85</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E20" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A20/10000))*(1+Supuestos!$B$4+$B20/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A20/10000)*(1+Supuestos!$B$4+$B20/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -4373,7 +4544,7 @@
         <v>0.85</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E21" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A21/10000))*(1+Supuestos!$B$4+$B21/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A21/10000)*(1+Supuestos!$B$4+$B21/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -4516,7 +4687,7 @@
         <v>0.85</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E22" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A22/10000))*(1+Supuestos!$B$4+$B22/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A22/10000)*(1+Supuestos!$B$4+$B22/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -4659,7 +4830,7 @@
         <v>0.85</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E23" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A23/10000))*(1+Supuestos!$B$4+$B23/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A23/10000)*(1+Supuestos!$B$4+$B23/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -4802,7 +4973,7 @@
         <v>0.85</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E24" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A24/10000))*(1+Supuestos!$B$4+$B24/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A24/10000)*(1+Supuestos!$B$4+$B24/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -4945,7 +5116,7 @@
         <v>0.85</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E25" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A25/10000))*(1+Supuestos!$B$4+$B25/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A25/10000)*(1+Supuestos!$B$4+$B25/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -5088,7 +5259,7 @@
         <v>0.85</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E26" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A26/10000))*(1+Supuestos!$B$4+$B26/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A26/10000)*(1+Supuestos!$B$4+$B26/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -5231,7 +5402,7 @@
         <v>0.85</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E27" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A27/10000))*(1+Supuestos!$B$4+$B27/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A27/10000)*(1+Supuestos!$B$4+$B27/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -5374,7 +5545,7 @@
         <v>0.85</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E28" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A28/10000))*(1+Supuestos!$B$4+$B28/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A28/10000)*(1+Supuestos!$B$4+$B28/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -5517,7 +5688,7 @@
         <v>0.85</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A29/10000))*(1+Supuestos!$B$4+$B29/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A29/10000)*(1+Supuestos!$B$4+$B29/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -5660,7 +5831,7 @@
         <v>0.85</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E30" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A30/10000))*(1+Supuestos!$B$4+$B30/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A30/10000)*(1+Supuestos!$B$4+$B30/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -5803,7 +5974,7 @@
         <v>0.85</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A31/10000))*(1+Supuestos!$B$4+$B31/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A31/10000)*(1+Supuestos!$B$4+$B31/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -5946,7 +6117,7 @@
         <v>0.85</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E32" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A32/10000))*(1+Supuestos!$B$4+$B32/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A32/10000)*(1+Supuestos!$B$4+$B32/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -6089,7 +6260,7 @@
         <v>0.85</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E33" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A33/10000))*(1+Supuestos!$B$4+$B33/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A33/10000)*(1+Supuestos!$B$4+$B33/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -6232,7 +6403,7 @@
         <v>0.85</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E34" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A34/10000))*(1+Supuestos!$B$4+$B34/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A34/10000)*(1+Supuestos!$B$4+$B34/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -6375,7 +6546,7 @@
         <v>0.85</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E35" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A35/10000))*(1+Supuestos!$B$4+$B35/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A35/10000)*(1+Supuestos!$B$4+$B35/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -6518,7 +6689,7 @@
         <v>0.85</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E36" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A36/10000))*(1+Supuestos!$B$4+$B36/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A36/10000)*(1+Supuestos!$B$4+$B36/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -6661,7 +6832,7 @@
         <v>0.85</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E37" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A37/10000))*(1+Supuestos!$B$4+$B37/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A37/10000)*(1+Supuestos!$B$4+$B37/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -6804,7 +6975,7 @@
         <v>0.85</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E38" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A38/10000))*(1+Supuestos!$B$4+$B38/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A38/10000)*(1+Supuestos!$B$4+$B38/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -6947,7 +7118,7 @@
         <v>0.85</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E39" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A39/10000))*(1+Supuestos!$B$4+$B39/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A39/10000)*(1+Supuestos!$B$4+$B39/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -7090,7 +7261,7 @@
         <v>0.85</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E40" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A40/10000))*(1+Supuestos!$B$4+$B40/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A40/10000)*(1+Supuestos!$B$4+$B40/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -7232,7 +7403,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E41" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A41/10000))*(1+Supuestos!$B$4+$B41/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A41/10000)*(1+Supuestos!$B$4+$B41/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -7374,7 +7545,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E42" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A42/10000))*(1+Supuestos!$B$4+$B42/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A42/10000)*(1+Supuestos!$B$4+$B42/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -7516,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E43" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A43/10000))*(1+Supuestos!$B$4+$B43/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A43/10000)*(1+Supuestos!$B$4+$B43/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -7658,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E44" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A44/10000))*(1+Supuestos!$B$4+$B44/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A44/10000)*(1+Supuestos!$B$4+$B44/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -7800,7 +7971,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E45" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A45/10000))*(1+Supuestos!$B$4+$B45/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A45/10000)*(1+Supuestos!$B$4+$B45/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -7942,7 +8113,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E46" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A46/10000))*(1+Supuestos!$B$4+$B46/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A46/10000)*(1+Supuestos!$B$4+$B46/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -8084,7 +8255,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E47" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A47/10000))*(1+Supuestos!$B$4+$B47/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A47/10000)*(1+Supuestos!$B$4+$B47/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -8226,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E48" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A48/10000))*(1+Supuestos!$B$4+$B48/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A48/10000)*(1+Supuestos!$B$4+$B48/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -8368,7 +8539,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E49" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A49/10000))*(1+Supuestos!$B$4+$B49/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A49/10000)*(1+Supuestos!$B$4+$B49/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -8510,7 +8681,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E50" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A50/10000))*(1+Supuestos!$B$4+$B50/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A50/10000)*(1+Supuestos!$B$4+$B50/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -8652,7 +8823,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E51" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A51/10000))*(1+Supuestos!$B$4+$B51/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A51/10000)*(1+Supuestos!$B$4+$B51/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -8794,7 +8965,7 @@
         <v>0.85</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E52" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A52/10000))*(1+Supuestos!$B$4+$B52/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A52/10000)*(1+Supuestos!$B$4+$B52/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -8936,7 +9107,7 @@
         <v>0.85</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E53" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A53/10000))*(1+Supuestos!$B$4+$B53/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A53/10000)*(1+Supuestos!$B$4+$B53/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -9078,7 +9249,7 @@
         <v>0.85</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E54" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A54/10000))*(1+Supuestos!$B$4+$B54/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A54/10000)*(1+Supuestos!$B$4+$B54/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -9220,7 +9391,7 @@
         <v>0.85</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E55" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A55/10000))*(1+Supuestos!$B$4+$B55/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A55/10000)*(1+Supuestos!$B$4+$B55/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -9362,7 +9533,7 @@
         <v>0.85</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E56" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A56/10000))*(1+Supuestos!$B$4+$B56/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A56/10000)*(1+Supuestos!$B$4+$B56/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -9504,7 +9675,7 @@
         <v>0.85</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E57" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A57/10000))*(1+Supuestos!$B$4+$B57/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A57/10000)*(1+Supuestos!$B$4+$B57/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -9646,7 +9817,7 @@
         <v>0.85</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E58" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A58/10000))*(1+Supuestos!$B$4+$B58/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A58/10000)*(1+Supuestos!$B$4+$B58/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -9788,7 +9959,7 @@
         <v>0.85</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E59" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A59/10000))*(1+Supuestos!$B$4+$B59/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A59/10000)*(1+Supuestos!$B$4+$B59/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -9930,7 +10101,7 @@
         <v>0.85</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E60" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A60/10000))*(1+Supuestos!$B$4+$B60/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A60/10000)*(1+Supuestos!$B$4+$B60/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -10072,7 +10243,7 @@
         <v>0.85</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E61" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A61/10000))*(1+Supuestos!$B$4+$B61/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A61/10000)*(1+Supuestos!$B$4+$B61/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -10214,7 +10385,7 @@
         <v>0.85</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E62" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A62/10000))*(1+Supuestos!$B$4+$B62/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A62/10000)*(1+Supuestos!$B$4+$B62/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -10356,7 +10527,7 @@
         <v>0.7</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E63" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A63/10000))*(1+Supuestos!$B$4+$B63/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A63/10000)*(1+Supuestos!$B$4+$B63/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -10498,7 +10669,7 @@
         <v>0.7</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E64" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A64/10000))*(1+Supuestos!$B$4+$B64/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A64/10000)*(1+Supuestos!$B$4+$B64/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -10640,7 +10811,7 @@
         <v>0.7</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E65" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A65/10000))*(1+Supuestos!$B$4+$B65/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A65/10000)*(1+Supuestos!$B$4+$B65/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -10782,7 +10953,7 @@
         <v>0.7</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E66" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A66/10000))*(1+Supuestos!$B$4+$B66/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A66/10000)*(1+Supuestos!$B$4+$B66/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -10924,7 +11095,7 @@
         <v>0.7</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E67" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A67/10000))*(1+Supuestos!$B$4+$B67/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A67/10000)*(1+Supuestos!$B$4+$B67/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -11066,7 +11237,7 @@
         <v>0.7</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E68" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A68/10000))*(1+Supuestos!$B$4+$B68/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A68/10000)*(1+Supuestos!$B$4+$B68/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -11208,7 +11379,7 @@
         <v>0.7</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E69" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A69/10000))*(1+Supuestos!$B$4+$B69/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A69/10000)*(1+Supuestos!$B$4+$B69/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -11350,7 +11521,7 @@
         <v>0.7</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E70" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A70/10000))*(1+Supuestos!$B$4+$B70/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A70/10000)*(1+Supuestos!$B$4+$B70/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -11492,7 +11663,7 @@
         <v>0.7</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E71" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A71/10000))*(1+Supuestos!$B$4+$B71/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A71/10000)*(1+Supuestos!$B$4+$B71/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -11634,7 +11805,7 @@
         <v>0.7</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E72" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A72/10000))*(1+Supuestos!$B$4+$B72/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A72/10000)*(1+Supuestos!$B$4+$B72/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -11776,7 +11947,7 @@
         <v>0.7</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E73" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A73/10000))*(1+Supuestos!$B$4+$B73/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A73/10000)*(1+Supuestos!$B$4+$B73/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -11918,7 +12089,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E74" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A74/10000))*(1+Supuestos!$B$4+$B74/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A74/10000)*(1+Supuestos!$B$4+$B74/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -12060,7 +12231,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E75" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A75/10000))*(1+Supuestos!$B$4+$B75/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A75/10000)*(1+Supuestos!$B$4+$B75/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -12202,7 +12373,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E76" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A76/10000))*(1+Supuestos!$B$4+$B76/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A76/10000)*(1+Supuestos!$B$4+$B76/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -12344,7 +12515,7 @@
         <v>1</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E77" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A77/10000))*(1+Supuestos!$B$4+$B77/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A77/10000)*(1+Supuestos!$B$4+$B77/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -12486,7 +12657,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E78" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A78/10000))*(1+Supuestos!$B$4+$B78/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A78/10000)*(1+Supuestos!$B$4+$B78/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -12628,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E79" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A79/10000))*(1+Supuestos!$B$4+$B79/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A79/10000)*(1+Supuestos!$B$4+$B79/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -12770,7 +12941,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E80" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A80/10000))*(1+Supuestos!$B$4+$B80/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A80/10000)*(1+Supuestos!$B$4+$B80/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -12912,7 +13083,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E81" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A81/10000))*(1+Supuestos!$B$4+$B81/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A81/10000)*(1+Supuestos!$B$4+$B81/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -13054,7 +13225,7 @@
         <v>1</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E82" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A82/10000))*(1+Supuestos!$B$4+$B82/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A82/10000)*(1+Supuestos!$B$4+$B82/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -13196,7 +13367,7 @@
         <v>1</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E83" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A83/10000))*(1+Supuestos!$B$4+$B83/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A83/10000)*(1+Supuestos!$B$4+$B83/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -13338,7 +13509,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E84" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A84/10000))*(1+Supuestos!$B$4+$B84/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A84/10000)*(1+Supuestos!$B$4+$B84/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -13480,7 +13651,7 @@
         <v>0.85</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E85" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A85/10000))*(1+Supuestos!$B$4+$B85/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A85/10000)*(1+Supuestos!$B$4+$B85/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -13622,7 +13793,7 @@
         <v>0.85</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E86" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A86/10000))*(1+Supuestos!$B$4+$B86/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A86/10000)*(1+Supuestos!$B$4+$B86/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -13764,7 +13935,7 @@
         <v>0.85</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E87" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A87/10000))*(1+Supuestos!$B$4+$B87/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A87/10000)*(1+Supuestos!$B$4+$B87/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -13906,7 +14077,7 @@
         <v>0.85</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E88" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A88/10000))*(1+Supuestos!$B$4+$B88/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A88/10000)*(1+Supuestos!$B$4+$B88/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -14048,7 +14219,7 @@
         <v>0.85</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E89" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A89/10000))*(1+Supuestos!$B$4+$B89/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A89/10000)*(1+Supuestos!$B$4+$B89/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -14190,7 +14361,7 @@
         <v>0.85</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E90" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A90/10000))*(1+Supuestos!$B$4+$B90/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A90/10000)*(1+Supuestos!$B$4+$B90/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -14332,7 +14503,7 @@
         <v>0.85</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E91" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A91/10000))*(1+Supuestos!$B$4+$B91/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A91/10000)*(1+Supuestos!$B$4+$B91/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -14474,7 +14645,7 @@
         <v>0.85</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E92" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A92/10000))*(1+Supuestos!$B$4+$B92/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A92/10000)*(1+Supuestos!$B$4+$B92/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -14616,7 +14787,7 @@
         <v>0.85</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E93" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A93/10000))*(1+Supuestos!$B$4+$B93/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A93/10000)*(1+Supuestos!$B$4+$B93/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -14758,7 +14929,7 @@
         <v>0.85</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E94" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A94/10000))*(1+Supuestos!$B$4+$B94/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A94/10000)*(1+Supuestos!$B$4+$B94/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -14900,7 +15071,7 @@
         <v>0.85</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E95" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A95/10000))*(1+Supuestos!$B$4+$B95/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A95/10000)*(1+Supuestos!$B$4+$B95/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -15042,7 +15213,7 @@
         <v>0.7</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E96" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A96/10000))*(1+Supuestos!$B$4+$B96/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A96/10000)*(1+Supuestos!$B$4+$B96/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -15184,7 +15355,7 @@
         <v>0.7</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E97" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A97/10000))*(1+Supuestos!$B$4+$B97/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A97/10000)*(1+Supuestos!$B$4+$B97/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -15326,7 +15497,7 @@
         <v>0.7</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E98" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A98/10000))*(1+Supuestos!$B$4+$B98/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A98/10000)*(1+Supuestos!$B$4+$B98/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -15468,7 +15639,7 @@
         <v>0.7</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E99" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A99/10000))*(1+Supuestos!$B$4+$B99/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A99/10000)*(1+Supuestos!$B$4+$B99/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -15610,7 +15781,7 @@
         <v>0.7</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E100" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A100/10000))*(1+Supuestos!$B$4+$B100/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A100/10000)*(1+Supuestos!$B$4+$B100/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -15752,7 +15923,7 @@
         <v>0.7</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E101" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A101/10000))*(1+Supuestos!$B$4+$B101/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A101/10000)*(1+Supuestos!$B$4+$B101/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -15894,7 +16065,7 @@
         <v>0.7</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E102" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A102/10000))*(1+Supuestos!$B$4+$B102/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A102/10000)*(1+Supuestos!$B$4+$B102/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -16036,7 +16207,7 @@
         <v>0.7</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E103" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A103/10000))*(1+Supuestos!$B$4+$B103/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A103/10000)*(1+Supuestos!$B$4+$B103/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -16178,7 +16349,7 @@
         <v>0.7</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E104" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A104/10000))*(1+Supuestos!$B$4+$B104/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A104/10000)*(1+Supuestos!$B$4+$B104/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -16320,7 +16491,7 @@
         <v>0.7</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E105" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A105/10000))*(1+Supuestos!$B$4+$B105/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A105/10000)*(1+Supuestos!$B$4+$B105/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -16462,7 +16633,7 @@
         <v>0.7</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E106" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A106/10000))*(1+Supuestos!$B$4+$B106/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A106/10000)*(1+Supuestos!$B$4+$B106/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -16607,7 +16778,7 @@
         <v>0.85</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E107" s="0" t="n">
         <f aca="false">(1-Supuestos!C$28)*((1+((1+Supuestos!C$26)/(1+Supuestos!$B$4)-1+Supuestos!$B$14*$A107/10000))*(1+Supuestos!$B$4+$B107/10000)-1)+Supuestos!C$28*((1+Supuestos!C$27+$A107/10000)*(1+Supuestos!$B$4+$B107/10000)-1)*(1-Supuestos!$B$6)</f>
@@ -16759,60 +16930,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>45478</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="5" t="n">
         <v>1381.56</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="5" t="n">
         <v>6.22</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>6483.67</v>
       </c>
       <c r="F5" s="4" t="n">
@@ -16821,19 +16992,19 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>45485</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="5" t="n">
         <v>1362.81</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="5" t="n">
         <v>6.11</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>6550.01</v>
       </c>
       <c r="F6" s="4" t="n">
@@ -16858,19 +17029,19 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>45492</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="5" t="n">
         <v>1421.03</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>2.87</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>6558.68</v>
       </c>
       <c r="F7" s="4" t="n">
@@ -16895,19 +17066,19 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>45499</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="5" t="n">
         <v>1440.77</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="5" t="n">
         <v>6.08</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>2.77</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>6432.16</v>
       </c>
       <c r="F8" s="4" t="n">
@@ -16932,19 +17103,19 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>45506</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="5" t="n">
         <v>1423.4</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="5" t="n">
         <v>5.99</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>6315.46</v>
       </c>
       <c r="F9" s="4" t="n">
@@ -16969,19 +17140,19 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>45513</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="5" t="n">
         <v>1460.5</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="5" t="n">
         <v>5.91</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="5" t="n">
         <v>2.53</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="5" t="n">
         <v>6320.96</v>
       </c>
       <c r="F10" s="4" t="n">
@@ -17006,19 +17177,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>45520</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="5" t="n">
         <v>1512.11</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="5" t="n">
         <v>2.49</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="5" t="n">
         <v>6457.74</v>
       </c>
       <c r="F11" s="4" t="n">
@@ -17043,19 +17214,19 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>45527</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="5" t="n">
         <v>1519.71</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="5" t="n">
         <v>5.73</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="5" t="n">
         <v>6463.24</v>
       </c>
       <c r="F12" s="4" t="n">
@@ -17080,19 +17251,19 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>45534</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>1490.21</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>5.64</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="5" t="n">
         <v>2.37</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="5" t="n">
         <v>6459.96</v>
       </c>
       <c r="F13" s="4" t="n">
@@ -17117,19 +17288,19 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>45541</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="5" t="n">
         <v>1506.29</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="5" t="n">
         <v>5.5</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="5" t="n">
         <v>2.26</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="5" t="n">
         <v>6245.42</v>
       </c>
       <c r="F14" s="4" t="n">
@@ -17154,19 +17325,19 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>45547</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="5" t="n">
         <v>1509.05</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>5.37</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="5" t="n">
         <v>6343.16</v>
       </c>
       <c r="F15" s="4" t="n">
@@ -17191,19 +17362,19 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>45562</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="5" t="n">
         <v>1580.6</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="5" t="n">
         <v>5.16</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="5" t="n">
         <v>1.82</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="5" t="n">
         <v>6530.73</v>
       </c>
       <c r="F16" s="4" t="n">
@@ -17228,19 +17399,19 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>45568</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="5" t="n">
         <v>1524.65</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="5" t="n">
         <v>6389.82</v>
       </c>
       <c r="F17" s="4" t="n">
@@ -17265,19 +17436,19 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="7" t="n">
         <v>45575</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="5" t="n">
         <v>1588.79</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="5" t="n">
         <v>5.57</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="5" t="n">
         <v>2.31</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="5" t="n">
         <v>6578.77</v>
       </c>
       <c r="F18" s="4" t="n">
@@ -17302,19 +17473,19 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>45583</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="5" t="n">
         <v>1569.05</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="5" t="n">
         <v>5.49</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>2.21</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="5" t="n">
         <v>6643.52</v>
       </c>
       <c r="F19" s="4" t="n">
@@ -17339,19 +17510,19 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>45589</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="5" t="n">
         <v>1564.22</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="5" t="n">
         <v>5.75</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="5" t="n">
         <v>6725.8</v>
       </c>
       <c r="F20" s="4" t="n">
@@ -17376,19 +17547,19 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>45595</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="5" t="n">
         <v>1549.32</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="5" t="n">
         <v>5.76</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="5" t="n">
         <v>6550.32</v>
       </c>
       <c r="F21" s="4" t="n">
@@ -17413,19 +17584,19 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>45604</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="5" t="n">
         <v>1516.75</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="5" t="n">
         <v>2.35</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="5" t="n">
         <v>6519.72</v>
       </c>
       <c r="F22" s="4" t="n">
@@ -17450,19 +17621,19 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>45616</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="5" t="n">
         <v>1502.94</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="5" t="n">
         <v>5.91</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="5" t="n">
         <v>2.41</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="5" t="n">
         <v>6576.33</v>
       </c>
       <c r="F23" s="4" t="n">
@@ -17487,19 +17658,19 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>45625</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="5" t="n">
         <v>1623.33</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="5" t="n">
         <v>5.68</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="5" t="n">
         <v>2.18</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="5" t="n">
         <v>6576.6</v>
       </c>
       <c r="F24" s="4" t="n">
@@ -17524,19 +17695,19 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>45632</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="5" t="n">
         <v>1646.03</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="5" t="n">
         <v>5.58</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="5" t="n">
         <v>2.18</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="5" t="n">
         <v>6648.65</v>
       </c>
       <c r="F25" s="4" t="n">
@@ -17561,19 +17732,19 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="7" t="n">
         <v>45645</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="5" t="n">
         <v>1672</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="5" t="n">
         <v>5.88</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="5" t="n">
         <v>6699.84</v>
       </c>
       <c r="F26" s="4" t="n">
@@ -17598,19 +17769,19 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>45653</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="5" t="n">
         <v>1630.1</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="5" t="n">
         <v>5.99</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>2.65</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>6703.27</v>
       </c>
       <c r="F27" s="4" t="n">
@@ -17635,19 +17806,19 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="7" t="n">
         <v>45659</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="5" t="n">
         <v>1630</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="5" t="n">
         <v>5.93</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="5" t="n">
         <v>2.58</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="5" t="n">
         <v>6681.92</v>
       </c>
       <c r="F28" s="4" t="n">
@@ -17672,19 +17843,19 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="7" t="n">
         <v>45666</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="5" t="n">
         <v>1620</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="5" t="n">
         <v>6.05</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>2.75</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="5" t="n">
         <v>6802.58</v>
       </c>
       <c r="F29" s="4" t="n">
@@ -17709,19 +17880,19 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="7" t="n">
         <v>45674</v>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="5" t="n">
         <v>1601</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="5" t="n">
         <v>5.93</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="5" t="n">
         <v>2.64</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="5" t="n">
         <v>6958.79</v>
       </c>
       <c r="F30" s="4" t="n">
@@ -17746,19 +17917,19 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="7" t="n">
         <v>45681</v>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="5" t="n">
         <v>1684.8</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="5" t="n">
         <v>6.01</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="5" t="n">
         <v>2.38</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="5" t="n">
         <v>7068.67</v>
       </c>
       <c r="F31" s="4" t="n">
@@ -17783,19 +17954,19 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="7" t="n">
         <v>45688</v>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="5" t="n">
         <v>1759.9</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="5" t="n">
         <v>6.03</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="5" t="n">
         <v>2.55</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="5" t="n">
         <v>7199.59</v>
       </c>
       <c r="F32" s="4" t="n">
@@ -17820,19 +17991,19 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>45694</v>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="5" t="n">
         <v>1805</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="5" t="n">
         <v>5.98</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="5" t="n">
         <v>2.49</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="5" t="n">
         <v>7301.44</v>
       </c>
       <c r="F33" s="4" t="n">
@@ -17857,19 +18028,19 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="7" t="n">
         <v>45699</v>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="5" t="n">
         <v>1791</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="5" t="n">
         <v>2.45</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="5" t="n">
         <v>7278.04</v>
       </c>
       <c r="F34" s="4" t="n">
@@ -17894,19 +18065,19 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>45708</v>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="5" t="n">
         <v>1881.3</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="5" t="n">
         <v>7322.48</v>
       </c>
       <c r="F35" s="4" t="n">
@@ -17931,19 +18102,19 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="7" t="n">
         <v>45716</v>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="5" t="n">
         <v>1900</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="5" t="n">
         <v>5.94</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="5" t="n">
         <v>2.65</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="5" t="n">
         <v>7332.12</v>
       </c>
       <c r="F36" s="4" t="n">
@@ -17968,19 +18139,19 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>45720</v>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="5" t="n">
         <v>1855</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="5" t="n">
         <v>5.86</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="5" t="n">
         <v>2.58</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="5" t="n">
         <v>7313.89</v>
       </c>
       <c r="F37" s="4" t="n">
@@ -18005,19 +18176,19 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="7" t="n">
         <v>45730</v>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="5" t="n">
         <v>1940</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="5" t="n">
         <v>5.76</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="5" t="n">
         <v>2.52</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="5" t="n">
         <v>7509</v>
       </c>
       <c r="F38" s="4" t="n">
@@ -18042,19 +18213,19 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="7" t="n">
         <v>45735</v>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="5" t="n">
         <v>1970.1</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="5" t="n">
         <v>5.76</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="5" t="n">
         <v>2.54</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="5" t="n">
         <v>7594.95</v>
       </c>
       <c r="F39" s="4" t="n">
@@ -18079,19 +18250,19 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="7" t="n">
         <v>45744</v>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="5" t="n">
         <v>1970</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="5" t="n">
         <v>5.85</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="5" t="n">
         <v>2.63</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="5" t="n">
         <v>7694.49</v>
       </c>
       <c r="F40" s="4" t="n">
@@ -18116,19 +18287,19 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="7" t="n">
         <v>45751</v>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="5" t="n">
         <v>5.55</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="5" t="n">
         <v>2.28</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="5" t="n">
         <v>7504.21</v>
       </c>
       <c r="F41" s="4" t="n">
@@ -18153,19 +18324,19 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="7" t="n">
         <v>45758</v>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="5" t="n">
         <v>2049.9</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="5" t="n">
         <v>5.68</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="5" t="n">
         <v>2.42</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="5" t="n">
         <v>7430.69</v>
       </c>
       <c r="F42" s="4" t="n">
@@ -18190,19 +18361,19 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="7" t="n">
         <v>45764</v>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="5" t="n">
         <v>2179.9</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="5" t="n">
         <v>5.58</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="5" t="n">
         <v>2.49</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="5" t="n">
         <v>7815.25</v>
       </c>
       <c r="F43" s="4" t="n">
@@ -18227,19 +18398,19 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="7" t="n">
         <v>45772</v>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="5" t="n">
         <v>2200</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="5" t="n">
         <v>5.71</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="5" t="n">
         <v>2.48</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="5" t="n">
         <v>7991.62</v>
       </c>
       <c r="F44" s="4" t="n">
@@ -18264,19 +18435,19 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="7" t="n">
         <v>45777</v>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="5" t="n">
         <v>2225</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="5" t="n">
         <v>2.45</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="5" t="n">
         <v>8041.14</v>
       </c>
       <c r="F45" s="4" t="n">
@@ -18301,19 +18472,19 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="7" t="n">
         <v>45784</v>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="5" t="n">
         <v>2240</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="5" t="n">
         <v>5.78</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="5" t="n">
         <v>2.53</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="5" t="n">
         <v>8173.81</v>
       </c>
       <c r="F46" s="4" t="n">
@@ -18338,19 +18509,19 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="7" t="n">
         <v>45793</v>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="5" t="n">
         <v>2177</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="5" t="n">
         <v>5.75</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="5" t="n">
         <v>2.56</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="5" t="n">
         <v>8386.16</v>
       </c>
       <c r="F47" s="4" t="n">
@@ -18375,19 +18546,19 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="n">
+      <c r="A48" s="7" t="n">
         <v>45799</v>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B48" s="5" t="n">
         <v>2225.5</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C48" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="5" t="n">
         <v>2.58</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="5" t="n">
         <v>8367.62</v>
       </c>
       <c r="F48" s="4" t="n">
@@ -18412,19 +18583,19 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+      <c r="A49" s="7" t="n">
         <v>45807</v>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="5" t="n">
         <v>2060</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="5" t="n">
         <v>5.77</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="5" t="n">
         <v>2.57</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="5" t="n">
         <v>8047.51</v>
       </c>
       <c r="F49" s="4" t="n">
@@ -18449,19 +18620,19 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="n">
+      <c r="A50" s="7" t="n">
         <v>45813</v>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="5" t="n">
         <v>2070</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="5" t="n">
         <v>5.75</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="5" t="n">
         <v>8145.59</v>
       </c>
       <c r="F50" s="4" t="n">
@@ -18486,19 +18657,19 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
+      <c r="A51" s="7" t="n">
         <v>45821</v>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="5" t="n">
         <v>2080</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="5" t="n">
         <v>5.76</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="5" t="n">
         <v>2.61</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="5" t="n">
         <v>8209.92</v>
       </c>
       <c r="F51" s="4" t="n">
@@ -18523,19 +18694,19 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="n">
+      <c r="A52" s="7" t="n">
         <v>45824</v>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="5" t="n">
         <v>2070.6</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C52" s="5" t="n">
         <v>5.73</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="5" t="n">
         <v>8165.29</v>
       </c>
       <c r="F52" s="4" t="n">
@@ -18560,19 +18731,19 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="n">
+      <c r="A53" s="7" t="n">
         <v>45835</v>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B53" s="5" t="n">
         <v>2050.1</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C53" s="5" t="n">
         <v>5.68</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="5" t="n">
         <v>2.69</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="5" t="n">
         <v>8213.08</v>
       </c>
       <c r="F53" s="4" t="n">
@@ -18597,19 +18768,19 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="n">
+      <c r="A54" s="7" t="n">
         <v>45841</v>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="5" t="n">
         <v>2080</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="C54" s="5" t="n">
         <v>5.67</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="5" t="n">
         <v>2.65</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="5" t="n">
         <v>8290.26</v>
       </c>
       <c r="F54" s="4" t="n">
@@ -18634,19 +18805,19 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="n">
+      <c r="A55" s="7" t="n">
         <v>45849</v>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="5" t="n">
         <v>2190</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="5" t="n">
         <v>5.61</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="5" t="n">
         <v>2.68</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="5" t="n">
         <v>8231.92</v>
       </c>
       <c r="F55" s="4" t="n">
@@ -18671,19 +18842,19 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="n">
+      <c r="A56" s="7" t="n">
         <v>45863</v>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="5" t="n">
         <v>2065</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="5" t="n">
         <v>5.6</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="5" t="n">
         <v>2.52</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="5" t="n">
         <v>8221.9</v>
       </c>
       <c r="F56" s="4" t="n">
@@ -18708,19 +18879,19 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="n">
+      <c r="A57" s="7" t="n">
         <v>45870</v>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="5" t="n">
         <v>2124</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="5" t="n">
         <v>5.6</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="5" t="n">
         <v>2.45</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="5" t="n">
         <v>8161.33</v>
       </c>
       <c r="F57" s="4" t="n">
@@ -18745,19 +18916,19 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="n">
+      <c r="A58" s="7" t="n">
         <v>45877</v>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B58" s="5" t="n">
         <v>2164.9</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C58" s="5" t="n">
         <v>5.63</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="5" t="n">
         <v>2.36</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="5" t="n">
         <v>8520.53</v>
       </c>
       <c r="F58" s="4" t="n">
@@ -18782,19 +18953,19 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="n">
+      <c r="A59" s="7" t="n">
         <v>45882</v>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B59" s="5" t="n">
         <v>2228.1</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C59" s="5" t="n">
         <v>5.59</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="5" t="n">
         <v>2.37</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="5" t="n">
         <v>8737.86</v>
       </c>
       <c r="F59" s="4" t="n">
@@ -18819,19 +18990,19 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="n">
+      <c r="A60" s="7" t="n">
         <v>45891</v>
       </c>
-      <c r="B60" s="3" t="n">
+      <c r="B60" s="5" t="n">
         <v>2242.2</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" s="5" t="n">
         <v>5.57</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="5" t="n">
         <v>2.49</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="5" t="n">
         <v>8854.26</v>
       </c>
       <c r="F60" s="4" t="n">
@@ -18856,19 +19027,19 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="n">
+      <c r="A61" s="7" t="n">
         <v>45898</v>
       </c>
-      <c r="B61" s="3" t="n">
+      <c r="B61" s="5" t="n">
         <v>2270.1</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="C61" s="5" t="n">
         <v>5.63</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="5" t="n">
         <v>2.48</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" s="5" t="n">
         <v>8899.91</v>
       </c>
       <c r="F61" s="4" t="n">
@@ -18893,19 +19064,19 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="n">
+      <c r="A62" s="7" t="n">
         <v>45905</v>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B62" s="5" t="n">
         <v>2454.11</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="C62" s="5" t="n">
         <v>5.67</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="5" t="n">
         <v>2.41</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" s="5" t="n">
         <v>9210.68</v>
       </c>
       <c r="F62" s="4" t="n">
@@ -18930,19 +19101,19 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="n">
+      <c r="A63" s="7" t="n">
         <v>45912</v>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B63" s="5" t="n">
         <v>2515</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="C63" s="5" t="n">
         <v>5.62</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="5" t="n">
         <v>2.42</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" s="5" t="n">
         <v>8989.75</v>
       </c>
       <c r="F63" s="4" t="n">
@@ -18967,19 +19138,19 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="n">
+      <c r="A64" s="7" t="n">
         <v>45916</v>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B64" s="5" t="n">
         <v>2580</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C64" s="5" t="n">
         <v>5.6</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="5" t="n">
         <v>2.41</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" s="5" t="n">
         <v>9066.03</v>
       </c>
       <c r="F64" s="4" t="n">
@@ -19004,19 +19175,19 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="n">
+      <c r="A65" s="7" t="n">
         <v>45925</v>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B65" s="5" t="n">
         <v>2585</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C65" s="5" t="n">
         <v>5.58</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" s="5" t="n">
         <v>9040.46</v>
       </c>
       <c r="F65" s="4" t="n">
@@ -19041,19 +19212,19 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="n">
+      <c r="A66" s="7" t="n">
         <v>45932</v>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="5" t="n">
         <v>2580</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="5" t="n">
         <v>5.63</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="5" t="n">
         <v>2.34</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="5" t="n">
         <v>8899.67</v>
       </c>
       <c r="F66" s="4" t="n">
@@ -19078,19 +19249,19 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="n">
+      <c r="A67" s="7" t="n">
         <v>45940</v>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="5" t="n">
         <v>2537</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C67" s="5" t="n">
         <v>5.58</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="5" t="n">
         <v>2.34</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="5" t="n">
         <v>8675.8</v>
       </c>
       <c r="F67" s="4" t="n">
@@ -19115,19 +19286,19 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="n">
+      <c r="A68" s="7" t="n">
         <v>45947</v>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="5" t="n">
         <v>2689.9</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C68" s="5" t="n">
         <v>5.57</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="5" t="n">
         <v>2.36</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" s="5" t="n">
         <v>9129.98</v>
       </c>
       <c r="F68" s="4" t="n">
@@ -19152,19 +19323,19 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="n">
+      <c r="A69" s="7" t="n">
         <v>45954</v>
       </c>
-      <c r="B69" s="3" t="n">
+      <c r="B69" s="5" t="n">
         <v>2730</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C69" s="5" t="n">
         <v>5.55</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="5" t="n">
         <v>2.38</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="5" t="n">
         <v>9184.41</v>
       </c>
       <c r="F69" s="4" t="n">
@@ -19189,19 +19360,19 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="n">
+      <c r="A70" s="7" t="n">
         <v>45960</v>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="5" t="n">
         <v>2655</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="5" t="n">
         <v>5.56</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="5" t="n">
         <v>2.37</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="5" t="n">
         <v>9428.89</v>
       </c>
       <c r="F70" s="4" t="n">
@@ -19226,19 +19397,19 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="n">
+      <c r="A71" s="7" t="n">
         <v>45968</v>
       </c>
-      <c r="B71" s="3" t="n">
+      <c r="B71" s="5" t="n">
         <v>2955</v>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" s="5" t="n">
         <v>5.52</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="5" t="n">
         <v>2.37</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="5" t="n">
         <v>9605.06</v>
       </c>
       <c r="F71" s="4" t="n">
@@ -19263,19 +19434,19 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="n">
+      <c r="A72" s="7" t="n">
         <v>45975</v>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="5" t="n">
         <v>2977</v>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C72" s="5" t="n">
         <v>5.38</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="5" t="n">
         <v>2.36</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="5" t="n">
         <v>9603.02</v>
       </c>
       <c r="F72" s="4" t="n">
@@ -19300,19 +19471,19 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="n">
+      <c r="A73" s="7" t="n">
         <v>45981</v>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="5" t="n">
         <v>3015</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="5" t="n">
         <v>5.35</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="5" t="n">
         <v>2.33</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" s="5" t="n">
         <v>9802.08</v>
       </c>
       <c r="F73" s="4" t="n">
@@ -19337,19 +19508,19 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="n">
+      <c r="A74" s="7" t="n">
         <v>45986</v>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="5" t="n">
         <v>3110</v>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C74" s="5" t="n">
         <v>5.31</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="5" t="n">
         <v>2.31</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" s="5" t="n">
         <v>9950.81</v>
       </c>
       <c r="F74" s="4" t="n">
@@ -19374,19 +19545,19 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="n">
+      <c r="A75" s="7" t="n">
         <v>45996</v>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="5" t="n">
         <v>3243</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="5" t="n">
         <v>5.32</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="5" t="n">
         <v>2.32</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="5" t="n">
         <v>10222.61</v>
       </c>
       <c r="F75" s="4" t="n">
@@ -19411,19 +19582,19 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6" t="n">
+      <c r="A76" s="7" t="n">
         <v>46003</v>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="5" t="n">
         <v>3275</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C76" s="5" t="n">
         <v>5.32</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="5" t="n">
         <v>2.34</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="E76" s="5" t="n">
         <v>10400.01</v>
       </c>
       <c r="F76" s="4" t="n">
@@ -19448,19 +19619,19 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="n">
+      <c r="A77" s="7" t="n">
         <v>46009</v>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="5" t="n">
         <v>3140</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="5" t="n">
         <v>5.39</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="5" t="n">
         <v>2.32</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E77" s="5" t="n">
         <v>10194.26</v>
       </c>
       <c r="F77" s="4" t="n">
@@ -19485,19 +19656,19 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="n">
+      <c r="A78" s="7" t="n">
         <v>46017</v>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="5" t="n">
         <v>3125</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="5" t="n">
         <v>5.4</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="5" t="n">
         <v>2.34</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E78" s="5" t="n">
         <v>10483.15</v>
       </c>
       <c r="F78" s="4" t="n">
@@ -19522,19 +19693,19 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6" t="n">
+      <c r="A79" s="7" t="n">
         <v>46020</v>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="5" t="n">
         <v>3194.9</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="5" t="n">
         <v>5.41</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="5" t="n">
         <v>2.33</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="E79" s="5" t="n">
         <v>10521.68</v>
       </c>
       <c r="F79" s="4" t="n">
@@ -19559,19 +19730,19 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6" t="n">
+      <c r="A80" s="7" t="n">
         <v>46031</v>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="5" t="n">
         <v>3395</v>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="5" t="n">
         <v>5.31</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="5" t="n">
         <v>2.31</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="5" t="n">
         <v>10929.15</v>
       </c>
       <c r="F80" s="4" t="n">
@@ -19596,19 +19767,19 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="n">
+      <c r="A81" s="7" t="n">
         <v>46038</v>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="5" t="n">
         <v>3650</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="5" t="n">
         <v>5.34</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="5" t="n">
         <v>2.32</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="5" t="n">
         <v>11156.73</v>
       </c>
       <c r="F81" s="4" t="n">
@@ -19633,19 +19804,19 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="n">
+      <c r="A82" s="7" t="n">
         <v>46045</v>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="C82" s="5" t="n">
         <v>5.34</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="5" t="n">
         <v>2.33</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="5" t="n">
         <v>11500.1</v>
       </c>
       <c r="F82" s="4" t="n">
@@ -19670,19 +19841,19 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6" t="n">
+      <c r="A83" s="7" t="n">
         <v>46052</v>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="C83" s="5" t="n">
         <v>5.34</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="5" t="n">
         <v>2.33</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="5" t="n">
         <v>11420.07</v>
       </c>
       <c r="F83" s="4" t="n">
@@ -19707,19 +19878,19 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="n">
+      <c r="A84" s="7" t="n">
         <v>46057</v>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="5" t="n">
         <v>3889.9</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" s="5" t="n">
         <v>5.34</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="5" t="n">
         <v>2.36</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="5" t="n">
         <v>11425.88</v>
       </c>
       <c r="F84" s="4" t="n">
@@ -19744,19 +19915,19 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6" t="n">
+      <c r="A85" s="7" t="n">
         <v>46063</v>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="5" t="n">
         <v>3725.5</v>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C85" s="5" t="n">
         <v>5.31</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="5" t="n">
         <v>2.31</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="5" t="n">
         <v>11009.28</v>
       </c>
       <c r="F85" s="4" t="n">
@@ -19781,19 +19952,19 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="n">
+      <c r="A86" s="7" t="n">
         <v>46073</v>
       </c>
-      <c r="B86" s="3" t="n">
+      <c r="B86" s="5" t="n">
         <v>3905</v>
       </c>
-      <c r="C86" s="3" t="n">
+      <c r="C86" s="5" t="n">
         <v>5.28</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="E86" s="5" t="n">
         <v>10855.08</v>
       </c>
       <c r="F86" s="4" t="n">
@@ -19818,19 +19989,19 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6" t="n">
+      <c r="A87" s="7" t="n">
         <v>46080</v>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B87" s="5" t="n">
         <v>4080</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="C87" s="5" t="n">
         <v>5.25</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="5" t="n">
         <v>2.29</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="E87" s="5" t="n">
         <v>10877.74</v>
       </c>
       <c r="F87" s="4" t="n">
@@ -19855,19 +20026,19 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="n">
+      <c r="A88" s="7" t="n">
         <v>46085</v>
       </c>
-      <c r="B88" s="3" t="n">
+      <c r="B88" s="5" t="n">
         <v>3920</v>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="C88" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="5" t="n">
         <v>2.24</v>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="5" t="n">
         <v>10494.97</v>
       </c>
       <c r="F88" s="4" t="n">
@@ -19892,19 +20063,19 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="n">
+      <c r="A89" s="7" t="n">
         <v>46094</v>
       </c>
-      <c r="B89" s="3" t="n">
+      <c r="B89" s="5" t="n">
         <v>3824.9</v>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="C89" s="5" t="n">
         <v>5.46</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="5" t="n">
         <v>2.15</v>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="E89" s="5" t="n">
         <v>10466.52</v>
       </c>
       <c r="F89" s="4" t="n">
@@ -19929,19 +20100,19 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6" t="n">
+      <c r="A90" s="7" t="n">
         <v>46101</v>
       </c>
-      <c r="B90" s="3" t="n">
+      <c r="B90" s="5" t="n">
         <v>3900</v>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="C90" s="5" t="n">
         <v>5.66</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" s="5" t="n">
         <v>2.25</v>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="E90" s="5" t="n">
         <v>10277.51</v>
       </c>
       <c r="F90" s="4" t="n">
@@ -19966,19 +20137,19 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="n">
+      <c r="A91" s="7" t="n">
         <v>46108</v>
       </c>
-      <c r="B91" s="3" t="n">
+      <c r="B91" s="5" t="n">
         <v>3810</v>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="C91" s="5" t="n">
         <v>5.69</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" s="5" t="n">
         <v>2.16</v>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="E91" s="5" t="n">
         <v>10417.19</v>
       </c>
       <c r="F91" s="4" t="n">
@@ -20003,19 +20174,19 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6" t="n">
+      <c r="A92" s="7" t="n">
         <v>46114</v>
       </c>
-      <c r="B92" s="3" t="n">
+      <c r="B92" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="C92" s="5" t="n">
         <v>5.56</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="E92" s="5" t="n">
         <v>10739.15</v>
       </c>
       <c r="F92" s="4" t="n">
@@ -20040,19 +20211,19 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6" t="n">
+      <c r="A93" s="7" t="n">
         <v>46122</v>
       </c>
-      <c r="B93" s="3" t="n">
+      <c r="B93" s="5" t="n">
         <v>4150</v>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="C93" s="5" t="n">
         <v>5.46</v>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="E93" s="3" t="n">
+      <c r="E93" s="5" t="n">
         <v>11076.65</v>
       </c>
       <c r="F93" s="4" t="n">
@@ -20077,19 +20248,19 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6" t="n">
+      <c r="A94" s="7" t="n">
         <v>46129</v>
       </c>
-      <c r="B94" s="3" t="n">
+      <c r="B94" s="5" t="n">
         <v>4585</v>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="C94" s="5" t="n">
         <v>5.34</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="5" t="n">
         <v>2.15</v>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="E94" s="5" t="n">
         <v>11429.19</v>
       </c>
       <c r="F94" s="4" t="n">
@@ -20114,19 +20285,19 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="n">
+      <c r="A95" s="7" t="n">
         <v>46135</v>
       </c>
-      <c r="B95" s="3" t="n">
+      <c r="B95" s="5" t="n">
         <v>4414.7</v>
       </c>
-      <c r="C95" s="3" t="n">
+      <c r="C95" s="5" t="n">
         <v>5.46</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="5" t="n">
         <v>2.18</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="E95" s="5" t="n">
         <v>10992.09</v>
       </c>
       <c r="F95" s="4" t="n">
@@ -20151,19 +20322,19 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6" t="n">
+      <c r="A96" s="7" t="n">
         <v>46142</v>
       </c>
-      <c r="B96" s="3" t="n">
+      <c r="B96" s="5" t="n">
         <v>4469.9</v>
       </c>
-      <c r="C96" s="3" t="n">
+      <c r="C96" s="5" t="n">
         <v>5.61</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="5" t="n">
         <v>2.21</v>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="E96" s="5" t="n">
         <v>10908.3</v>
       </c>
       <c r="F96" s="4" t="n">
@@ -20188,19 +20359,19 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="n">
+      <c r="A97" s="7" t="n">
         <v>46150</v>
       </c>
-      <c r="B97" s="3" t="n">
+      <c r="B97" s="5" t="n">
         <v>4009</v>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="C97" s="5" t="n">
         <v>5.56</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="5" t="n">
         <v>2.25</v>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="E97" s="5" t="n">
         <v>10758.9</v>
       </c>
       <c r="F97" s="4" t="n">
@@ -20225,19 +20396,19 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6" t="n">
+      <c r="A98" s="7" t="n">
         <v>46156</v>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B98" s="5" t="n">
         <v>3746.3</v>
       </c>
-      <c r="C98" s="3" t="n">
+      <c r="C98" s="5" t="n">
         <v>5.53</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" s="5" t="n">
         <v>2.27</v>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="5" t="n">
         <v>10482.27</v>
       </c>
       <c r="F98" s="4" t="n">
@@ -20262,19 +20433,19 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="n">
+      <c r="A99" s="7" t="n">
         <v>46164</v>
       </c>
-      <c r="B99" s="3" t="n">
+      <c r="B99" s="5" t="n">
         <v>3849.9</v>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="C99" s="5" t="n">
         <v>5.62</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="5" t="n">
         <v>2.31</v>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="E99" s="5" t="n">
         <v>10563.88</v>
       </c>
       <c r="F99" s="4" t="n">
@@ -20299,19 +20470,19 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6" t="n">
+      <c r="A100" s="7" t="n">
         <v>46171</v>
       </c>
-      <c r="B100" s="3" t="n">
+      <c r="B100" s="5" t="n">
         <v>3880</v>
       </c>
-      <c r="C100" s="3" t="n">
+      <c r="C100" s="5" t="n">
         <v>5.53</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" s="5" t="n">
         <v>2.38</v>
       </c>
-      <c r="E100" s="3" t="n">
+      <c r="E100" s="5" t="n">
         <v>10788.19</v>
       </c>
       <c r="F100" s="4" t="n">
@@ -20336,19 +20507,19 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="n">
+      <c r="A101" s="7" t="n">
         <v>46177</v>
       </c>
-      <c r="B101" s="3" t="n">
+      <c r="B101" s="5" t="n">
         <v>3600</v>
       </c>
-      <c r="C101" s="3" t="n">
+      <c r="C101" s="5" t="n">
         <v>5.57</v>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="D101" s="5" t="n">
         <v>2.45</v>
       </c>
-      <c r="E101" s="3" t="n">
+      <c r="E101" s="5" t="n">
         <v>10304.04</v>
       </c>
       <c r="F101" s="4" t="n">
@@ -20373,19 +20544,19 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6" t="n">
+      <c r="A102" s="7" t="n">
         <v>46185</v>
       </c>
-      <c r="B102" s="3" t="n">
+      <c r="B102" s="5" t="n">
         <v>3712</v>
       </c>
-      <c r="C102" s="3" t="n">
+      <c r="C102" s="5" t="n">
         <v>5.54</v>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="D102" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E102" s="3" t="n">
+      <c r="E102" s="5" t="n">
         <v>10922.98</v>
       </c>
       <c r="F102" s="4" t="n">
@@ -20410,19 +20581,19 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="n">
+      <c r="A103" s="7" t="n">
         <v>46192</v>
       </c>
-      <c r="B103" s="3" t="n">
+      <c r="B103" s="5" t="n">
         <v>3820</v>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="C103" s="5" t="n">
         <v>5.45</v>
       </c>
-      <c r="D103" s="3" t="n">
+      <c r="D103" s="5" t="n">
         <v>2.49</v>
       </c>
-      <c r="E103" s="3" t="n">
+      <c r="E103" s="5" t="n">
         <v>10888.43</v>
       </c>
       <c r="F103" s="4" t="n">
@@ -20447,19 +20618,19 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="n">
+      <c r="A104" s="7" t="n">
         <v>46199</v>
       </c>
-      <c r="B104" s="3" t="n">
+      <c r="B104" s="5" t="n">
         <v>3765</v>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="C104" s="5" t="n">
         <v>5.45</v>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="D104" s="5" t="n">
         <v>2.43</v>
       </c>
-      <c r="E104" s="3" t="n">
+      <c r="E104" s="5" t="n">
         <v>10762.98</v>
       </c>
       <c r="F104" s="4" t="n">
@@ -20484,19 +20655,19 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6" t="n">
+      <c r="A105" s="7" t="n">
         <v>46206</v>
       </c>
-      <c r="B105" s="3" t="n">
+      <c r="B105" s="5" t="n">
         <v>3919.7</v>
       </c>
-      <c r="C105" s="3" t="n">
+      <c r="C105" s="5" t="n">
         <v>5.42</v>
       </c>
-      <c r="D105" s="3" t="n">
+      <c r="D105" s="5" t="n">
         <v>2.45</v>
       </c>
-      <c r="E105" s="3" t="n">
+      <c r="E105" s="5" t="n">
         <v>10821.14</v>
       </c>
       <c r="F105" s="4" t="n">
@@ -20521,19 +20692,19 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6" t="n">
+      <c r="A106" s="7" t="n">
         <v>46213</v>
       </c>
-      <c r="B106" s="3" t="n">
+      <c r="B106" s="5" t="n">
         <v>3901</v>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="C106" s="5" t="n">
         <v>5.48</v>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="D106" s="5" t="n">
         <v>2.42</v>
       </c>
-      <c r="E106" s="3" t="n">
+      <c r="E106" s="5" t="n">
         <v>10960.89</v>
       </c>
       <c r="F106" s="4" t="n">
@@ -20558,19 +20729,19 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6" t="n">
+      <c r="A107" s="7" t="n">
         <v>46220</v>
       </c>
-      <c r="B107" s="3" t="n">
+      <c r="B107" s="5" t="n">
         <v>3950</v>
       </c>
-      <c r="C107" s="3" t="n">
+      <c r="C107" s="5" t="n">
         <v>5.54</v>
       </c>
-      <c r="D107" s="3" t="n">
+      <c r="D107" s="5" t="n">
         <v>2.44</v>
       </c>
-      <c r="E107" s="3" t="n">
+      <c r="E107" s="5" t="n">
         <v>10886.14</v>
       </c>
       <c r="F107" s="4" t="n">
@@ -20595,19 +20766,19 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6" t="n">
+      <c r="A108" s="7" t="n">
         <v>46225</v>
       </c>
-      <c r="B108" s="3" t="n">
+      <c r="B108" s="5" t="n">
         <v>3820.2</v>
       </c>
-      <c r="C108" s="3" t="n">
+      <c r="C108" s="5" t="n">
         <v>5.68</v>
       </c>
-      <c r="D108" s="3" t="n">
+      <c r="D108" s="5" t="n">
         <v>2.48</v>
       </c>
-      <c r="E108" s="3" t="n">
+      <c r="E108" s="5" t="n">
         <v>11009.22</v>
       </c>
       <c r="F108" s="4" t="n">
@@ -20632,19 +20803,19 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6" t="n">
+      <c r="A109" s="7" t="n">
         <v>46233</v>
       </c>
-      <c r="B109" s="3" t="n">
+      <c r="B109" s="5" t="n">
         <v>3690</v>
       </c>
-      <c r="C109" s="3" t="n">
+      <c r="C109" s="5" t="n">
         <v>5.68</v>
       </c>
-      <c r="D109" s="3" t="n">
+      <c r="D109" s="5" t="n">
         <v>2.53</v>
       </c>
-      <c r="E109" s="3" t="n">
+      <c r="E109" s="5" t="n">
         <v>11030.67</v>
       </c>
       <c r="F109" s="4" t="n">
@@ -20669,19 +20840,19 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6" t="n">
+      <c r="A110" s="7" t="n">
         <v>46240</v>
       </c>
-      <c r="B110" s="3" t="n">
+      <c r="B110" s="5" t="n">
         <v>3940</v>
       </c>
-      <c r="C110" s="3" t="n">
+      <c r="C110" s="5" t="n">
         <v>5.63</v>
       </c>
-      <c r="D110" s="3" t="n">
+      <c r="D110" s="5" t="n">
         <v>2.56</v>
       </c>
-      <c r="E110" s="3" t="n">
+      <c r="E110" s="5" t="n">
         <v>11275.15</v>
       </c>
       <c r="F110" s="4" t="n">
@@ -20706,19 +20877,19 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="6" t="n">
+      <c r="A111" s="7" t="n">
         <v>46248</v>
       </c>
-      <c r="B111" s="3" t="n">
+      <c r="B111" s="5" t="n">
         <v>3970</v>
       </c>
-      <c r="C111" s="3" t="n">
+      <c r="C111" s="5" t="n">
         <v>5.66</v>
       </c>
-      <c r="D111" s="3" t="n">
+      <c r="D111" s="5" t="n">
         <v>2.52</v>
       </c>
-      <c r="E111" s="3" t="n">
+      <c r="E111" s="5" t="n">
         <v>11042.67</v>
       </c>
       <c r="F111" s="4" t="n">
@@ -20743,19 +20914,19 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="6" t="n">
+      <c r="A112" s="7" t="n">
         <v>46253</v>
       </c>
-      <c r="B112" s="3" t="n">
+      <c r="B112" s="5" t="n">
         <v>4000.1</v>
       </c>
-      <c r="C112" s="3" t="n">
+      <c r="C112" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="D112" s="3" t="n">
+      <c r="D112" s="5" t="n">
         <v>2.51</v>
       </c>
-      <c r="E112" s="3" t="n">
+      <c r="E112" s="5" t="n">
         <v>11241.32</v>
       </c>
       <c r="F112" s="4" t="n">
@@ -20780,19 +20951,19 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6" t="n">
+      <c r="A113" s="7" t="n">
         <v>46259</v>
       </c>
-      <c r="B113" s="3" t="n">
+      <c r="B113" s="5" t="n">
         <v>4062</v>
       </c>
-      <c r="C113" s="3" t="n">
+      <c r="C113" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="D113" s="3" t="n">
+      <c r="D113" s="5" t="n">
         <v>2.51</v>
       </c>
-      <c r="E113" s="3" t="n">
+      <c r="E113" s="5" t="n">
         <v>11450.75</v>
       </c>
       <c r="F113" s="4" t="n">
@@ -20817,19 +20988,19 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="6" t="n">
+      <c r="A114" s="7" t="n">
         <v>46268</v>
       </c>
-      <c r="B114" s="3" t="n">
+      <c r="B114" s="5" t="n">
         <v>3955.04</v>
       </c>
-      <c r="C114" s="3" t="n">
+      <c r="C114" s="5" t="n">
         <v>5.71</v>
       </c>
-      <c r="D114" s="3" t="n">
+      <c r="D114" s="5" t="n">
         <v>2.54</v>
       </c>
-      <c r="E114" s="3" t="n">
+      <c r="E114" s="5" t="n">
         <v>11479.48</v>
       </c>
       <c r="F114" s="4" t="n">
@@ -20854,19 +21025,19 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6" t="n">
+      <c r="A115" s="7" t="n">
         <v>46276</v>
       </c>
-      <c r="B115" s="3" t="n">
+      <c r="B115" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="C115" s="3" t="n">
+      <c r="C115" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D115" s="3" t="n">
+      <c r="D115" s="5" t="n">
         <v>2.52</v>
       </c>
-      <c r="E115" s="3" t="n">
+      <c r="E115" s="5" t="n">
         <v>11220.6</v>
       </c>
       <c r="F115" s="4" t="n">
@@ -20891,19 +21062,19 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="6" t="n">
+      <c r="A116" s="7" t="n">
         <v>46282</v>
       </c>
-      <c r="B116" s="3" t="n">
+      <c r="B116" s="5" t="n">
         <v>3900</v>
       </c>
-      <c r="C116" s="3" t="n">
+      <c r="C116" s="5" t="n">
         <v>6.03</v>
       </c>
-      <c r="D116" s="3" t="n">
+      <c r="D116" s="5" t="n">
         <v>2.62</v>
       </c>
-      <c r="E116" s="3" t="n">
+      <c r="E116" s="5" t="n">
         <v>11381.18</v>
       </c>
       <c r="F116" s="4" t="n">
@@ -20928,19 +21099,19 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6" t="n">
+      <c r="A117" s="7" t="n">
         <v>46289</v>
       </c>
-      <c r="B117" s="3" t="n">
+      <c r="B117" s="5" t="n">
         <v>3666</v>
       </c>
-      <c r="C117" s="3" t="n">
+      <c r="C117" s="5" t="n">
         <v>6.04</v>
       </c>
-      <c r="D117" s="3" t="n">
+      <c r="D117" s="5" t="n">
         <v>2.73</v>
       </c>
-      <c r="E117" s="3" t="n">
+      <c r="E117" s="5" t="n">
         <v>11299.82</v>
       </c>
       <c r="F117" s="4" t="n">
@@ -20965,19 +21136,19 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="6" t="n">
+      <c r="A118" s="7" t="n">
         <v>46295</v>
       </c>
-      <c r="B118" s="3" t="n">
+      <c r="B118" s="5" t="n">
         <v>3555</v>
       </c>
-      <c r="C118" s="3" t="n">
+      <c r="C118" s="5" t="n">
         <v>6.25</v>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="D118" s="5" t="n">
         <v>2.82</v>
       </c>
-      <c r="E118" s="3" t="n">
+      <c r="E118" s="5" t="n">
         <v>10969.49</v>
       </c>
       <c r="F118" s="4" t="n">

--- a/secciones/valuacion/modelos/Mallplaza_Sensibilidad_Tasas_Inflacion.xlsx
+++ b/secciones/valuacion/modelos/Mallplaza_Sensibilidad_Tasas_Inflacion.xlsx
@@ -791,31 +791,31 @@
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">Calculo!AI6</f>
-        <v>2522.32427145383</v>
+        <v>2538.13946300749</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">Calculo!AI7</f>
-        <v>2269.94576626277</v>
+        <v>2280.40327422701</v>
       </c>
       <c r="D6" s="0" t="n">
         <f aca="false">Calculo!AI8</f>
-        <v>2053.10833423148</v>
+        <v>2058.99849539439</v>
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">Calculo!AI9</f>
-        <v>1864.88552791714</v>
+        <v>1866.84413525407</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">Calculo!AI10</f>
-        <v>1700.03737988343</v>
+        <v>1698.58332061787</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">Calculo!AI11</f>
-        <v>1554.52672137775</v>
+        <v>1550.08882029799</v>
       </c>
       <c r="H6" s="0" t="n">
         <f aca="false">Calculo!AI12</f>
-        <v>1425.19292673489</v>
+        <v>1418.12950817865</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -824,31 +824,31 @@
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">Calculo!AI13</f>
-        <v>2519.48967403073</v>
+        <v>2535.27367025598</v>
       </c>
       <c r="C7" s="0" t="n">
         <f aca="false">Calculo!AI14</f>
-        <v>2266.46118093163</v>
+        <v>2276.8728543792</v>
       </c>
       <c r="D7" s="0" t="n">
         <f aca="false">Calculo!AI15</f>
-        <v>2049.20802462752</v>
+        <v>2055.04294084036</v>
       </c>
       <c r="E7" s="0" t="n">
         <f aca="false">Calculo!AI16</f>
-        <v>1860.7307780146</v>
+        <v>1862.62832998216</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">Calculo!AI17</f>
-        <v>1695.74059488589</v>
+        <v>1694.22217898572</v>
       </c>
       <c r="G7" s="0" t="n">
         <f aca="false">Calculo!AI18</f>
-        <v>1550.16689566966</v>
+        <v>1545.66310019562</v>
       </c>
       <c r="H7" s="0" t="n">
         <f aca="false">Calculo!AI19</f>
-        <v>1420.82582031647</v>
+        <v>1413.69621457943</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -857,31 +857,31 @@
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">Calculo!AI20</f>
-        <v>2516.95545045931</v>
+        <v>2532.71458877864</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">Calculo!AI21</f>
-        <v>2263.25164465211</v>
+        <v>2273.62325693371</v>
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">Calculo!AI22</f>
-        <v>2045.56167696511</v>
+        <v>2051.34665209483</v>
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">Calculo!AI23</f>
-        <v>1856.81199718015</v>
+        <v>1858.65339722932</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">Calculo!AI24</f>
-        <v>1691.66413461539</v>
+        <v>1690.08591754013</v>
       </c>
       <c r="G8" s="0" t="n">
         <f aca="false">Calculo!AI25</f>
-        <v>1546.01359238008</v>
+        <v>1541.4481510996</v>
       </c>
       <c r="H8" s="0" t="n">
         <f aca="false">Calculo!AI26</f>
-        <v>1416.65291908699</v>
+        <v>1409.46110103801</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -890,31 +890,31 @@
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">Calculo!AI27</f>
-        <v>2514.71089461663</v>
+        <v>2530.45127889161</v>
       </c>
       <c r="C9" s="0" t="n">
         <f aca="false">Calculo!AI28</f>
-        <v>2260.30715941169</v>
+        <v>2270.64426612137</v>
       </c>
       <c r="D9" s="0" t="n">
         <f aca="false">Calculo!AI29</f>
-        <v>2042.15994019964</v>
+        <v>2047.90007479544</v>
       </c>
       <c r="E9" s="0" t="n">
         <f aca="false">Calculo!AI30</f>
-        <v>1853.12042347488</v>
+        <v>1854.91038488575</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">Calculo!AI31</f>
-        <v>1687.79977352677</v>
+        <v>1686.16613253477</v>
       </c>
       <c r="G9" s="0" t="n">
         <f aca="false">Calculo!AI32</f>
-        <v>1542.05907511109</v>
+        <v>1537.4360693255</v>
       </c>
       <c r="H9" s="0" t="n">
         <f aca="false">Calculo!AI33</f>
-        <v>1412.66693371665</v>
+        <v>1405.41672091293</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -923,31 +923,31 @@
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">Calculo!AI34</f>
-        <v>2512.74571285406</v>
+        <v>2528.47322250459</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">Calculo!AI35</f>
-        <v>2257.61811501104</v>
+        <v>2267.9260625543</v>
       </c>
       <c r="D10" s="0" t="n">
         <f aca="false">Calculo!AI36</f>
-        <v>2038.9938283514</v>
+        <v>2044.69402770454</v>
       </c>
       <c r="E10" s="0" t="n">
         <f aca="false">Calculo!AI37</f>
-        <v>1849.64763902609</v>
+        <v>1851.39069249837</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">Calculo!AI38</f>
-        <v>1684.13961074471</v>
+        <v>1682.45475205022</v>
       </c>
       <c r="G10" s="0" t="n">
         <f aca="false">Calculo!AI39</f>
-        <v>1538.295914203</v>
+        <v>1533.61926468339</v>
       </c>
       <c r="H10" s="0" t="n">
         <f aca="false">Calculo!AI40</f>
-        <v>1408.86086501871</v>
+        <v>1401.55592409122</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -984,31 +984,31 @@
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">Calculo!AJ6</f>
-        <v>0.358416616913486</v>
+        <v>0.36557976155806</v>
       </c>
       <c r="C14" s="0" t="n">
         <f aca="false">Calculo!AJ7</f>
-        <v>0.222496283797194</v>
+        <v>0.226911525100046</v>
       </c>
       <c r="D14" s="0" t="n">
         <f aca="false">Calculo!AJ8</f>
-        <v>0.105716861669056</v>
+        <v>0.107790456501319</v>
       </c>
       <c r="E14" s="0" t="n">
         <f aca="false">Calculo!AJ9</f>
-        <v>0.00434806041174873</v>
+        <v>0.00440681303838719</v>
       </c>
       <c r="F14" s="0" t="n">
         <f aca="false">Calculo!AJ10</f>
-        <v>-0.0844321436606436</v>
+        <v>-0.0861215312387231</v>
       </c>
       <c r="G14" s="0" t="n">
         <f aca="false">Calculo!AJ11</f>
-        <v>-0.162797997999508</v>
+        <v>-0.16601512546196</v>
       </c>
       <c r="H14" s="0" t="n">
         <f aca="false">Calculo!AJ12</f>
-        <v>-0.232451681215296</v>
+        <v>-0.237012392793277</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1017,31 +1017,31 @@
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">Calculo!AJ13</f>
-        <v>0.356890023253275</v>
+        <v>0.364037896487476</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">Calculo!AJ14</f>
-        <v>0.220619634283707</v>
+        <v>0.225012074749016</v>
       </c>
       <c r="D15" s="0" t="n">
         <f aca="false">Calculo!AJ15</f>
-        <v>0.103616320736594</v>
+        <v>0.105662273506075</v>
       </c>
       <c r="E15" s="0" t="n">
         <f aca="false">Calculo!AJ16</f>
-        <v>0.00211048875190589</v>
+        <v>0.00213860892986517</v>
       </c>
       <c r="F15" s="0" t="n">
         <f aca="false">Calculo!AJ17</f>
-        <v>-0.0867462093840776</v>
+        <v>-0.0884679297865385</v>
       </c>
       <c r="G15" s="0" t="n">
         <f aca="false">Calculo!AJ18</f>
-        <v>-0.165146014769496</v>
+        <v>-0.168396268771937</v>
       </c>
       <c r="H15" s="0" t="n">
         <f aca="false">Calculo!AJ19</f>
-        <v>-0.23480361906633</v>
+        <v>-0.239397610825763</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1050,15 +1050,15 @@
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">Calculo!AJ20</f>
-        <v>0.355525198179298</v>
+        <v>0.362661049421125</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">Calculo!AJ21</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
       <c r="D16" s="0" t="n">
         <f aca="false">Calculo!AJ22</f>
-        <v>0.101652552908755</v>
+        <v>0.103673581719301</v>
       </c>
       <c r="E16" s="0" t="n">
         <f aca="false">Calculo!AJ23</f>
@@ -1066,15 +1066,15 @@
       </c>
       <c r="F16" s="0" t="n">
         <f aca="false">Calculo!AJ24</f>
-        <v>-0.0889416175765557</v>
+        <v>-0.0906933374132452</v>
       </c>
       <c r="G16" s="0" t="n">
         <f aca="false">Calculo!AJ25</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
       <c r="H16" s="0" t="n">
         <f aca="false">Calculo!AJ26</f>
-        <v>-0.237050966259161</v>
+        <v>-0.241676203245274</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1083,31 +1083,31 @@
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">Calculo!AJ27</f>
-        <v>0.354316375828897</v>
+        <v>0.361443334547334</v>
       </c>
       <c r="C17" s="0" t="n">
         <f aca="false">Calculo!AJ28</f>
-        <v>0.217305339929035</v>
+        <v>0.221660945233899</v>
       </c>
       <c r="D17" s="0" t="n">
         <f aca="false">Calculo!AJ29</f>
-        <v>0.0998205221104631</v>
+        <v>0.101819240665436</v>
       </c>
       <c r="E17" s="0" t="n">
         <f aca="false">Calculo!AJ30</f>
-        <v>-0.0019881246517538</v>
+        <v>-0.00201383020048185</v>
       </c>
       <c r="F17" s="0" t="n">
         <f aca="false">Calculo!AJ31</f>
-        <v>-0.0910227981669906</v>
+        <v>-0.0928022755354365</v>
       </c>
       <c r="G17" s="0" t="n">
         <f aca="false">Calculo!AJ32</f>
-        <v>-0.169512542221321</v>
+        <v>-0.172822608229515</v>
       </c>
       <c r="H17" s="0" t="n">
         <f aca="false">Calculo!AJ33</f>
-        <v>-0.239197648516919</v>
+        <v>-0.243852176523081</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1116,31 +1116,31 @@
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">Calculo!AJ34</f>
-        <v>0.35325801248056</v>
+        <v>0.360379092881849</v>
       </c>
       <c r="C18" s="0" t="n">
         <f aca="false">Calculo!AJ35</f>
-        <v>0.215857134938582</v>
+        <v>0.220198486675938</v>
       </c>
       <c r="D18" s="0" t="n">
         <f aca="false">Calculo!AJ36</f>
-        <v>0.098115388875087</v>
+        <v>0.100094310618944</v>
       </c>
       <c r="E18" s="0" t="n">
         <f aca="false">Calculo!AJ37</f>
-        <v>-0.00385841871171311</v>
+        <v>-0.00390750892112202</v>
       </c>
       <c r="F18" s="0" t="n">
         <f aca="false">Calculo!AJ38</f>
-        <v>-0.0929940062309281</v>
+        <v>-0.0947990870389044</v>
       </c>
       <c r="G18" s="0" t="n">
         <f aca="false">Calculo!AJ39</f>
-        <v>-0.171539220697012</v>
+        <v>-0.174876140452252</v>
       </c>
       <c r="H18" s="0" t="n">
         <f aca="false">Calculo!AJ40</f>
-        <v>-0.241247435304015</v>
+        <v>-0.245929377591051</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1192,47 +1192,47 @@
       </c>
       <c r="B22" s="0" t="n">
         <f aca="false">Calculo!AJ41</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
       <c r="C22" s="0" t="n">
         <f aca="false">Calculo!AJ42</f>
-        <v>-0.151993554258035</v>
+        <v>-0.154976465301876</v>
       </c>
       <c r="D22" s="0" t="n">
         <f aca="false">Calculo!AJ43</f>
-        <v>-0.136213490162946</v>
+        <v>-0.138889842623276</v>
       </c>
       <c r="E22" s="0" t="n">
         <f aca="false">Calculo!AJ44</f>
-        <v>-0.120027733474049</v>
+        <v>-0.122388945740681</v>
       </c>
       <c r="F22" s="0" t="n">
         <f aca="false">Calculo!AJ45</f>
-        <v>-0.103420639156367</v>
+        <v>-0.105457796479268</v>
       </c>
       <c r="G22" s="0" t="n">
         <f aca="false">Calculo!AJ46</f>
-        <v>-0.0863757491506102</v>
+        <v>-0.0880795863189292</v>
       </c>
       <c r="H22" s="0" t="n">
         <f aca="false">Calculo!AJ47</f>
-        <v>-0.0688757388844042</v>
+        <v>-0.0702366217659202</v>
       </c>
       <c r="I22" s="0" t="n">
         <f aca="false">Calculo!AJ48</f>
-        <v>-0.0509023595045717</v>
+        <v>-0.0519102653543994</v>
       </c>
       <c r="J22" s="0" t="n">
         <f aca="false">Calculo!AJ49</f>
-        <v>-0.0324363754258225</v>
+        <v>-0.0330808718645884</v>
       </c>
       <c r="K22" s="0" t="n">
         <f aca="false">Calculo!AJ50</f>
-        <v>-0.0134574967466479</v>
+        <v>-0.0137277192987832</v>
       </c>
       <c r="L22" s="0" t="n">
         <f aca="false">Calculo!AJ51</f>
-        <v>0.00605569396649108</v>
+        <v>0.0061710658943217</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1241,47 +1241,47 @@
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">Calculo!AJ52</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
       <c r="C23" s="0" t="n">
         <f aca="false">Calculo!AJ53</f>
-        <v>-0.15287899234932</v>
+        <v>-0.155876096653678</v>
       </c>
       <c r="D23" s="0" t="n">
         <f aca="false">Calculo!AJ54</f>
-        <v>-0.138005507731023</v>
+        <v>-0.140710696140094</v>
       </c>
       <c r="E23" s="0" t="n">
         <f aca="false">Calculo!AJ55</f>
-        <v>-0.122748295009658</v>
+        <v>-0.125153452847816</v>
       </c>
       <c r="F23" s="0" t="n">
         <f aca="false">Calculo!AJ56</f>
-        <v>-0.107092574437963</v>
+        <v>-0.109189272295299</v>
       </c>
       <c r="G23" s="0" t="n">
         <f aca="false">Calculo!AJ57</f>
-        <v>-0.0910227981669906</v>
+        <v>-0.0928022755354365</v>
       </c>
       <c r="H23" s="0" t="n">
         <f aca="false">Calculo!AJ58</f>
-        <v>-0.0745225997138173</v>
+        <v>-0.0759757475466749</v>
       </c>
       <c r="I23" s="0" t="n">
         <f aca="false">Calculo!AJ59</f>
-        <v>-0.0575747393867963</v>
+        <v>-0.0586920814955493</v>
       </c>
       <c r="J23" s="0" t="n">
         <f aca="false">Calculo!AJ60</f>
-        <v>-0.0401610452861012</v>
+        <v>-0.0409327184802405</v>
       </c>
       <c r="K23" s="0" t="n">
         <f aca="false">Calculo!AJ61</f>
-        <v>-0.0222623494551681</v>
+        <v>-0.022678082321721</v>
       </c>
       <c r="L23" s="0" t="n">
         <f aca="false">Calculo!AJ62</f>
-        <v>-0.00385841871171311</v>
+        <v>-0.00390750892112202</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1290,47 +1290,47 @@
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">Calculo!AJ63</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">Calculo!AJ64</f>
-        <v>-0.153764430440606</v>
+        <v>-0.156775728005479</v>
       </c>
       <c r="D24" s="0" t="n">
         <f aca="false">Calculo!AJ65</f>
-        <v>-0.1397975252991</v>
+        <v>-0.142531549656912</v>
       </c>
       <c r="E24" s="0" t="n">
         <f aca="false">Calculo!AJ66</f>
-        <v>-0.125468856545268</v>
+        <v>-0.127917959954951</v>
       </c>
       <c r="F24" s="0" t="n">
         <f aca="false">Calculo!AJ67</f>
-        <v>-0.110764509719558</v>
+        <v>-0.112920748111328</v>
       </c>
       <c r="G24" s="0" t="n">
         <f aca="false">Calculo!AJ68</f>
-        <v>-0.0956698471833708</v>
+        <v>-0.0975249647519435</v>
       </c>
       <c r="H24" s="0" t="n">
         <f aca="false">Calculo!AJ69</f>
-        <v>-0.0801694605432303</v>
+        <v>-0.0817148733274294</v>
       </c>
       <c r="I24" s="0" t="n">
         <f aca="false">Calculo!AJ70</f>
-        <v>-0.0642471192690213</v>
+        <v>-0.0654738976366995</v>
       </c>
       <c r="J24" s="0" t="n">
         <f aca="false">Calculo!AJ71</f>
-        <v>-0.0478857151463799</v>
+        <v>-0.0487845650958934</v>
       </c>
       <c r="K24" s="0" t="n">
         <f aca="false">Calculo!AJ72</f>
-        <v>-0.0310672021636879</v>
+        <v>-0.0316284453446585</v>
       </c>
       <c r="L24" s="0" t="n">
         <f aca="false">Calculo!AJ73</f>
-        <v>-0.0137725313899169</v>
+        <v>-0.0139860837365653</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1339,47 +1339,47 @@
       </c>
       <c r="B25" s="0" t="n">
         <f aca="false">Calculo!AJ74</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
       <c r="C25" s="0" t="n">
         <f aca="false">Calculo!AJ75</f>
-        <v>0.193186396479287</v>
+        <v>0.197042122790646</v>
       </c>
       <c r="D25" s="0" t="n">
         <f aca="false">Calculo!AJ76</f>
-        <v>0.168281230684348</v>
+        <v>0.171637054024299</v>
       </c>
       <c r="E25" s="0" t="n">
         <f aca="false">Calculo!AJ77</f>
-        <v>0.144139216355283</v>
+        <v>0.147011331182325</v>
       </c>
       <c r="F25" s="0" t="n">
         <f aca="false">Calculo!AJ78</f>
-        <v>0.120726126350907</v>
+        <v>0.123129998099332</v>
       </c>
       <c r="G25" s="0" t="n">
         <f aca="false">Calculo!AJ79</f>
-        <v>0.0980097473170249</v>
+        <v>0.0999601553001979</v>
       </c>
       <c r="H25" s="0" t="n">
         <f aca="false">Calculo!AJ80</f>
-        <v>0.0759597337568947</v>
+        <v>0.0774708109615088</v>
       </c>
       <c r="I25" s="0" t="n">
         <f aca="false">Calculo!AJ81</f>
-        <v>0.0545474746098629</v>
+        <v>0.0556327446476352</v>
       </c>
       <c r="J25" s="0" t="n">
         <f aca="false">Calculo!AJ82</f>
-        <v>0.0337459711050507</v>
+        <v>0.034418382562089</v>
       </c>
       <c r="K25" s="0" t="n">
         <f aca="false">Calculo!AJ83</f>
-        <v>0.0135297247938668</v>
+        <v>0.0138016831945562</v>
       </c>
       <c r="L25" s="0" t="n">
         <f aca="false">Calculo!AJ84</f>
-        <v>-0.00612536521473805</v>
+        <v>-0.00624196763325058</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1388,47 +1388,47 @@
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">Calculo!AJ85</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
       <c r="C26" s="0" t="n">
         <f aca="false">Calculo!AJ86</f>
-        <v>0.194375376288335</v>
+        <v>0.198251650961849</v>
       </c>
       <c r="D26" s="0" t="n">
         <f aca="false">Calculo!AJ87</f>
-        <v>0.170623769128919</v>
+        <v>0.174019935675659</v>
       </c>
       <c r="E26" s="0" t="n">
         <f aca="false">Calculo!AJ88</f>
-        <v>0.147601528998447</v>
+        <v>0.150533063199794</v>
       </c>
       <c r="F26" s="0" t="n">
         <f aca="false">Calculo!AJ89</f>
-        <v>0.125275967804174</v>
+        <v>0.127757649176433</v>
       </c>
       <c r="G26" s="0" t="n">
         <f aca="false">Calculo!AJ90</f>
-        <v>0.103616320736594</v>
+        <v>0.105662273506075</v>
       </c>
       <c r="H26" s="0" t="n">
         <f aca="false">Calculo!AJ91</f>
-        <v>0.0825936068995816</v>
+        <v>0.084217338008399</v>
       </c>
       <c r="I26" s="0" t="n">
         <f aca="false">Calculo!AJ92</f>
-        <v>0.0621805018864448</v>
+        <v>0.06339493628354</v>
       </c>
       <c r="J26" s="0" t="n">
         <f aca="false">Calculo!AJ93</f>
-        <v>0.0423512211242185</v>
+        <v>0.0431687345710288</v>
       </c>
       <c r="K26" s="0" t="n">
         <f aca="false">Calculo!AJ94</f>
-        <v>0.0230814129392316</v>
+        <v>0.0235138625371079</v>
       </c>
       <c r="L26" s="0" t="n">
         <f aca="false">Calculo!AJ95</f>
-        <v>0.00434806041174873</v>
+        <v>0.00440681303838719</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1437,47 +1437,47 @@
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">Calculo!AJ96</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
       <c r="C27" s="0" t="n">
         <f aca="false">Calculo!AJ97</f>
-        <v>0.195564356097383</v>
+        <v>0.199461179133052</v>
       </c>
       <c r="D27" s="0" t="n">
         <f aca="false">Calculo!AJ98</f>
-        <v>0.172966307573491</v>
+        <v>0.17640281732702</v>
       </c>
       <c r="E27" s="0" t="n">
         <f aca="false">Calculo!AJ99</f>
-        <v>0.15106384164161</v>
+        <v>0.154054795217262</v>
       </c>
       <c r="F27" s="0" t="n">
         <f aca="false">Calculo!AJ100</f>
-        <v>0.12982580925744</v>
+        <v>0.132385300253534</v>
       </c>
       <c r="G27" s="0" t="n">
         <f aca="false">Calculo!AJ101</f>
-        <v>0.109222894156163</v>
+        <v>0.111364391711952</v>
       </c>
       <c r="H27" s="0" t="n">
         <f aca="false">Calculo!AJ102</f>
-        <v>0.0892274800422681</v>
+        <v>0.0909638650552891</v>
       </c>
       <c r="I27" s="0" t="n">
         <f aca="false">Calculo!AJ103</f>
-        <v>0.0698135291630264</v>
+        <v>0.0711571279194452</v>
       </c>
       <c r="J27" s="0" t="n">
         <f aca="false">Calculo!AJ104</f>
-        <v>0.0509564711433863</v>
+        <v>0.0519190865799686</v>
       </c>
       <c r="K27" s="0" t="n">
         <f aca="false">Calculo!AJ105</f>
-        <v>0.0326331010845964</v>
+        <v>0.0332260418796599</v>
       </c>
       <c r="L27" s="0" t="n">
         <f aca="false">Calculo!AJ106</f>
-        <v>0.0148214860382356</v>
+        <v>0.0150555937100247</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1595,23 +1595,23 @@
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI35+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2396.37158617503</v>
+        <v>2404.61794420965</v>
       </c>
       <c r="C42" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI36+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2221.47215684732</v>
+        <v>2226.03231632984</v>
       </c>
       <c r="D42" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI37+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2069.99520538708</v>
+        <v>2071.3896481649</v>
       </c>
       <c r="E42" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI38+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1937.58878276197</v>
+        <v>1936.24089580638</v>
       </c>
       <c r="F42" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI39+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1820.9138255286</v>
+        <v>1817.17250591291</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI28+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2398.52282169555</v>
+        <v>2406.79250706329</v>
       </c>
       <c r="C43" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI29+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2224.00504632591</v>
+        <v>2228.59715400255</v>
       </c>
       <c r="D43" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI30+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2072.77343294611</v>
+        <v>2074.2054020748</v>
       </c>
       <c r="E43" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI31+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1940.51691298762</v>
+        <v>1939.21000019402</v>
       </c>
       <c r="F43" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI32+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1823.92435425508</v>
+        <v>1820.2259496266</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B44" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI21+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2400.87840988789</v>
+        <v>2409.17569971317</v>
       </c>
       <c r="C44" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI22+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2226.72643573829</v>
+        <v>2231.35441584207</v>
       </c>
       <c r="D44" s="3" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI23+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2075.72669191032</v>
+        <v>2077.19981194966</v>
       </c>
       <c r="E44" s="4" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI24+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1943.60840185851</v>
+        <v>1942.3458281983</v>
       </c>
       <c r="F44" s="4" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI25+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1827.08796807026</v>
+        <v>1823.43561504588</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1673,23 +1673,23 @@
       </c>
       <c r="B45" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI14+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2403.44603891151</v>
+        <v>2411.77537766956</v>
       </c>
       <c r="C45" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI15+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2229.64351386822</v>
+        <v>2234.31144683849</v>
       </c>
       <c r="D45" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI16+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2078.86171657788</v>
+        <v>2080.37975815193</v>
       </c>
       <c r="E45" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI17+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1946.86957007491</v>
+        <v>1945.65483735478</v>
       </c>
       <c r="F45" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI18+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1830.41061070193</v>
+        <v>1826.80757432269</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1699,23 +1699,23 @@
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI7+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2406.23370717642</v>
+        <v>2414.59971354781</v>
       </c>
       <c r="C46" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI8+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2232.76376155139</v>
+        <v>2237.47589048172</v>
       </c>
       <c r="D46" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI9+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>2082.18551649992</v>
+        <v>2083.75240236946</v>
       </c>
       <c r="E46" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI10+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1950.30699807294</v>
+        <v>1949.1437506605</v>
       </c>
       <c r="F46" s="0" t="n">
         <f aca="false">Supuestos!$B$12*Calculo!AI11+(1-Supuestos!$B$12)*Supuestos!$B$11</f>
-        <v>1833.8984712684</v>
+        <v>1830.3481504046</v>
       </c>
     </row>
   </sheetData>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">Calculo!AI107</f>
-        <v>1546.01359238008</v>
+        <v>1541.4481510996</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">B19/Calculo!AI5-1</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1939,25 +1939,25 @@
         <v>62</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>63</v>
@@ -2336,35 +2336,35 @@
       </c>
       <c r="X5" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C5+$C5*((1+Supuestos!$B$4+$B5/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y5" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C5+$C5*((1+Supuestos!$B$4+$B5/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z5" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C5+$C5*((1+Supuestos!$B$4+$B5/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA5" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C5+$C5*((1+Supuestos!$B$4+$B5/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB5" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C5+$C5*((1+Supuestos!$B$4+$B5/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC5" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C5+$C5*((1+Supuestos!$B$4+$B5/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD5" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C5+$C5*((1+Supuestos!$B$4+$B5/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE5" s="0" t="n">
         <f aca="false">SUMPRODUCT(X5:AC5,R5:W5)</f>
-        <v>1277298.84211244</v>
+        <v>1189254.51564242</v>
       </c>
       <c r="AF5" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B5/10000)-1</f>
@@ -2372,15 +2372,15 @@
       </c>
       <c r="AG5" s="0" t="n">
         <f aca="false">AD5/(K5-AF5)</f>
-        <v>7133037.37151091</v>
+        <v>7292231.82587913</v>
       </c>
       <c r="AH5" s="0" t="n">
         <f aca="false">AG5*Q5</f>
-        <v>4125700.43171208</v>
+        <v>4217777.42428979</v>
       </c>
       <c r="AI5" s="0" t="n">
         <f aca="false">(AE5+AH5-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1856.81199718015</v>
+        <v>1858.65339722932</v>
       </c>
       <c r="AJ5" s="0" t="n">
         <f aca="false">AI5/AI$5-1</f>
@@ -2479,35 +2479,35 @@
       </c>
       <c r="X6" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C6+$C6*((1+Supuestos!$B$4+$B6/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y6" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C6+$C6*((1+Supuestos!$B$4+$B6/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z6" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C6+$C6*((1+Supuestos!$B$4+$B6/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA6" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C6+$C6*((1+Supuestos!$B$4+$B6/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB6" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C6+$C6*((1+Supuestos!$B$4+$B6/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC6" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C6+$C6*((1+Supuestos!$B$4+$B6/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD6" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C6+$C6*((1+Supuestos!$B$4+$B6/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE6" s="0" t="n">
         <f aca="false">SUMPRODUCT(X6:AC6,R6:W6)</f>
-        <v>1331802.62001465</v>
+        <v>1243049.58732731</v>
       </c>
       <c r="AF6" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B6/10000)-1</f>
@@ -2515,19 +2515,19 @@
       </c>
       <c r="AG6" s="0" t="n">
         <f aca="false">AD6/(K6-AF6)</f>
-        <v>8441768.32519305</v>
+        <v>8630170.91338072</v>
       </c>
       <c r="AH6" s="0" t="n">
         <f aca="false">AG6*Q6</f>
-        <v>5528668.53446923</v>
+        <v>5652056.83665909</v>
       </c>
       <c r="AI6" s="0" t="n">
         <f aca="false">(AE6+AH6-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2522.32427145383</v>
+        <v>2538.13946300749</v>
       </c>
       <c r="AJ6" s="0" t="n">
         <f aca="false">AI6/AI$5-1</f>
-        <v>0.358416616913486</v>
+        <v>0.36557976155806</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2622,35 +2622,35 @@
       </c>
       <c r="X7" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C7+$C7*((1+Supuestos!$B$4+$B7/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y7" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C7+$C7*((1+Supuestos!$B$4+$B7/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z7" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C7+$C7*((1+Supuestos!$B$4+$B7/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA7" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C7+$C7*((1+Supuestos!$B$4+$B7/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB7" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C7+$C7*((1+Supuestos!$B$4+$B7/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC7" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C7+$C7*((1+Supuestos!$B$4+$B7/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD7" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C7+$C7*((1+Supuestos!$B$4+$B7/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE7" s="0" t="n">
         <f aca="false">SUMPRODUCT(X7:AC7,R7:W7)</f>
-        <v>1314548.06278427</v>
+        <v>1226011.9230748</v>
       </c>
       <c r="AF7" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B7/10000)-1</f>
@@ -2658,19 +2658,19 @@
       </c>
       <c r="AG7" s="0" t="n">
         <f aca="false">AD7/(K7-AF7)</f>
-        <v>7813417.19792379</v>
+        <v>7987796.30499851</v>
       </c>
       <c r="AH7" s="0" t="n">
         <f aca="false">AG7*Q7</f>
-        <v>4993214.1653312</v>
+        <v>5104652.24748234</v>
       </c>
       <c r="AI7" s="0" t="n">
         <f aca="false">(AE7+AH7-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2269.94576626277</v>
+        <v>2280.40327422701</v>
       </c>
       <c r="AJ7" s="0" t="n">
         <f aca="false">AI7/AI$5-1</f>
-        <v>0.222496283797194</v>
+        <v>0.226911525100046</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2765,35 +2765,35 @@
       </c>
       <c r="X8" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C8+$C8*((1+Supuestos!$B$4+$B8/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y8" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C8+$C8*((1+Supuestos!$B$4+$B8/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z8" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C8+$C8*((1+Supuestos!$B$4+$B8/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA8" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C8+$C8*((1+Supuestos!$B$4+$B8/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB8" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C8+$C8*((1+Supuestos!$B$4+$B8/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC8" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C8+$C8*((1+Supuestos!$B$4+$B8/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD8" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C8+$C8*((1+Supuestos!$B$4+$B8/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE8" s="0" t="n">
         <f aca="false">SUMPRODUCT(X8:AC8,R8:W8)</f>
-        <v>1297651.85950974</v>
+        <v>1209334.33498606</v>
       </c>
       <c r="AF8" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B8/10000)-1</f>
@@ -2801,19 +2801,19 @@
       </c>
       <c r="AG8" s="0" t="n">
         <f aca="false">AD8/(K8-AF8)</f>
-        <v>7272126.69674876</v>
+        <v>7434425.33354116</v>
       </c>
       <c r="AH8" s="0" t="n">
         <f aca="false">AG8*Q8</f>
-        <v>4535236.39245721</v>
+        <v>4636453.36992766</v>
       </c>
       <c r="AI8" s="0" t="n">
         <f aca="false">(AE8+AH8-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2053.10833423148</v>
+        <v>2058.99849539439</v>
       </c>
       <c r="AJ8" s="0" t="n">
         <f aca="false">AI8/AI$5-1</f>
-        <v>0.105716861669056</v>
+        <v>0.107790456501319</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2908,35 +2908,35 @@
       </c>
       <c r="X9" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C9+$C9*((1+Supuestos!$B$4+$B9/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y9" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C9+$C9*((1+Supuestos!$B$4+$B9/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z9" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C9+$C9*((1+Supuestos!$B$4+$B9/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA9" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C9+$C9*((1+Supuestos!$B$4+$B9/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB9" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C9+$C9*((1+Supuestos!$B$4+$B9/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC9" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C9+$C9*((1+Supuestos!$B$4+$B9/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD9" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C9+$C9*((1+Supuestos!$B$4+$B9/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE9" s="0" t="n">
         <f aca="false">SUMPRODUCT(X9:AC9,R9:W9)</f>
-        <v>1281104.55457198</v>
+        <v>1193007.2439841</v>
       </c>
       <c r="AF9" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B9/10000)-1</f>
@@ -2944,19 +2944,19 @@
       </c>
       <c r="AG9" s="0" t="n">
         <f aca="false">AD9/(K9-AF9)</f>
-        <v>6800975.19198506</v>
+        <v>6952758.71399267</v>
       </c>
       <c r="AH9" s="0" t="n">
         <f aca="false">AG9*Q9</f>
-        <v>4139575.75156657</v>
+        <v>4231962.41222232</v>
       </c>
       <c r="AI9" s="0" t="n">
         <f aca="false">(AE9+AH9-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1864.88552791714</v>
+        <v>1866.84413525407</v>
       </c>
       <c r="AJ9" s="0" t="n">
         <f aca="false">AI9/AI$5-1</f>
-        <v>0.00434806041174873</v>
+        <v>0.00440681303838719</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3051,35 +3051,35 @@
       </c>
       <c r="X10" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C10+$C10*((1+Supuestos!$B$4+$B10/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y10" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C10+$C10*((1+Supuestos!$B$4+$B10/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z10" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C10+$C10*((1+Supuestos!$B$4+$B10/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA10" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C10+$C10*((1+Supuestos!$B$4+$B10/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB10" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C10+$C10*((1+Supuestos!$B$4+$B10/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC10" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C10+$C10*((1+Supuestos!$B$4+$B10/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD10" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C10+$C10*((1+Supuestos!$B$4+$B10/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE10" s="0" t="n">
         <f aca="false">SUMPRODUCT(X10:AC10,R10:W10)</f>
-        <v>1264896.98941961</v>
+        <v>1177021.37328673</v>
       </c>
       <c r="AF10" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B10/10000)-1</f>
@@ -3087,19 +3087,19 @@
       </c>
       <c r="AG10" s="0" t="n">
         <f aca="false">AD10/(K10-AF10)</f>
-        <v>6387159.54282777</v>
+        <v>6529707.56626086</v>
       </c>
       <c r="AH10" s="0" t="n">
         <f aca="false">AG10*Q10</f>
-        <v>3794765.87252509</v>
+        <v>3879457.09886642</v>
       </c>
       <c r="AI10" s="0" t="n">
         <f aca="false">(AE10+AH10-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1700.03737988343</v>
+        <v>1698.58332061787</v>
       </c>
       <c r="AJ10" s="0" t="n">
         <f aca="false">AI10/AI$5-1</f>
-        <v>-0.0844321436606436</v>
+        <v>-0.0861215312387231</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3194,35 +3194,35 @@
       </c>
       <c r="X11" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C11+$C11*((1+Supuestos!$B$4+$B11/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y11" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C11+$C11*((1+Supuestos!$B$4+$B11/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z11" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C11+$C11*((1+Supuestos!$B$4+$B11/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA11" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C11+$C11*((1+Supuestos!$B$4+$B11/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB11" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C11+$C11*((1+Supuestos!$B$4+$B11/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC11" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C11+$C11*((1+Supuestos!$B$4+$B11/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD11" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C11+$C11*((1+Supuestos!$B$4+$B11/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE11" s="0" t="n">
         <f aca="false">SUMPRODUCT(X11:AC11,R11:W11)</f>
-        <v>1249020.29183014</v>
+        <v>1161367.7374494</v>
       </c>
       <c r="AF11" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B11/10000)-1</f>
@@ -3230,19 +3230,19 @@
       </c>
       <c r="AG11" s="0" t="n">
         <f aca="false">AD11/(K11-AF11)</f>
-        <v>6020813.9853912</v>
+        <v>6155185.94327341</v>
       </c>
       <c r="AH11" s="0" t="n">
         <f aca="false">AG11*Q11</f>
-        <v>3491974.22798713</v>
+        <v>3569907.77900321</v>
       </c>
       <c r="AI11" s="0" t="n">
         <f aca="false">(AE11+AH11-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1554.52672137775</v>
+        <v>1550.08882029799</v>
       </c>
       <c r="AJ11" s="0" t="n">
         <f aca="false">AI11/AI$5-1</f>
-        <v>-0.162797997999508</v>
+        <v>-0.16601512546196</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3337,35 +3337,35 @@
       </c>
       <c r="X12" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C12+$C12*((1+Supuestos!$B$4+$B12/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y12" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C12+$C12*((1+Supuestos!$B$4+$B12/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z12" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C12+$C12*((1+Supuestos!$B$4+$B12/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA12" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C12+$C12*((1+Supuestos!$B$4+$B12/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB12" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C12+$C12*((1+Supuestos!$B$4+$B12/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC12" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C12+$C12*((1+Supuestos!$B$4+$B12/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD12" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C12+$C12*((1+Supuestos!$B$4+$B12/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE12" s="0" t="n">
         <f aca="false">SUMPRODUCT(X12:AC12,R12:W12)</f>
-        <v>1233465.8656082</v>
+        <v>1146037.63185466</v>
       </c>
       <c r="AF12" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B12/10000)-1</f>
@@ -3373,19 +3373,19 @@
       </c>
       <c r="AG12" s="0" t="n">
         <f aca="false">AD12/(K12-AF12)</f>
-        <v>5694213.43901513</v>
+        <v>5821296.35674954</v>
       </c>
       <c r="AH12" s="0" t="n">
         <f aca="false">AG12*Q12</f>
-        <v>3224287.64394121</v>
+        <v>3296246.99105657</v>
       </c>
       <c r="AI12" s="0" t="n">
         <f aca="false">(AE12+AH12-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1425.19292673489</v>
+        <v>1418.12950817865</v>
       </c>
       <c r="AJ12" s="0" t="n">
         <f aca="false">AI12/AI$5-1</f>
-        <v>-0.232451681215296</v>
+        <v>-0.237012392793277</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3480,35 +3480,35 @@
       </c>
       <c r="X13" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C13+$C13*((1+Supuestos!$B$4+$B13/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y13" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C13+$C13*((1+Supuestos!$B$4+$B13/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z13" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C13+$C13*((1+Supuestos!$B$4+$B13/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA13" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C13+$C13*((1+Supuestos!$B$4+$B13/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB13" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C13+$C13*((1+Supuestos!$B$4+$B13/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC13" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C13+$C13*((1+Supuestos!$B$4+$B13/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD13" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C13+$C13*((1+Supuestos!$B$4+$B13/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE13" s="0" t="n">
         <f aca="false">SUMPRODUCT(X13:AC13,R13:W13)</f>
-        <v>1329788.58932394</v>
+        <v>1241060.83430853</v>
       </c>
       <c r="AF13" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B13/10000)-1</f>
@@ -3516,19 +3516,19 @@
       </c>
       <c r="AG13" s="0" t="n">
         <f aca="false">AD13/(K13-AF13)</f>
-        <v>8653715.45158958</v>
+        <v>8846848.25572654</v>
       </c>
       <c r="AH13" s="0" t="n">
         <f aca="false">AG13*Q13</f>
-        <v>5524474.79680335</v>
+        <v>5647769.50355207</v>
       </c>
       <c r="AI13" s="0" t="n">
         <f aca="false">(AE13+AH13-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2519.48967403073</v>
+        <v>2535.27367025598</v>
       </c>
       <c r="AJ13" s="0" t="n">
         <f aca="false">AI13/AI$5-1</f>
-        <v>0.356890023253275</v>
+        <v>0.364037896487476</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3623,35 +3623,35 @@
       </c>
       <c r="X14" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C14+$C14*((1+Supuestos!$B$4+$B14/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y14" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C14+$C14*((1+Supuestos!$B$4+$B14/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z14" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C14+$C14*((1+Supuestos!$B$4+$B14/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA14" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C14+$C14*((1+Supuestos!$B$4+$B14/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB14" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C14+$C14*((1+Supuestos!$B$4+$B14/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC14" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C14+$C14*((1+Supuestos!$B$4+$B14/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD14" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C14+$C14*((1+Supuestos!$B$4+$B14/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE14" s="0" t="n">
         <f aca="false">SUMPRODUCT(X14:AC14,R14:W14)</f>
-        <v>1312563.15777169</v>
+        <v>1224052.65488354</v>
       </c>
       <c r="AF14" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B14/10000)-1</f>
@@ -3659,19 +3659,19 @@
       </c>
       <c r="AG14" s="0" t="n">
         <f aca="false">AD14/(K14-AF14)</f>
-        <v>8006652.11952858</v>
+        <v>8185343.82533336</v>
       </c>
       <c r="AH14" s="0" t="n">
         <f aca="false">AG14*Q14</f>
-        <v>4987567.82846858</v>
+        <v>5098879.89620689</v>
       </c>
       <c r="AI14" s="0" t="n">
         <f aca="false">(AE14+AH14-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2266.46118093163</v>
+        <v>2276.8728543792</v>
       </c>
       <c r="AJ14" s="0" t="n">
         <f aca="false">AI14/AI$5-1</f>
-        <v>0.220619634283707</v>
+        <v>0.225012074749016</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3766,35 +3766,35 @@
       </c>
       <c r="X15" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C15+$C15*((1+Supuestos!$B$4+$B15/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y15" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C15+$C15*((1+Supuestos!$B$4+$B15/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z15" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C15+$C15*((1+Supuestos!$B$4+$B15/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA15" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C15+$C15*((1+Supuestos!$B$4+$B15/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB15" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C15+$C15*((1+Supuestos!$B$4+$B15/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC15" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C15+$C15*((1+Supuestos!$B$4+$B15/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD15" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C15+$C15*((1+Supuestos!$B$4+$B15/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE15" s="0" t="n">
         <f aca="false">SUMPRODUCT(X15:AC15,R15:W15)</f>
-        <v>1295695.50250287</v>
+        <v>1207403.96211123</v>
       </c>
       <c r="AF15" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B15/10000)-1</f>
@@ -3802,19 +3802,19 @@
       </c>
       <c r="AG15" s="0" t="n">
         <f aca="false">AD15/(K15-AF15)</f>
-        <v>7449622.31378554</v>
+        <v>7615882.28099516</v>
       </c>
       <c r="AH15" s="0" t="n">
         <f aca="false">AG15*Q15</f>
-        <v>4528651.0714314</v>
+        <v>4629721.07832916</v>
       </c>
       <c r="AI15" s="0" t="n">
         <f aca="false">(AE15+AH15-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2049.20802462752</v>
+        <v>2055.04294084036</v>
       </c>
       <c r="AJ15" s="0" t="n">
         <f aca="false">AI15/AI$5-1</f>
-        <v>0.103616320736594</v>
+        <v>0.105662273506075</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3909,35 +3909,35 @@
       </c>
       <c r="X16" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C16+$C16*((1+Supuestos!$B$4+$B16/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y16" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C16+$C16*((1+Supuestos!$B$4+$B16/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z16" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C16+$C16*((1+Supuestos!$B$4+$B16/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA16" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C16+$C16*((1+Supuestos!$B$4+$B16/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB16" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C16+$C16*((1+Supuestos!$B$4+$B16/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC16" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C16+$C16*((1+Supuestos!$B$4+$B16/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD16" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C16+$C16*((1+Supuestos!$B$4+$B16/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE16" s="0" t="n">
         <f aca="false">SUMPRODUCT(X16:AC16,R16:W16)</f>
-        <v>1279176.18182195</v>
+        <v>1191105.19117612</v>
       </c>
       <c r="AF16" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B16/10000)-1</f>
@@ -3945,19 +3945,19 @@
       </c>
       <c r="AG16" s="0" t="n">
         <f aca="false">AD16/(K16-AF16)</f>
-        <v>6965057.1808769</v>
+        <v>7120502.66921566</v>
       </c>
       <c r="AH16" s="0" t="n">
         <f aca="false">AG16*Q16</f>
-        <v>4132405.22203002</v>
+        <v>4224631.8514848</v>
       </c>
       <c r="AI16" s="0" t="n">
         <f aca="false">(AE16+AH16-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1860.7307780146</v>
+        <v>1862.62832998216</v>
       </c>
       <c r="AJ16" s="0" t="n">
         <f aca="false">AI16/AI$5-1</f>
-        <v>0.00211048875190589</v>
+        <v>0.00213860892986517</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4052,35 +4052,35 @@
       </c>
       <c r="X17" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C17+$C17*((1+Supuestos!$B$4+$B17/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y17" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C17+$C17*((1+Supuestos!$B$4+$B17/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z17" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C17+$C17*((1+Supuestos!$B$4+$B17/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA17" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C17+$C17*((1+Supuestos!$B$4+$B17/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB17" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C17+$C17*((1+Supuestos!$B$4+$B17/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC17" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C17+$C17*((1+Supuestos!$B$4+$B17/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD17" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C17+$C17*((1+Supuestos!$B$4+$B17/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE17" s="0" t="n">
         <f aca="false">SUMPRODUCT(X17:AC17,R17:W17)</f>
-        <v>1262996.05071394</v>
+        <v>1175147.07916021</v>
       </c>
       <c r="AF17" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B17/10000)-1</f>
@@ -4088,19 +4088,19 @@
       </c>
       <c r="AG17" s="0" t="n">
         <f aca="false">AD17/(K17-AF17)</f>
-        <v>6539679.80212916</v>
+        <v>6685631.75830436</v>
       </c>
       <c r="AH17" s="0" t="n">
         <f aca="false">AG17*Q17</f>
-        <v>3787256.85208616</v>
+        <v>3871780.49281852</v>
       </c>
       <c r="AI17" s="0" t="n">
         <f aca="false">(AE17+AH17-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1695.74059488589</v>
+        <v>1694.22217898572</v>
       </c>
       <c r="AJ17" s="0" t="n">
         <f aca="false">AI17/AI$5-1</f>
-        <v>-0.0867462093840776</v>
+        <v>-0.0884679297865385</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4195,35 +4195,35 @@
       </c>
       <c r="X18" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C18+$C18*((1+Supuestos!$B$4+$B18/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y18" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C18+$C18*((1+Supuestos!$B$4+$B18/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z18" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C18+$C18*((1+Supuestos!$B$4+$B18/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA18" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C18+$C18*((1+Supuestos!$B$4+$B18/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB18" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C18+$C18*((1+Supuestos!$B$4+$B18/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC18" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C18+$C18*((1+Supuestos!$B$4+$B18/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD18" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C18+$C18*((1+Supuestos!$B$4+$B18/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE18" s="0" t="n">
         <f aca="false">SUMPRODUCT(X18:AC18,R18:W18)</f>
-        <v>1247146.2501176</v>
+        <v>1159520.65409808</v>
       </c>
       <c r="AF18" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B18/10000)-1</f>
@@ -4231,19 +4231,19 @@
       </c>
       <c r="AG18" s="0" t="n">
         <f aca="false">AD18/(K18-AF18)</f>
-        <v>6163270.0214003</v>
+        <v>6300821.29963971</v>
       </c>
       <c r="AH18" s="0" t="n">
         <f aca="false">AG18*Q18</f>
-        <v>3484300.25139894</v>
+        <v>3562062.53533031</v>
       </c>
       <c r="AI18" s="0" t="n">
         <f aca="false">(AE18+AH18-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1550.16689566966</v>
+        <v>1545.66310019562</v>
       </c>
       <c r="AJ18" s="0" t="n">
         <f aca="false">AI18/AI$5-1</f>
-        <v>-0.165146014769496</v>
+        <v>-0.168396268771937</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4338,35 +4338,35 @@
       </c>
       <c r="X19" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C19+$C19*((1+Supuestos!$B$4+$B19/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y19" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C19+$C19*((1+Supuestos!$B$4+$B19/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z19" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C19+$C19*((1+Supuestos!$B$4+$B19/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA19" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C19+$C19*((1+Supuestos!$B$4+$B19/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB19" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C19+$C19*((1+Supuestos!$B$4+$B19/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC19" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C19+$C19*((1+Supuestos!$B$4+$B19/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD19" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C19+$C19*((1+Supuestos!$B$4+$B19/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE19" s="0" t="n">
         <f aca="false">SUMPRODUCT(X19:AC19,R19:W19)</f>
-        <v>1231618.19663523</v>
+        <v>1144217.22447834</v>
       </c>
       <c r="AF19" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B19/10000)-1</f>
@@ -4374,19 +4374,19 @@
       </c>
       <c r="AG19" s="0" t="n">
         <f aca="false">AD19/(K19-AF19)</f>
-        <v>5827832.62002856</v>
+        <v>5957897.63802499</v>
       </c>
       <c r="AH19" s="0" t="n">
         <f aca="false">AG19*Q19</f>
-        <v>3216571.34985783</v>
+        <v>3288358.48545062</v>
       </c>
       <c r="AI19" s="0" t="n">
         <f aca="false">(AE19+AH19-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1420.82582031647</v>
+        <v>1413.69621457943</v>
       </c>
       <c r="AJ19" s="0" t="n">
         <f aca="false">AI19/AI$5-1</f>
-        <v>-0.23480361906633</v>
+        <v>-0.239397610825763</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4481,35 +4481,35 @@
       </c>
       <c r="X20" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C20+$C20*((1+Supuestos!$B$4+$B20/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y20" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C20+$C20*((1+Supuestos!$B$4+$B20/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z20" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C20+$C20*((1+Supuestos!$B$4+$B20/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA20" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C20+$C20*((1+Supuestos!$B$4+$B20/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB20" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C20+$C20*((1+Supuestos!$B$4+$B20/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC20" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C20+$C20*((1+Supuestos!$B$4+$B20/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD20" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C20+$C20*((1+Supuestos!$B$4+$B20/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE20" s="0" t="n">
         <f aca="false">SUMPRODUCT(X20:AC20,R20:W20)</f>
-        <v>1327828.27275912</v>
+        <v>1239126.19202126</v>
       </c>
       <c r="AF20" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B20/10000)-1</f>
@@ -4517,19 +4517,19 @@
       </c>
       <c r="AG20" s="0" t="n">
         <f aca="false">AD20/(K20-AF20)</f>
-        <v>8870901.01063711</v>
+        <v>9068880.94156852</v>
       </c>
       <c r="AH20" s="0" t="n">
         <f aca="false">AG20*Q20</f>
-        <v>5520885.16374678</v>
+        <v>5644099.75740397</v>
       </c>
       <c r="AI20" s="0" t="n">
         <f aca="false">(AE20+AH20-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2516.95545045931</v>
+        <v>2532.71458877864</v>
       </c>
       <c r="AJ20" s="0" t="n">
         <f aca="false">AI20/AI$5-1</f>
-        <v>0.355525198179298</v>
+        <v>0.362661049421125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4624,35 +4624,35 @@
       </c>
       <c r="X21" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C21+$C21*((1+Supuestos!$B$4+$B21/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y21" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C21+$C21*((1+Supuestos!$B$4+$B21/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z21" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C21+$C21*((1+Supuestos!$B$4+$B21/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA21" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C21+$C21*((1+Supuestos!$B$4+$B21/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB21" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C21+$C21*((1+Supuestos!$B$4+$B21/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC21" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C21+$C21*((1+Supuestos!$B$4+$B21/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD21" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C21+$C21*((1+Supuestos!$B$4+$B21/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE21" s="0" t="n">
         <f aca="false">SUMPRODUCT(X21:AC21,R21:W21)</f>
-        <v>1310631.05293323</v>
+        <v>1222146.56553767</v>
       </c>
       <c r="AF21" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B21/10000)-1</f>
@@ -4660,19 +4660,19 @@
       </c>
       <c r="AG21" s="0" t="n">
         <f aca="false">AD21/(K21-AF21)</f>
-        <v>8204590.23273713</v>
+        <v>8387699.50265796</v>
       </c>
       <c r="AH21" s="0" t="n">
         <f aca="false">AG21*Q21</f>
-        <v>4982471.04885489</v>
+        <v>5093669.36714715</v>
       </c>
       <c r="AI21" s="0" t="n">
         <f aca="false">(AE21+AH21-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2263.25164465211</v>
+        <v>2273.62325693371</v>
       </c>
       <c r="AJ21" s="0" t="n">
         <f aca="false">AI21/AI$5-1</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4767,35 +4767,35 @@
       </c>
       <c r="X22" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C22+$C22*((1+Supuestos!$B$4+$B22/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y22" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C22+$C22*((1+Supuestos!$B$4+$B22/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z22" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C22+$C22*((1+Supuestos!$B$4+$B22/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA22" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C22+$C22*((1+Supuestos!$B$4+$B22/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB22" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C22+$C22*((1+Supuestos!$B$4+$B22/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC22" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C22+$C22*((1+Supuestos!$B$4+$B22/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD22" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C22+$C22*((1+Supuestos!$B$4+$B22/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE22" s="0" t="n">
         <f aca="false">SUMPRODUCT(X22:AC22,R22:W22)</f>
-        <v>1293791.05215962</v>
+        <v>1205525.85711866</v>
       </c>
       <c r="AF22" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B22/10000)-1</f>
@@ -4803,19 +4803,19 @@
       </c>
       <c r="AG22" s="0" t="n">
         <f aca="false">AD22/(K22-AF22)</f>
-        <v>7631382.14828452</v>
+        <v>7801698.61431394</v>
       </c>
       <c r="AH22" s="0" t="n">
         <f aca="false">AG22*Q22</f>
-        <v>4522570.02039398</v>
+        <v>4623504.31096902</v>
       </c>
       <c r="AI22" s="0" t="n">
         <f aca="false">(AE22+AH22-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2045.56167696511</v>
+        <v>2051.34665209483</v>
       </c>
       <c r="AJ22" s="0" t="n">
         <f aca="false">AI22/AI$5-1</f>
-        <v>0.101652552908755</v>
+        <v>0.103673581719301</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4910,35 +4910,35 @@
       </c>
       <c r="X23" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C23+$C23*((1+Supuestos!$B$4+$B23/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y23" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C23+$C23*((1+Supuestos!$B$4+$B23/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z23" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C23+$C23*((1+Supuestos!$B$4+$B23/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA23" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C23+$C23*((1+Supuestos!$B$4+$B23/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB23" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C23+$C23*((1+Supuestos!$B$4+$B23/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC23" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C23+$C23*((1+Supuestos!$B$4+$B23/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD23" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C23+$C23*((1+Supuestos!$B$4+$B23/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE23" s="0" t="n">
         <f aca="false">SUMPRODUCT(X23:AC23,R23:W23)</f>
-        <v>1277298.84211244</v>
+        <v>1189254.51564242</v>
       </c>
       <c r="AF23" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B23/10000)-1</f>
@@ -4946,15 +4946,15 @@
       </c>
       <c r="AG23" s="0" t="n">
         <f aca="false">AD23/(K23-AF23)</f>
-        <v>7133037.37151091</v>
+        <v>7292231.82587913</v>
       </c>
       <c r="AH23" s="0" t="n">
         <f aca="false">AG23*Q23</f>
-        <v>4125700.43171208</v>
+        <v>4217777.42428979</v>
       </c>
       <c r="AI23" s="0" t="n">
         <f aca="false">(AE23+AH23-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1856.81199718015</v>
+        <v>1858.65339722932</v>
       </c>
       <c r="AJ23" s="0" t="n">
         <f aca="false">AI23/AI$5-1</f>
@@ -5053,35 +5053,35 @@
       </c>
       <c r="X24" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C24+$C24*((1+Supuestos!$B$4+$B24/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y24" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C24+$C24*((1+Supuestos!$B$4+$B24/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z24" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C24+$C24*((1+Supuestos!$B$4+$B24/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA24" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C24+$C24*((1+Supuestos!$B$4+$B24/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB24" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C24+$C24*((1+Supuestos!$B$4+$B24/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC24" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C24+$C24*((1+Supuestos!$B$4+$B24/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD24" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C24+$C24*((1+Supuestos!$B$4+$B24/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE24" s="0" t="n">
         <f aca="false">SUMPRODUCT(X24:AC24,R24:W24)</f>
-        <v>1261145.29077672</v>
+        <v>1173323.29150517</v>
       </c>
       <c r="AF24" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B24/10000)-1</f>
@@ -5089,19 +5089,19 @@
       </c>
       <c r="AG24" s="0" t="n">
         <f aca="false">AD24/(K24-AF24)</f>
-        <v>6695788.74687793</v>
+        <v>6845224.72773811</v>
       </c>
       <c r="AH24" s="0" t="n">
         <f aca="false">AG24*Q24</f>
-        <v>3780180.16403098</v>
+        <v>3864545.8679077</v>
       </c>
       <c r="AI24" s="0" t="n">
         <f aca="false">(AE24+AH24-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1691.66413461539</v>
+        <v>1690.08591754013</v>
       </c>
       <c r="AJ24" s="0" t="n">
         <f aca="false">AI24/AI$5-1</f>
-        <v>-0.0889416175765557</v>
+        <v>-0.0906933374132452</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5196,35 +5196,35 @@
       </c>
       <c r="X25" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C25+$C25*((1+Supuestos!$B$4+$B25/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y25" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C25+$C25*((1+Supuestos!$B$4+$B25/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z25" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C25+$C25*((1+Supuestos!$B$4+$B25/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA25" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C25+$C25*((1+Supuestos!$B$4+$B25/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB25" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C25+$C25*((1+Supuestos!$B$4+$B25/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC25" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C25+$C25*((1+Supuestos!$B$4+$B25/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD25" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C25+$C25*((1+Supuestos!$B$4+$B25/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE25" s="0" t="n">
         <f aca="false">SUMPRODUCT(X25:AC25,R25:W25)</f>
-        <v>1245321.55173293</v>
+        <v>1157723.22568801</v>
       </c>
       <c r="AF25" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B25/10000)-1</f>
@@ -5232,19 +5232,19 @@
       </c>
       <c r="AG25" s="0" t="n">
         <f aca="false">AD25/(K25-AF25)</f>
-        <v>6309049.80175791</v>
+        <v>6449854.57936698</v>
       </c>
       <c r="AH25" s="0" t="n">
         <f aca="false">AG25*Q25</f>
-        <v>3477029.21557944</v>
+        <v>3554629.22522011</v>
       </c>
       <c r="AI25" s="0" t="n">
         <f aca="false">(AE25+AH25-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1546.01359238008</v>
+        <v>1541.4481510996</v>
       </c>
       <c r="AJ25" s="0" t="n">
         <f aca="false">AI25/AI$5-1</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5339,35 +5339,35 @@
       </c>
       <c r="X26" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C26+$C26*((1+Supuestos!$B$4+$B26/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y26" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C26+$C26*((1+Supuestos!$B$4+$B26/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z26" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C26+$C26*((1+Supuestos!$B$4+$B26/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA26" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C26+$C26*((1+Supuestos!$B$4+$B26/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB26" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C26+$C26*((1+Supuestos!$B$4+$B26/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC26" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C26+$C26*((1+Supuestos!$B$4+$B26/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD26" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C26+$C26*((1+Supuestos!$B$4+$B26/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE26" s="0" t="n">
         <f aca="false">SUMPRODUCT(X26:AC26,R26:W26)</f>
-        <v>1229819.05387779</v>
+        <v>1142445.63926959</v>
       </c>
       <c r="AF26" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B26/10000)-1</f>
@@ -5375,19 +5375,19 @@
       </c>
       <c r="AG26" s="0" t="n">
         <f aca="false">AD26/(K26-AF26)</f>
-        <v>5964546.34604984</v>
+        <v>6097662.5280715</v>
       </c>
       <c r="AH26" s="0" t="n">
         <f aca="false">AG26*Q26</f>
-        <v>3209231.83892272</v>
+        <v>3280855.17200365</v>
       </c>
       <c r="AI26" s="0" t="n">
         <f aca="false">(AE26+AH26-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1416.65291908699</v>
+        <v>1409.46110103801</v>
       </c>
       <c r="AJ26" s="0" t="n">
         <f aca="false">AI26/AI$5-1</f>
-        <v>-0.237050966259161</v>
+        <v>-0.241676203245274</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5482,35 +5482,35 @@
       </c>
       <c r="X27" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C27+$C27*((1+Supuestos!$B$4+$B27/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y27" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C27+$C27*((1+Supuestos!$B$4+$B27/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z27" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C27+$C27*((1+Supuestos!$B$4+$B27/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA27" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C27+$C27*((1+Supuestos!$B$4+$B27/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB27" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C27+$C27*((1+Supuestos!$B$4+$B27/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC27" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C27+$C27*((1+Supuestos!$B$4+$B27/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD27" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C27+$C27*((1+Supuestos!$B$4+$B27/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE27" s="0" t="n">
         <f aca="false">SUMPRODUCT(X27:AC27,R27:W27)</f>
-        <v>1325920.09501203</v>
+        <v>1237244.06177613</v>
       </c>
       <c r="AF27" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B27/10000)-1</f>
@@ -5518,19 +5518,19 @@
       </c>
       <c r="AG27" s="0" t="n">
         <f aca="false">AD27/(K27-AF27)</f>
-        <v>9093428.15012881</v>
+        <v>9296374.42074252</v>
       </c>
       <c r="AH27" s="0" t="n">
         <f aca="false">AG27*Q27</f>
-        <v>5517877.7641984</v>
+        <v>5641025.23899651</v>
       </c>
       <c r="AI27" s="0" t="n">
         <f aca="false">(AE27+AH27-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2514.71089461663</v>
+        <v>2530.45127889161</v>
       </c>
       <c r="AJ27" s="0" t="n">
         <f aca="false">AI27/AI$5-1</f>
-        <v>0.354316375828897</v>
+        <v>0.361443334547334</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5625,35 +5625,35 @@
       </c>
       <c r="X28" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C28+$C28*((1+Supuestos!$B$4+$B28/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y28" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C28+$C28*((1+Supuestos!$B$4+$B28/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z28" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C28+$C28*((1+Supuestos!$B$4+$B28/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA28" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C28+$C28*((1+Supuestos!$B$4+$B28/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB28" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C28+$C28*((1+Supuestos!$B$4+$B28/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC28" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C28+$C28*((1+Supuestos!$B$4+$B28/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD28" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C28+$C28*((1+Supuestos!$B$4+$B28/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE28" s="0" t="n">
         <f aca="false">SUMPRODUCT(X28:AC28,R28:W28)</f>
-        <v>1308750.20109063</v>
+        <v>1220292.08510704</v>
       </c>
       <c r="AF28" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B28/10000)-1</f>
@@ -5661,19 +5661,19 @@
       </c>
       <c r="AG28" s="0" t="n">
         <f aca="false">AD28/(K28-AF28)</f>
-        <v>8407321.72310883</v>
+        <v>8594955.53528454</v>
       </c>
       <c r="AH28" s="0" t="n">
         <f aca="false">AG28*Q28</f>
-        <v>4977903.47802097</v>
+        <v>5088999.85769875</v>
       </c>
       <c r="AI28" s="0" t="n">
         <f aca="false">(AE28+AH28-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2260.30715941169</v>
+        <v>2270.64426612137</v>
       </c>
       <c r="AJ28" s="0" t="n">
         <f aca="false">AI28/AI$5-1</f>
-        <v>0.217305339929035</v>
+        <v>0.221660945233899</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5768,35 +5768,35 @@
       </c>
       <c r="X29" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C29+$C29*((1+Supuestos!$B$4+$B29/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y29" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C29+$C29*((1+Supuestos!$B$4+$B29/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z29" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C29+$C29*((1+Supuestos!$B$4+$B29/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA29" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C29+$C29*((1+Supuestos!$B$4+$B29/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB29" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C29+$C29*((1+Supuestos!$B$4+$B29/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC29" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C29+$C29*((1+Supuestos!$B$4+$B29/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD29" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C29+$C29*((1+Supuestos!$B$4+$B29/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE29" s="0" t="n">
         <f aca="false">SUMPRODUCT(X29:AC29,R29:W29)</f>
-        <v>1291936.98878619</v>
+        <v>1203698.47817597</v>
       </c>
       <c r="AF29" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B29/10000)-1</f>
@@ -5804,19 +5804,19 @@
       </c>
       <c r="AG29" s="0" t="n">
         <f aca="false">AD29/(K29-AF29)</f>
-        <v>7817486.14118573</v>
+        <v>7991956.05855188</v>
       </c>
       <c r="AH29" s="0" t="n">
         <f aca="false">AG29*Q29</f>
-        <v>4516974.28025102</v>
+        <v>4617783.68562605</v>
       </c>
       <c r="AI29" s="0" t="n">
         <f aca="false">(AE29+AH29-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2042.15994019964</v>
+        <v>2047.90007479544</v>
       </c>
       <c r="AJ29" s="0" t="n">
         <f aca="false">AI29/AI$5-1</f>
-        <v>0.0998205221104631</v>
+        <v>0.101819240665436</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5911,35 +5911,35 @@
       </c>
       <c r="X30" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C30+$C30*((1+Supuestos!$B$4+$B30/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y30" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C30+$C30*((1+Supuestos!$B$4+$B30/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z30" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C30+$C30*((1+Supuestos!$B$4+$B30/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA30" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C30+$C30*((1+Supuestos!$B$4+$B30/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB30" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C30+$C30*((1+Supuestos!$B$4+$B30/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC30" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C30+$C30*((1+Supuestos!$B$4+$B30/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD30" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C30+$C30*((1+Supuestos!$B$4+$B30/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE30" s="0" t="n">
         <f aca="false">SUMPRODUCT(X30:AC30,R30:W30)</f>
-        <v>1275471.04260648</v>
+        <v>1187453.70300515</v>
       </c>
       <c r="AF30" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B30/10000)-1</f>
@@ -5947,19 +5947,19 @@
       </c>
       <c r="AG30" s="0" t="n">
         <f aca="false">AD30/(K30-AF30)</f>
-        <v>7304987.43399038</v>
+        <v>7468019.45361297</v>
       </c>
       <c r="AH30" s="0" t="n">
         <f aca="false">AG30*Q30</f>
-        <v>4119443.68480351</v>
+        <v>4211381.03989464</v>
       </c>
       <c r="AI30" s="0" t="n">
         <f aca="false">(AE30+AH30-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1853.12042347488</v>
+        <v>1854.91038488575</v>
       </c>
       <c r="AJ30" s="0" t="n">
         <f aca="false">AI30/AI$5-1</f>
-        <v>-0.0019881246517538</v>
+        <v>-0.00201383020048185</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6054,35 +6054,35 @@
       </c>
       <c r="X31" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C31+$C31*((1+Supuestos!$B$4+$B31/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y31" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C31+$C31*((1+Supuestos!$B$4+$B31/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z31" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C31+$C31*((1+Supuestos!$B$4+$B31/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA31" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C31+$C31*((1+Supuestos!$B$4+$B31/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB31" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C31+$C31*((1+Supuestos!$B$4+$B31/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC31" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C31+$C31*((1+Supuestos!$B$4+$B31/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD31" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C31+$C31*((1+Supuestos!$B$4+$B31/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE31" s="0" t="n">
         <f aca="false">SUMPRODUCT(X31:AC31,R31:W31)</f>
-        <v>1259343.24301737</v>
+        <v>1171548.52277278</v>
       </c>
       <c r="AF31" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B31/10000)-1</f>
@@ -6090,19 +6090,19 @@
       </c>
       <c r="AG31" s="0" t="n">
         <f aca="false">AD31/(K31-AF31)</f>
-        <v>6855551.24843406</v>
+        <v>7008552.793715</v>
       </c>
       <c r="AH31" s="0" t="n">
         <f aca="false">AG31*Q31</f>
-        <v>3773519.26100625</v>
+        <v>3857736.30747837</v>
       </c>
       <c r="AI31" s="0" t="n">
         <f aca="false">(AE31+AH31-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1687.79977352677</v>
+        <v>1686.16613253477</v>
       </c>
       <c r="AJ31" s="0" t="n">
         <f aca="false">AI31/AI$5-1</f>
-        <v>-0.0910227981669906</v>
+        <v>-0.0928022755354365</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6197,35 +6197,35 @@
       </c>
       <c r="X32" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C32+$C32*((1+Supuestos!$B$4+$B32/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y32" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C32+$C32*((1+Supuestos!$B$4+$B32/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z32" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C32+$C32*((1+Supuestos!$B$4+$B32/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA32" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C32+$C32*((1+Supuestos!$B$4+$B32/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB32" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C32+$C32*((1+Supuestos!$B$4+$B32/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC32" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C32+$C32*((1+Supuestos!$B$4+$B32/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD32" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C32+$C32*((1+Supuestos!$B$4+$B32/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE32" s="0" t="n">
         <f aca="false">SUMPRODUCT(X32:AC32,R32:W32)</f>
-        <v>1243544.75573822</v>
+        <v>1155973.99089089</v>
       </c>
       <c r="AF32" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B32/10000)-1</f>
@@ -6233,19 +6233,19 @@
       </c>
       <c r="AG32" s="0" t="n">
         <f aca="false">AD32/(K32-AF32)</f>
-        <v>6458212.5222887</v>
+        <v>6602346.29940671</v>
       </c>
       <c r="AH32" s="0" t="n">
         <f aca="false">AG32*Q32</f>
-        <v>3470145.61875507</v>
+        <v>3547592.00093195</v>
       </c>
       <c r="AI32" s="0" t="n">
         <f aca="false">(AE32+AH32-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1542.05907511109</v>
+        <v>1537.4360693255</v>
       </c>
       <c r="AJ32" s="0" t="n">
         <f aca="false">AI32/AI$5-1</f>
-        <v>-0.169512542221321</v>
+        <v>-0.172822608229515</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6340,35 +6340,35 @@
       </c>
       <c r="X33" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C33+$C33*((1+Supuestos!$B$4+$B33/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y33" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C33+$C33*((1+Supuestos!$B$4+$B33/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z33" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C33+$C33*((1+Supuestos!$B$4+$B33/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA33" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C33+$C33*((1+Supuestos!$B$4+$B33/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB33" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C33+$C33*((1+Supuestos!$B$4+$B33/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC33" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C33+$C33*((1+Supuestos!$B$4+$B33/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD33" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C33+$C33*((1+Supuestos!$B$4+$B33/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE33" s="0" t="n">
         <f aca="false">SUMPRODUCT(X33:AC33,R33:W33)</f>
-        <v>1228067.02147302</v>
+        <v>1140721.44052884</v>
       </c>
       <c r="AF33" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B33/10000)-1</f>
@@ -6376,19 +6376,19 @@
       </c>
       <c r="AG33" s="0" t="n">
         <f aca="false">AD33/(K33-AF33)</f>
-        <v>6104409.01144323</v>
+        <v>6240646.63522163</v>
       </c>
       <c r="AH33" s="0" t="n">
         <f aca="false">AG33*Q33</f>
-        <v>3202254.56336644</v>
+        <v>3273722.17827048</v>
       </c>
       <c r="AI33" s="0" t="n">
         <f aca="false">(AE33+AH33-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1412.66693371665</v>
+        <v>1405.41672091293</v>
       </c>
       <c r="AJ33" s="0" t="n">
         <f aca="false">AI33/AI$5-1</f>
-        <v>-0.239197648516919</v>
+        <v>-0.243852176523081</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6483,35 +6483,35 @@
       </c>
       <c r="X34" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C34+$C34*((1+Supuestos!$B$4+$B34/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y34" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C34+$C34*((1+Supuestos!$B$4+$B34/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z34" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C34+$C34*((1+Supuestos!$B$4+$B34/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA34" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C34+$C34*((1+Supuestos!$B$4+$B34/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB34" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C34+$C34*((1+Supuestos!$B$4+$B34/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC34" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C34+$C34*((1+Supuestos!$B$4+$B34/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD34" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C34+$C34*((1+Supuestos!$B$4+$B34/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE34" s="0" t="n">
         <f aca="false">SUMPRODUCT(X34:AC34,R34:W34)</f>
-        <v>1324062.53369539</v>
+        <v>1235412.89879664</v>
       </c>
       <c r="AF34" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B34/10000)-1</f>
@@ -6519,19 +6519,19 @@
       </c>
       <c r="AG34" s="0" t="n">
         <f aca="false">AD34/(K34-AF34)</f>
-        <v>9321401.53553174</v>
+        <v>9529435.69462962</v>
       </c>
       <c r="AH34" s="0" t="n">
         <f aca="false">AG34*Q34</f>
-        <v>5515431.57745501</v>
+        <v>5638524.45848841</v>
       </c>
       <c r="AI34" s="0" t="n">
         <f aca="false">(AE34+AH34-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2512.74571285406</v>
+        <v>2528.47322250459</v>
       </c>
       <c r="AJ34" s="0" t="n">
         <f aca="false">AI34/AI$5-1</f>
-        <v>0.35325801248056</v>
+        <v>0.360379092881849</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6626,35 +6626,35 @@
       </c>
       <c r="X35" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C35+$C35*((1+Supuestos!$B$4+$B35/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y35" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C35+$C35*((1+Supuestos!$B$4+$B35/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z35" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C35+$C35*((1+Supuestos!$B$4+$B35/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA35" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C35+$C35*((1+Supuestos!$B$4+$B35/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB35" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C35+$C35*((1+Supuestos!$B$4+$B35/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC35" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C35+$C35*((1+Supuestos!$B$4+$B35/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD35" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C35+$C35*((1+Supuestos!$B$4+$B35/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE35" s="0" t="n">
         <f aca="false">SUMPRODUCT(X35:AC35,R35:W35)</f>
-        <v>1306919.10702105</v>
+        <v>1218487.69658584</v>
       </c>
       <c r="AF35" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B35/10000)-1</f>
@@ -6662,19 +6662,19 @@
       </c>
       <c r="AG35" s="0" t="n">
         <f aca="false">AD35/(K35-AF35)</f>
-        <v>8614938.04622254</v>
+        <v>8807205.4198889</v>
       </c>
       <c r="AH35" s="0" t="n">
         <f aca="false">AG35*Q35</f>
-        <v>4973845.56485312</v>
+        <v>5084851.38040808</v>
       </c>
       <c r="AI35" s="0" t="n">
         <f aca="false">(AE35+AH35-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2257.61811501104</v>
+        <v>2267.9260625543</v>
       </c>
       <c r="AJ35" s="0" t="n">
         <f aca="false">AI35/AI$5-1</f>
-        <v>0.215857134938582</v>
+        <v>0.220198486675938</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6769,35 +6769,35 @@
       </c>
       <c r="X36" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C36+$C36*((1+Supuestos!$B$4+$B36/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y36" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C36+$C36*((1+Supuestos!$B$4+$B36/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z36" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C36+$C36*((1+Supuestos!$B$4+$B36/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA36" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C36+$C36*((1+Supuestos!$B$4+$B36/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB36" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C36+$C36*((1+Supuestos!$B$4+$B36/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC36" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C36+$C36*((1+Supuestos!$B$4+$B36/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD36" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C36+$C36*((1+Supuestos!$B$4+$B36/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE36" s="0" t="n">
         <f aca="false">SUMPRODUCT(X36:AC36,R36:W36)</f>
-        <v>1290131.84370106</v>
+        <v>1201920.33540949</v>
       </c>
       <c r="AF36" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B36/10000)-1</f>
@@ -6805,19 +6805,19 @@
       </c>
       <c r="AG36" s="0" t="n">
         <f aca="false">AD36/(K36-AF36)</f>
-        <v>8008015.31867878</v>
+        <v>8186737.44823344</v>
       </c>
       <c r="AH36" s="0" t="n">
         <f aca="false">AG36*Q36</f>
-        <v>4511845.64038851</v>
+        <v>4612540.58526346</v>
       </c>
       <c r="AI36" s="0" t="n">
         <f aca="false">(AE36+AH36-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2038.9938283514</v>
+        <v>2044.69402770454</v>
       </c>
       <c r="AJ36" s="0" t="n">
         <f aca="false">AI36/AI$5-1</f>
-        <v>0.098115388875087</v>
+        <v>0.100094310618944</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6912,35 +6912,35 @@
       </c>
       <c r="X37" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C37+$C37*((1+Supuestos!$B$4+$B37/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y37" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C37+$C37*((1+Supuestos!$B$4+$B37/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z37" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C37+$C37*((1+Supuestos!$B$4+$B37/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA37" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C37+$C37*((1+Supuestos!$B$4+$B37/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB37" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C37+$C37*((1+Supuestos!$B$4+$B37/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC37" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C37+$C37*((1+Supuestos!$B$4+$B37/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD37" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C37+$C37*((1+Supuestos!$B$4+$B37/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE37" s="0" t="n">
         <f aca="false">SUMPRODUCT(X37:AC37,R37:W37)</f>
-        <v>1273691.34055792</v>
+        <v>1185701.28990184</v>
       </c>
       <c r="AF37" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B37/10000)-1</f>
@@ -6948,19 +6948,19 @@
       </c>
       <c r="AG37" s="0" t="n">
         <f aca="false">AD37/(K37-AF37)</f>
-        <v>7480979.98181372</v>
+        <v>7647939.78649677</v>
       </c>
       <c r="AH37" s="0" t="n">
         <f aca="false">AG37*Q37</f>
-        <v>4113617.98890922</v>
+        <v>4205425.3266696</v>
       </c>
       <c r="AI37" s="0" t="n">
         <f aca="false">(AE37+AH37-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1849.64763902609</v>
+        <v>1851.39069249837</v>
       </c>
       <c r="AJ37" s="0" t="n">
         <f aca="false">AI37/AI$5-1</f>
-        <v>-0.00385841871171311</v>
+        <v>-0.00390750892112202</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7055,35 +7055,35 @@
       </c>
       <c r="X38" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C38+$C38*((1+Supuestos!$B$4+$B38/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y38" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C38+$C38*((1+Supuestos!$B$4+$B38/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z38" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C38+$C38*((1+Supuestos!$B$4+$B38/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA38" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C38+$C38*((1+Supuestos!$B$4+$B38/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB38" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C38+$C38*((1+Supuestos!$B$4+$B38/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC38" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C38+$C38*((1+Supuestos!$B$4+$B38/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD38" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C38+$C38*((1+Supuestos!$B$4+$B38/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE38" s="0" t="n">
         <f aca="false">SUMPRODUCT(X38:AC38,R38:W38)</f>
-        <v>1257588.49003585</v>
+        <v>1169821.33550783</v>
       </c>
       <c r="AF38" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B38/10000)-1</f>
@@ -7091,19 +7091,19 @@
       </c>
       <c r="AG38" s="0" t="n">
         <f aca="false">AD38/(K38-AF38)</f>
-        <v>7019033.00997765</v>
+        <v>7175683.12577246</v>
       </c>
       <c r="AH38" s="0" t="n">
         <f aca="false">AG38*Q38</f>
-        <v>3767258.25749507</v>
+        <v>3851335.57148215</v>
       </c>
       <c r="AI38" s="0" t="n">
         <f aca="false">(AE38+AH38-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1684.13961074471</v>
+        <v>1682.45475205022</v>
       </c>
       <c r="AJ38" s="0" t="n">
         <f aca="false">AI38/AI$5-1</f>
-        <v>-0.0929940062309281</v>
+        <v>-0.0947990870389044</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7198,35 +7198,35 @@
       </c>
       <c r="X39" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C39+$C39*((1+Supuestos!$B$4+$B39/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y39" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C39+$C39*((1+Supuestos!$B$4+$B39/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z39" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C39+$C39*((1+Supuestos!$B$4+$B39/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA39" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C39+$C39*((1+Supuestos!$B$4+$B39/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB39" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C39+$C39*((1+Supuestos!$B$4+$B39/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC39" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C39+$C39*((1+Supuestos!$B$4+$B39/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD39" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C39+$C39*((1+Supuestos!$B$4+$B39/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE39" s="0" t="n">
         <f aca="false">SUMPRODUCT(X39:AC39,R39:W39)</f>
-        <v>1241814.46950629</v>
+        <v>1154271.53757147</v>
       </c>
       <c r="AF39" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B39/10000)-1</f>
@@ -7234,19 +7234,19 @@
       </c>
       <c r="AG39" s="0" t="n">
         <f aca="false">AD39/(K39-AF39)</f>
-        <v>6610818.12104595</v>
+        <v>6758357.73550398</v>
       </c>
       <c r="AH39" s="0" t="n">
         <f aca="false">AG39*Q39</f>
-        <v>3463634.58259828</v>
+        <v>3540935.65208515</v>
       </c>
       <c r="AI39" s="0" t="n">
         <f aca="false">(AE39+AH39-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1538.295914203</v>
+        <v>1533.61926468339</v>
       </c>
       <c r="AJ39" s="0" t="n">
         <f aca="false">AI39/AI$5-1</f>
-        <v>-0.171539220697012</v>
+        <v>-0.174876140452252</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7341,35 +7341,35 @@
       </c>
       <c r="X40" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C40+$C40*((1+Supuestos!$B$4+$B40/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y40" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C40+$C40*((1+Supuestos!$B$4+$B40/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z40" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C40+$C40*((1+Supuestos!$B$4+$B40/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA40" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C40+$C40*((1+Supuestos!$B$4+$B40/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB40" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C40+$C40*((1+Supuestos!$B$4+$B40/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC40" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C40+$C40*((1+Supuestos!$B$4+$B40/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD40" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C40+$C40*((1+Supuestos!$B$4+$B40/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE40" s="0" t="n">
         <f aca="false">SUMPRODUCT(X40:AC40,R40:W40)</f>
-        <v>1226360.73100903</v>
+        <v>1139043.24086935</v>
       </c>
       <c r="AF40" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B40/10000)-1</f>
@@ -7377,19 +7377,19 @@
       </c>
       <c r="AG40" s="0" t="n">
         <f aca="false">AD40/(K40-AF40)</f>
-        <v>6247475.67957088</v>
+        <v>6386906.25173643</v>
       </c>
       <c r="AH40" s="0" t="n">
         <f aca="false">AG40*Q40</f>
-        <v>3195625.56338195</v>
+        <v>3266945.23289042</v>
       </c>
       <c r="AI40" s="0" t="n">
         <f aca="false">(AE40+AH40-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1408.86086501871</v>
+        <v>1401.55592409122</v>
       </c>
       <c r="AJ40" s="0" t="n">
         <f aca="false">AI40/AI$5-1</f>
-        <v>-0.241247435304015</v>
+        <v>-0.245929377591051</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7483,35 +7483,35 @@
       </c>
       <c r="X41" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C41+$C41*((1+Supuestos!$B$4+$B41/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y41" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C41+$C41*((1+Supuestos!$B$4+$B41/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z41" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C41+$C41*((1+Supuestos!$B$4+$B41/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA41" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C41+$C41*((1+Supuestos!$B$4+$B41/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB41" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C41+$C41*((1+Supuestos!$B$4+$B41/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC41" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C41+$C41*((1+Supuestos!$B$4+$B41/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD41" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C41+$C41*((1+Supuestos!$B$4+$B41/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE41" s="0" t="n">
         <f aca="false">SUMPRODUCT(X41:AC41,R41:W41)</f>
-        <v>1245321.55173293</v>
+        <v>1157723.22568801</v>
       </c>
       <c r="AF41" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B41/10000)-1</f>
@@ -7519,19 +7519,19 @@
       </c>
       <c r="AG41" s="0" t="n">
         <f aca="false">AD41/(K41-AF41)</f>
-        <v>6309049.80175791</v>
+        <v>6449854.57936698</v>
       </c>
       <c r="AH41" s="0" t="n">
         <f aca="false">AG41*Q41</f>
-        <v>3477029.21557944</v>
+        <v>3554629.22522011</v>
       </c>
       <c r="AI41" s="0" t="n">
         <f aca="false">(AE41+AH41-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1546.01359238008</v>
+        <v>1541.4481510996</v>
       </c>
       <c r="AJ41" s="0" t="n">
         <f aca="false">AI41/AI$5-1</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7625,35 +7625,35 @@
       </c>
       <c r="X42" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C42+$C42*((1+Supuestos!$B$4+$B42/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113453.236264209</v>
+        <v>88535.2518770115</v>
       </c>
       <c r="Y42" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C42+$C42*((1+Supuestos!$B$4+$B42/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199634.073765909</v>
+        <v>150126.654930958</v>
       </c>
       <c r="Z42" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C42+$C42*((1+Supuestos!$B$4+$B42/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260192.21203752</v>
+        <v>213647.093792689</v>
       </c>
       <c r="AA42" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C42+$C42*((1+Supuestos!$B$4+$B42/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>376414.844445742</v>
+        <v>384056.369366458</v>
       </c>
       <c r="AB42" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C42+$C42*((1+Supuestos!$B$4+$B42/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>378534.695890009</v>
+        <v>388589.364868642</v>
       </c>
       <c r="AC42" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C42+$C42*((1+Supuestos!$B$4+$B42/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>400654.777593379</v>
+        <v>411685.526365467</v>
       </c>
       <c r="AD42" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C42+$C42*((1+Supuestos!$B$4+$B42/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>531923.39286711</v>
+        <v>543794.808910909</v>
       </c>
       <c r="AE42" s="0" t="n">
         <f aca="false">SUMPRODUCT(X42:AC42,R42:W42)</f>
-        <v>1248621.2248216</v>
+        <v>1160976.15542842</v>
       </c>
       <c r="AF42" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B42/10000)-1</f>
@@ -7661,19 +7661,19 @@
       </c>
       <c r="AG42" s="0" t="n">
         <f aca="false">AD42/(K42-AF42)</f>
-        <v>6418328.52528589</v>
+        <v>6561572.17512568</v>
       </c>
       <c r="AH42" s="0" t="n">
         <f aca="false">AG42*Q42</f>
-        <v>3536308.68246451</v>
+        <v>3615231.6856484</v>
       </c>
       <c r="AI42" s="0" t="n">
         <f aca="false">(AE42+AH42-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1574.58854213978</v>
+        <v>1570.60586350539</v>
       </c>
       <c r="AJ42" s="0" t="n">
         <f aca="false">AI42/AI$5-1</f>
-        <v>-0.151993554258035</v>
+        <v>-0.154976465301876</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7767,35 +7767,35 @@
       </c>
       <c r="X43" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C43+$C43*((1+Supuestos!$B$4+$B43/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113480.736747688</v>
+        <v>88556.7123686801</v>
       </c>
       <c r="Y43" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C43+$C43*((1+Supuestos!$B$4+$B43/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199827.705263257</v>
+        <v>150272.267593354</v>
       </c>
       <c r="Z43" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C43+$C43*((1+Supuestos!$B$4+$B43/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260697.194377825</v>
+        <v>214061.741135813</v>
       </c>
       <c r="AA43" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C43+$C43*((1+Supuestos!$B$4+$B43/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>377511.197673661</v>
+        <v>385174.979449111</v>
       </c>
       <c r="AB43" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C43+$C43*((1+Supuestos!$B$4+$B43/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>380005.44576982</v>
+        <v>390099.180924823</v>
       </c>
       <c r="AC43" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C43+$C43*((1+Supuestos!$B$4+$B43/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>402601.590142696</v>
+        <v>413685.93817614</v>
       </c>
       <c r="AD43" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C43+$C43*((1+Supuestos!$B$4+$B43/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>535026.486287538</v>
+        <v>546967.156877218</v>
       </c>
       <c r="AE43" s="0" t="n">
         <f aca="false">SUMPRODUCT(X43:AC43,R43:W43)</f>
-        <v>1251934.87246423</v>
+        <v>1164243.12117629</v>
       </c>
       <c r="AF43" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B43/10000)-1</f>
@@ -7803,19 +7803,19 @@
       </c>
       <c r="AG43" s="0" t="n">
         <f aca="false">AD43/(K43-AF43)</f>
-        <v>6530463.96617084</v>
+        <v>6676210.24418952</v>
       </c>
       <c r="AH43" s="0" t="n">
         <f aca="false">AG43*Q43</f>
-        <v>3597163.37582027</v>
+        <v>3677444.52830297</v>
       </c>
       <c r="AI43" s="0" t="n">
         <f aca="false">(AE43+AH43-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1603.88915446781</v>
+        <v>1600.50531939692</v>
       </c>
       <c r="AJ43" s="0" t="n">
         <f aca="false">AI43/AI$5-1</f>
-        <v>-0.136213490162946</v>
+        <v>-0.138889842623276</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7909,35 +7909,35 @@
       </c>
       <c r="X44" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C44+$C44*((1+Supuestos!$B$4+$B44/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113508.217252608</v>
+        <v>88578.1572697236</v>
       </c>
       <c r="Y44" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C44+$C44*((1+Supuestos!$B$4+$B44/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200021.336760605</v>
+        <v>150417.880255751</v>
       </c>
       <c r="Z44" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C44+$C44*((1+Supuestos!$B$4+$B44/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261202.666279294</v>
+        <v>214476.790463758</v>
       </c>
       <c r="AA44" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C44+$C44*((1+Supuestos!$B$4+$B44/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>378609.6776773</v>
+        <v>386295.759482748</v>
       </c>
       <c r="AB44" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C44+$C44*((1+Supuestos!$B$4+$B44/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>381480.477305314</v>
+        <v>391613.392366369</v>
       </c>
       <c r="AC44" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C44+$C44*((1+Supuestos!$B$4+$B44/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>404555.963118428</v>
+        <v>415694.118565406</v>
       </c>
       <c r="AD44" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C44+$C44*((1+Supuestos!$B$4+$B44/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>538144.650551117</v>
+        <v>550154.912036333</v>
       </c>
       <c r="AE44" s="0" t="n">
         <f aca="false">SUMPRODUCT(X44:AC44,R44:W44)</f>
-        <v>1255262.57079213</v>
+        <v>1167524.20003642</v>
       </c>
       <c r="AF44" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B44/10000)-1</f>
@@ -7945,19 +7945,19 @@
       </c>
       <c r="AG44" s="0" t="n">
         <f aca="false">AD44/(K44-AF44)</f>
-        <v>6645564.97433967</v>
+        <v>6793880.0657878</v>
       </c>
       <c r="AH44" s="0" t="n">
         <f aca="false">AG44*Q44</f>
-        <v>3659653.73426778</v>
+        <v>3741329.54066833</v>
       </c>
       <c r="AI44" s="0" t="n">
         <f aca="false">(AE44+AH44-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1633.94306167119</v>
+        <v>1631.17476744509</v>
       </c>
       <c r="AJ44" s="0" t="n">
         <f aca="false">AI44/AI$5-1</f>
-        <v>-0.120027733474049</v>
+        <v>-0.122388945740681</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8051,35 +8051,35 @@
       </c>
       <c r="X45" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C45+$C45*((1+Supuestos!$B$4+$B45/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113535.6778128</v>
+        <v>88599.5866065446</v>
       </c>
       <c r="Y45" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C45+$C45*((1+Supuestos!$B$4+$B45/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200214.968257953</v>
+        <v>150563.492918148</v>
       </c>
       <c r="Z45" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C45+$C45*((1+Supuestos!$B$4+$B45/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261708.627741927</v>
+        <v>214892.241776524</v>
       </c>
       <c r="AA45" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C45+$C45*((1+Supuestos!$B$4+$B45/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379710.28651749</v>
+        <v>387418.711570035</v>
       </c>
       <c r="AB45" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C45+$C45*((1+Supuestos!$B$4+$B45/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>382959.798798294</v>
+        <v>393132.007715596</v>
       </c>
       <c r="AC45" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C45+$C45*((1+Supuestos!$B$4+$B45/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>406517.918519856</v>
+        <v>417710.090138226</v>
       </c>
       <c r="AD45" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C45+$C45*((1+Supuestos!$B$4+$B45/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>541277.944156904</v>
+        <v>553358.134192886</v>
       </c>
       <c r="AE45" s="0" t="n">
         <f aca="false">SUMPRODUCT(X45:AC45,R45:W45)</f>
-        <v>1258604.39643171</v>
+        <v>1170819.46961741</v>
       </c>
       <c r="AF45" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B45/10000)-1</f>
@@ -8087,19 +8087,19 @@
       </c>
       <c r="AG45" s="0" t="n">
         <f aca="false">AD45/(K45-AF45)</f>
-        <v>6763745.98222737</v>
+        <v>6914698.62624777</v>
       </c>
       <c r="AH45" s="0" t="n">
         <f aca="false">AG45*Q45</f>
-        <v>3723843.30043675</v>
+        <v>3806951.68351258</v>
       </c>
       <c r="AI45" s="0" t="n">
         <f aca="false">(AE45+AH45-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1664.77931363856</v>
+        <v>1662.64390553881</v>
       </c>
       <c r="AJ45" s="0" t="n">
         <f aca="false">AI45/AI$5-1</f>
-        <v>-0.103420639156367</v>
+        <v>-0.105457796479268</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8193,35 +8193,35 @@
       </c>
       <c r="X46" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C46+$C46*((1+Supuestos!$B$4+$B46/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113563.118462009</v>
+        <v>88621.0004054751</v>
       </c>
       <c r="Y46" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C46+$C46*((1+Supuestos!$B$4+$B46/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200408.599755302</v>
+        <v>150709.105580544</v>
       </c>
       <c r="Z46" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C46+$C46*((1+Supuestos!$B$4+$B46/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>262215.078765723</v>
+        <v>215308.095074112</v>
       </c>
       <c r="AA46" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C46+$C46*((1+Supuestos!$B$4+$B46/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>380813.02625506</v>
+        <v>388543.837813637</v>
       </c>
       <c r="AB46" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C46+$C46*((1+Supuestos!$B$4+$B46/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>384443.4185586</v>
+        <v>394655.035503071</v>
       </c>
       <c r="AC46" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C46+$C46*((1+Supuestos!$B$4+$B46/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>408487.478388896</v>
+        <v>419733.875543367</v>
       </c>
       <c r="AD46" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C46+$C46*((1+Supuestos!$B$4+$B46/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>544426.425774088</v>
+        <v>556576.883325439</v>
       </c>
       <c r="AE46" s="0" t="n">
         <f aca="false">SUMPRODUCT(X46:AC46,R46:W46)</f>
-        <v>1261960.42650824</v>
+        <v>1174129.00803553</v>
       </c>
       <c r="AF46" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B46/10000)-1</f>
@@ -8229,19 +8229,19 @@
       </c>
       <c r="AG46" s="0" t="n">
         <f aca="false">AD46/(K46-AF46)</f>
-        <v>6885127.36725968</v>
+        <v>7038788.98956721</v>
       </c>
       <c r="AH46" s="0" t="n">
         <f aca="false">AG46*Q46</f>
-        <v>3789798.92255495</v>
+        <v>3874379.29697596</v>
       </c>
       <c r="AI46" s="0" t="n">
         <f aca="false">(AE46+AH46-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1696.42846989187</v>
+        <v>1694.94397489109</v>
       </c>
       <c r="AJ46" s="0" t="n">
         <f aca="false">AI46/AI$5-1</f>
-        <v>-0.0863757491506102</v>
+        <v>-0.0880795863189292</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8335,35 +8335,35 @@
       </c>
       <c r="X47" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C47+$C47*((1+Supuestos!$B$4+$B47/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113590.539233888</v>
+        <v>88642.3986927776</v>
       </c>
       <c r="Y47" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C47+$C47*((1+Supuestos!$B$4+$B47/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200602.23125265</v>
+        <v>150854.718242941</v>
       </c>
       <c r="Z47" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C47+$C47*((1+Supuestos!$B$4+$B47/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>262722.019350684</v>
+        <v>215724.350356521</v>
       </c>
       <c r="AA47" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C47+$C47*((1+Supuestos!$B$4+$B47/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>381917.898950839</v>
+        <v>389671.14031622</v>
       </c>
       <c r="AB47" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C47+$C47*((1+Supuestos!$B$4+$B47/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>385931.344904115</v>
+        <v>396182.484267618</v>
       </c>
       <c r="AC47" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C47+$C47*((1+Supuestos!$B$4+$B47/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>410464.664810135</v>
+        <v>421765.497473449</v>
       </c>
       <c r="AD47" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C47+$C47*((1+Supuestos!$B$4+$B47/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>547590.154242325</v>
+        <v>559811.219586828</v>
       </c>
       <c r="AE47" s="0" t="n">
         <f aca="false">SUMPRODUCT(X47:AC47,R47:W47)</f>
-        <v>1265330.7386496</v>
+        <v>1177452.8939185</v>
       </c>
       <c r="AF47" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B47/10000)-1</f>
@@ -8371,19 +8371,19 @@
       </c>
       <c r="AG47" s="0" t="n">
         <f aca="false">AD47/(K47-AF47)</f>
-        <v>7009835.84295166</v>
+        <v>7166280.69724142</v>
       </c>
       <c r="AH47" s="0" t="n">
         <f aca="false">AG47*Q47</f>
-        <v>3857590.97195222</v>
+        <v>3943684.32292896</v>
       </c>
       <c r="AI47" s="0" t="n">
         <f aca="false">(AE47+AH47-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1728.92269890494</v>
+        <v>1728.10786157418</v>
       </c>
       <c r="AJ47" s="0" t="n">
         <f aca="false">AI47/AI$5-1</f>
-        <v>-0.0688757388844042</v>
+        <v>-0.0702366217659202</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8477,35 +8477,35 @@
       </c>
       <c r="X48" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C48+$C48*((1+Supuestos!$B$4+$B48/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113617.940162002</v>
+        <v>88663.7814946446</v>
       </c>
       <c r="Y48" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C48+$C48*((1+Supuestos!$B$4+$B48/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200795.862749998</v>
+        <v>151000.330905338</v>
       </c>
       <c r="Z48" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C48+$C48*((1+Supuestos!$B$4+$B48/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263229.449496807</v>
+        <v>216141.007623751</v>
       </c>
       <c r="AA48" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C48+$C48*((1+Supuestos!$B$4+$B48/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>383024.906665657</v>
+        <v>390800.62118045</v>
       </c>
       <c r="AB48" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C48+$C48*((1+Supuestos!$B$4+$B48/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>387423.586160762</v>
+        <v>397714.362556311</v>
       </c>
       <c r="AC48" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C48+$C48*((1+Supuestos!$B$4+$B48/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>412449.499910882</v>
+        <v>423804.978664982</v>
       </c>
       <c r="AD48" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C48+$C48*((1+Supuestos!$B$4+$B48/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>550769.18857207</v>
+        <v>563061.203304496</v>
       </c>
       <c r="AE48" s="0" t="n">
         <f aca="false">SUMPRODUCT(X48:AC48,R48:W48)</f>
-        <v>1268715.41099006</v>
+        <v>1180791.20640941</v>
       </c>
       <c r="AF48" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B48/10000)-1</f>
@@ -8513,19 +8513,19 @@
       </c>
       <c r="AG48" s="0" t="n">
         <f aca="false">AD48/(K48-AF48)</f>
-        <v>7138004.88129249</v>
+        <v>7297310.20007485</v>
       </c>
       <c r="AH48" s="0" t="n">
         <f aca="false">AG48*Q48</f>
-        <v>3927293.57796429</v>
+        <v>4014942.54511885</v>
       </c>
       <c r="AI48" s="0" t="n">
         <f aca="false">(AE48+AH48-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1762.29588536728</v>
+        <v>1762.17020617729</v>
       </c>
       <c r="AJ48" s="0" t="n">
         <f aca="false">AI48/AI$5-1</f>
-        <v>-0.0509023595045717</v>
+        <v>-0.0519102653543994</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8619,35 +8619,35 @@
       </c>
       <c r="X49" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C49+$C49*((1+Supuestos!$B$4+$B49/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113645.321279826</v>
+        <v>88685.1488371993</v>
       </c>
       <c r="Y49" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C49+$C49*((1+Supuestos!$B$4+$B49/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200989.494247346</v>
+        <v>151145.943567734</v>
       </c>
       <c r="Z49" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C49+$C49*((1+Supuestos!$B$4+$B49/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263737.369204094</v>
+        <v>216558.066875802</v>
       </c>
       <c r="AA49" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C49+$C49*((1+Supuestos!$B$4+$B49/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384134.051460342</v>
+        <v>391932.282508992</v>
       </c>
       <c r="AB49" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C49+$C49*((1+Supuestos!$B$4+$B49/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>388920.150662504</v>
+        <v>399250.678924483</v>
       </c>
       <c r="AC49" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C49+$C49*((1+Supuestos!$B$4+$B49/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>414442.005861201</v>
+        <v>425852.341898413</v>
       </c>
       <c r="AD49" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C49+$C49*((1+Supuestos!$B$4+$B49/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>553963.587944905</v>
+        <v>566326.894980835</v>
       </c>
       <c r="AE49" s="0" t="n">
         <f aca="false">SUMPRODUCT(X49:AC49,R49:W49)</f>
-        <v>1272114.52217413</v>
+        <v>1184144.0251706</v>
       </c>
       <c r="AF49" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B49/10000)-1</f>
@@ -8655,19 +8655,19 @@
       </c>
       <c r="AG49" s="0" t="n">
         <f aca="false">AD49/(K49-AF49)</f>
-        <v>7269775.16937571</v>
+        <v>7432021.32500229</v>
       </c>
       <c r="AH49" s="0" t="n">
         <f aca="false">AG49*Q49</f>
-        <v>3998984.88188219</v>
+        <v>4088233.84878661</v>
       </c>
       <c r="AI49" s="0" t="n">
         <f aca="false">(AE49+AH49-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1796.58374614444</v>
+        <v>1797.16752235489</v>
       </c>
       <c r="AJ49" s="0" t="n">
         <f aca="false">AI49/AI$5-1</f>
-        <v>-0.0324363754258225</v>
+        <v>-0.0330808718645884</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8761,35 +8761,35 @@
       </c>
       <c r="X50" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C50+$C50*((1+Supuestos!$B$4+$B50/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113672.682620746</v>
+        <v>88706.5007464956</v>
       </c>
       <c r="Y50" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C50+$C50*((1+Supuestos!$B$4+$B50/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201183.125744694</v>
+        <v>151291.556230131</v>
       </c>
       <c r="Z50" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C50+$C50*((1+Supuestos!$B$4+$B50/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>264245.778472545</v>
+        <v>216975.528112675</v>
       </c>
       <c r="AA50" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C50+$C50*((1+Supuestos!$B$4+$B50/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>385245.335395723</v>
+        <v>393066.126404512</v>
       </c>
       <c r="AB50" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C50+$C50*((1+Supuestos!$B$4+$B50/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>390421.046751344</v>
+        <v>400791.441935718</v>
       </c>
       <c r="AC50" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C50+$C50*((1+Supuestos!$B$4+$B50/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>416442.204873957</v>
+        <v>427907.609998168</v>
       </c>
       <c r="AD50" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C50+$C50*((1+Supuestos!$B$4+$B50/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>557173.411713869</v>
+        <v>569608.355293518</v>
       </c>
       <c r="AE50" s="0" t="n">
         <f aca="false">SUMPRODUCT(X50:AC50,R50:W50)</f>
-        <v>1275528.15136042</v>
+        <v>1187511.43038761</v>
       </c>
       <c r="AF50" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B50/10000)-1</f>
@@ -8797,19 +8797,19 @@
       </c>
       <c r="AG50" s="0" t="n">
         <f aca="false">AD50/(K50-AF50)</f>
-        <v>7405295.10355884</v>
+        <v>7570565.78027716</v>
       </c>
       <c r="AH50" s="0" t="n">
         <f aca="false">AG50*Q50</f>
-        <v>4072747.31177359</v>
+        <v>4163642.50162174</v>
       </c>
       <c r="AI50" s="0" t="n">
         <f aca="false">(AE50+AH50-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1831.82395576896</v>
+        <v>1833.13832511842</v>
       </c>
       <c r="AJ50" s="0" t="n">
         <f aca="false">AI50/AI$5-1</f>
-        <v>-0.0134574967466479</v>
+        <v>-0.0137277192987832</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8903,35 +8903,35 @@
       </c>
       <c r="X51" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C51+$C51*((1+Supuestos!$B$4+$B51/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113700.024218062</v>
+        <v>88727.8372485186</v>
       </c>
       <c r="Y51" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C51+$C51*((1+Supuestos!$B$4+$B51/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201376.757242042</v>
+        <v>151437.168892528</v>
       </c>
       <c r="Z51" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C51+$C51*((1+Supuestos!$B$4+$B51/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>264754.67730216</v>
+        <v>217393.391334369</v>
       </c>
       <c r="AA51" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C51+$C51*((1+Supuestos!$B$4+$B51/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>386358.760532631</v>
+        <v>394202.154969675</v>
       </c>
       <c r="AB51" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C51+$C51*((1+Supuestos!$B$4+$B51/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>391926.282777328</v>
+        <v>402336.660161854</v>
       </c>
       <c r="AC51" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C51+$C51*((1+Supuestos!$B$4+$B51/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>418450.119204854</v>
+        <v>429970.80583269</v>
       </c>
       <c r="AD51" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C51+$C51*((1+Supuestos!$B$4+$B51/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>560398.71940379</v>
+        <v>572905.645095844</v>
       </c>
       <c r="AE51" s="0" t="n">
         <f aca="false">SUMPRODUCT(X51:AC51,R51:W51)</f>
-        <v>1278956.37822552</v>
+        <v>1190893.50277313</v>
       </c>
       <c r="AF51" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B51/10000)-1</f>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="AG51" s="0" t="n">
         <f aca="false">AD51/(K51-AF51)</f>
-        <v>7544721.32480075</v>
+        <v>7713103.70275645</v>
       </c>
       <c r="AH51" s="0" t="n">
         <f aca="false">AG51*Q51</f>
-        <v>4148667.88020502</v>
+        <v>4241257.45812901</v>
       </c>
       <c r="AI51" s="0" t="n">
         <f aca="false">(AE51+AH51-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1868.05628238838</v>
+        <v>1870.12326981833</v>
       </c>
       <c r="AJ51" s="0" t="n">
         <f aca="false">AI51/AI$5-1</f>
-        <v>0.00605569396649108</v>
+        <v>0.0061710658943217</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9045,35 +9045,35 @@
       </c>
       <c r="X52" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C52+$C52*((1+Supuestos!$B$4+$B52/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y52" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C52+$C52*((1+Supuestos!$B$4+$B52/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z52" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C52+$C52*((1+Supuestos!$B$4+$B52/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA52" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C52+$C52*((1+Supuestos!$B$4+$B52/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB52" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C52+$C52*((1+Supuestos!$B$4+$B52/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC52" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C52+$C52*((1+Supuestos!$B$4+$B52/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD52" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C52+$C52*((1+Supuestos!$B$4+$B52/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE52" s="0" t="n">
         <f aca="false">SUMPRODUCT(X52:AC52,R52:W52)</f>
-        <v>1245321.55173293</v>
+        <v>1157723.22568801</v>
       </c>
       <c r="AF52" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B52/10000)-1</f>
@@ -9081,19 +9081,19 @@
       </c>
       <c r="AG52" s="0" t="n">
         <f aca="false">AD52/(K52-AF52)</f>
-        <v>6309049.80175791</v>
+        <v>6449854.57936698</v>
       </c>
       <c r="AH52" s="0" t="n">
         <f aca="false">AG52*Q52</f>
-        <v>3477029.21557944</v>
+        <v>3554629.22522011</v>
       </c>
       <c r="AI52" s="0" t="n">
         <f aca="false">(AE52+AH52-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1546.01359238008</v>
+        <v>1541.4481510996</v>
       </c>
       <c r="AJ52" s="0" t="n">
         <f aca="false">AI52/AI$5-1</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9187,35 +9187,35 @@
       </c>
       <c r="X53" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C53+$C53*((1+Supuestos!$B$4+$B53/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113449.108189814</v>
+        <v>88532.0304606966</v>
       </c>
       <c r="Y53" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C53+$C53*((1+Supuestos!$B$4+$B53/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199605.029041307</v>
+        <v>150104.813031598</v>
       </c>
       <c r="Z53" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C53+$C53*((1+Supuestos!$B$4+$B53/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260116.538120648</v>
+        <v>213584.956988943</v>
       </c>
       <c r="AA53" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C53+$C53*((1+Supuestos!$B$4+$B53/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>376250.710168789</v>
+        <v>383888.903031308</v>
       </c>
       <c r="AB53" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C53+$C53*((1+Supuestos!$B$4+$B53/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>378314.724412326</v>
+        <v>388363.55049091</v>
       </c>
       <c r="AC53" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C53+$C53*((1+Supuestos!$B$4+$B53/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>400363.886481441</v>
+        <v>411386.626496476</v>
       </c>
       <c r="AD53" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C53+$C53*((1+Supuestos!$B$4+$B53/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>531460.180731133</v>
+        <v>543321.25885023</v>
       </c>
       <c r="AE53" s="0" t="n">
         <f aca="false">SUMPRODUCT(X53:AC53,R53:W53)</f>
-        <v>1248100.16884546</v>
+        <v>1160462.48392193</v>
       </c>
       <c r="AF53" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B53/10000)-1</f>
@@ -9223,19 +9223,19 @@
       </c>
       <c r="AG53" s="0" t="n">
         <f aca="false">AD53/(K53-AF53)</f>
-        <v>6412739.28498274</v>
+        <v>6555858.19468533</v>
       </c>
       <c r="AH53" s="0" t="n">
         <f aca="false">AG53*Q53</f>
-        <v>3533229.1768059</v>
+        <v>3612083.45187335</v>
       </c>
       <c r="AI53" s="0" t="n">
         <f aca="false">(AE53+AH53-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1572.94445006912</v>
+        <v>1568.93376063711</v>
       </c>
       <c r="AJ53" s="0" t="n">
         <f aca="false">AI53/AI$5-1</f>
-        <v>-0.15287899234932</v>
+        <v>-0.155876096653678</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9329,35 +9329,35 @@
       </c>
       <c r="X54" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C54+$C54*((1+Supuestos!$B$4+$B54/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113472.483600772</v>
+        <v>88550.2718786149</v>
       </c>
       <c r="Y54" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C54+$C54*((1+Supuestos!$B$4+$B54/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199769.615814053</v>
+        <v>150228.583794635</v>
       </c>
       <c r="Z54" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C54+$C54*((1+Supuestos!$B$4+$B54/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260545.773109908</v>
+        <v>213937.407230599</v>
       </c>
       <c r="AA54" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C54+$C54*((1+Supuestos!$B$4+$B54/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>377182.610412519</v>
+        <v>384839.721601563</v>
       </c>
       <c r="AB54" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C54+$C54*((1+Supuestos!$B$4+$B54/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>379564.861810165</v>
+        <v>389646.894138664</v>
       </c>
       <c r="AC54" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C54+$C54*((1+Supuestos!$B$4+$B54/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>402018.67714836</v>
+        <v>413086.976535548</v>
       </c>
       <c r="AD54" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C54+$C54*((1+Supuestos!$B$4+$B54/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>534097.810138496</v>
+        <v>546017.754621592</v>
       </c>
       <c r="AE54" s="0" t="n">
         <f aca="false">SUMPRODUCT(X54:AC54,R54:W54)</f>
-        <v>1250891.58220021</v>
+        <v>1163214.57758854</v>
       </c>
       <c r="AF54" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B54/10000)-1</f>
@@ -9365,19 +9365,19 @@
       </c>
       <c r="AG54" s="0" t="n">
         <f aca="false">AD54/(K54-AF54)</f>
-        <v>6519128.6654278</v>
+        <v>6664621.96327508</v>
       </c>
       <c r="AH54" s="0" t="n">
         <f aca="false">AG54*Q54</f>
-        <v>3590919.57309845</v>
+        <v>3671061.3769817</v>
       </c>
       <c r="AI54" s="0" t="n">
         <f aca="false">(AE54+AH54-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1600.56171474824</v>
+        <v>1597.12098382203</v>
       </c>
       <c r="AJ54" s="0" t="n">
         <f aca="false">AI54/AI$5-1</f>
-        <v>-0.138005507731023</v>
+        <v>-0.140710696140094</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9471,35 +9471,35 @@
       </c>
       <c r="X55" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C55+$C55*((1+Supuestos!$B$4+$B55/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113495.842029953</v>
+        <v>88568.5000445019</v>
       </c>
       <c r="Y55" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C55+$C55*((1+Supuestos!$B$4+$B55/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199934.202586799</v>
+        <v>150352.354557672</v>
       </c>
       <c r="Z55" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C55+$C55*((1+Supuestos!$B$4+$B55/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260975.424226157</v>
+        <v>214290.199159352</v>
       </c>
       <c r="AA55" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C55+$C55*((1+Supuestos!$B$4+$B55/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>378116.318415612</v>
+        <v>385792.384630154</v>
       </c>
       <c r="AB55" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C55+$C55*((1+Supuestos!$B$4+$B55/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>380818.638615335</v>
+        <v>390933.973863979</v>
       </c>
       <c r="AC55" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C55+$C55*((1+Supuestos!$B$4+$B55/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>403679.894177732</v>
+        <v>414793.929866424</v>
       </c>
       <c r="AD55" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C55+$C55*((1+Supuestos!$B$4+$B55/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>536748.249762539</v>
+        <v>548727.34650684</v>
       </c>
       <c r="AE55" s="0" t="n">
         <f aca="false">SUMPRODUCT(X55:AC55,R55:W55)</f>
-        <v>1253695.85590534</v>
+        <v>1165979.57162112</v>
       </c>
       <c r="AF55" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B55/10000)-1</f>
@@ -9507,19 +9507,19 @@
       </c>
       <c r="AG55" s="0" t="n">
         <f aca="false">AD55/(K55-AF55)</f>
-        <v>6628320.77770739</v>
+        <v>6776251.01480372</v>
       </c>
       <c r="AH55" s="0" t="n">
         <f aca="false">AG55*Q55</f>
-        <v>3650157.5080111</v>
+        <v>3731621.37853093</v>
       </c>
       <c r="AI55" s="0" t="n">
         <f aca="false">(AE55+AH55-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1628.8914903728</v>
+        <v>1626.03650691875</v>
       </c>
       <c r="AJ55" s="0" t="n">
         <f aca="false">AI55/AI$5-1</f>
-        <v>-0.122748295009658</v>
+        <v>-0.125153452847816</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9613,35 +9613,35 @@
       </c>
       <c r="X56" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C56+$C56*((1+Supuestos!$B$4+$B56/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113519.183506117</v>
+        <v>88586.7149807997</v>
       </c>
       <c r="Y56" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C56+$C56*((1+Supuestos!$B$4+$B56/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200098.789359545</v>
+        <v>150476.12532071</v>
       </c>
       <c r="Z56" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C56+$C56*((1+Supuestos!$B$4+$B56/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261405.491469395</v>
+        <v>214643.332775203</v>
       </c>
       <c r="AA56" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C56+$C56*((1+Supuestos!$B$4+$B56/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379051.835929774</v>
+        <v>386746.893904348</v>
       </c>
       <c r="AB56" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C56+$C56*((1+Supuestos!$B$4+$B56/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>382076.061884368</v>
+        <v>392224.796910822</v>
       </c>
       <c r="AC56" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C56+$C56*((1+Supuestos!$B$4+$B56/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>405347.556268947</v>
+        <v>416507.505703321</v>
       </c>
       <c r="AD56" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C56+$C56*((1+Supuestos!$B$4+$B56/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>539411.549327458</v>
+        <v>551450.08533991</v>
       </c>
       <c r="AE56" s="0" t="n">
         <f aca="false">SUMPRODUCT(X56:AC56,R56:W56)</f>
-        <v>1256513.05451198</v>
+        <v>1168757.5314034</v>
       </c>
       <c r="AF56" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B56/10000)-1</f>
@@ -9649,19 +9649,19 @@
       </c>
       <c r="AG56" s="0" t="n">
         <f aca="false">AD56/(K56-AF56)</f>
-        <v>6740423.73038764</v>
+        <v>6890855.87059419</v>
       </c>
       <c r="AH56" s="0" t="n">
         <f aca="false">AG56*Q56</f>
-        <v>3711003.01762709</v>
+        <v>3793824.8324839</v>
       </c>
       <c r="AI56" s="0" t="n">
         <f aca="false">(AE56+AH56-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1657.96122015483</v>
+        <v>1655.70838533666</v>
       </c>
       <c r="AJ56" s="0" t="n">
         <f aca="false">AI56/AI$5-1</f>
-        <v>-0.107092574437963</v>
+        <v>-0.109189272295299</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9755,35 +9755,35 @@
       </c>
       <c r="X57" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C57+$C57*((1+Supuestos!$B$4+$B57/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113542.508057945</v>
+        <v>88604.9167098906</v>
       </c>
       <c r="Y57" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C57+$C57*((1+Supuestos!$B$4+$B57/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200263.376132291</v>
+        <v>150599.896083747</v>
       </c>
       <c r="Z57" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C57+$C57*((1+Supuestos!$B$4+$B57/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261835.974839622</v>
+        <v>214996.808078153</v>
       </c>
       <c r="AA57" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C57+$C57*((1+Supuestos!$B$4+$B57/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379989.164706709</v>
+        <v>387703.25121141</v>
       </c>
       <c r="AB57" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C57+$C57*((1+Supuestos!$B$4+$B57/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383337.138680628</v>
+        <v>393519.370530176</v>
       </c>
       <c r="AC57" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C57+$C57*((1+Supuestos!$B$4+$B57/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>407021.68215763</v>
+        <v>418227.723297691</v>
       </c>
       <c r="AD57" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C57+$C57*((1+Supuestos!$B$4+$B57/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>542087.758702064</v>
+        <v>554186.02210258</v>
       </c>
       <c r="AE57" s="0" t="n">
         <f aca="false">SUMPRODUCT(X57:AC57,R57:W57)</f>
-        <v>1259343.24301737</v>
+        <v>1171548.52277278</v>
       </c>
       <c r="AF57" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B57/10000)-1</f>
@@ -9791,19 +9791,19 @@
       </c>
       <c r="AG57" s="0" t="n">
         <f aca="false">AD57/(K57-AF57)</f>
-        <v>6855551.24843406</v>
+        <v>7008552.793715</v>
       </c>
       <c r="AH57" s="0" t="n">
         <f aca="false">AG57*Q57</f>
-        <v>3773519.26100625</v>
+        <v>3857736.30747837</v>
       </c>
       <c r="AI57" s="0" t="n">
         <f aca="false">(AE57+AH57-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1687.79977352677</v>
+        <v>1686.16613253477</v>
       </c>
       <c r="AJ57" s="0" t="n">
         <f aca="false">AI57/AI$5-1</f>
-        <v>-0.0910227981669906</v>
+        <v>-0.0928022755354365</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9897,35 +9897,35 @@
       </c>
       <c r="X58" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C58+$C58*((1+Supuestos!$B$4+$B58/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113565.815714042</v>
+        <v>88623.1052540977</v>
       </c>
       <c r="Y58" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C58+$C58*((1+Supuestos!$B$4+$B58/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200427.962905036</v>
+        <v>150723.666846784</v>
       </c>
       <c r="Z58" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C58+$C58*((1+Supuestos!$B$4+$B58/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>262266.874336838</v>
+        <v>215350.625068201</v>
       </c>
       <c r="AA58" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C58+$C58*((1+Supuestos!$B$4+$B58/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>380928.306498121</v>
+        <v>388661.458338606</v>
       </c>
       <c r="AB58" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C58+$C58*((1+Supuestos!$B$4+$B58/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>384601.876074316</v>
+        <v>394817.70198004</v>
       </c>
       <c r="AC58" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C58+$C58*((1+Supuestos!$B$4+$B58/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>408702.290615684</v>
+        <v>419954.60193826</v>
       </c>
       <c r="AD58" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C58+$C58*((1+Supuestos!$B$4+$B58/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>544776.927900066</v>
+        <v>556935.207924761</v>
       </c>
       <c r="AE58" s="0" t="n">
         <f aca="false">SUMPRODUCT(X58:AC58,R58:W58)</f>
-        <v>1262186.48686802</v>
+        <v>1174352.61202356</v>
       </c>
       <c r="AF58" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B58/10000)-1</f>
@@ -9933,19 +9933,19 @@
       </c>
       <c r="AG58" s="0" t="n">
         <f aca="false">AD58/(K58-AF58)</f>
-        <v>6973823.04269305</v>
+        <v>7129464.16670792</v>
       </c>
       <c r="AH58" s="0" t="n">
         <f aca="false">AG58*Q58</f>
-        <v>3837772.72566732</v>
+        <v>3923423.77489524</v>
       </c>
       <c r="AI58" s="0" t="n">
         <f aca="false">(AE58+AH58-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1718.43753997048</v>
+        <v>1717.44081594465</v>
       </c>
       <c r="AJ58" s="0" t="n">
         <f aca="false">AI58/AI$5-1</f>
-        <v>-0.0745225997138173</v>
+        <v>-0.0759757475466749</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10039,35 +10039,35 @@
       </c>
       <c r="X59" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C59+$C59*((1+Supuestos!$B$4+$B59/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113589.106502938</v>
+        <v>88641.2806356846</v>
       </c>
       <c r="Y59" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C59+$C59*((1+Supuestos!$B$4+$B59/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200592.549677782</v>
+        <v>150847.437609821</v>
       </c>
       <c r="Z59" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C59+$C59*((1+Supuestos!$B$4+$B59/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>262698.189961043</v>
+        <v>215704.783745346</v>
       </c>
       <c r="AA59" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C59+$C59*((1+Supuestos!$B$4+$B59/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>381869.263055716</v>
+        <v>389621.517073201</v>
       </c>
       <c r="AB59" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C59+$C59*((1+Supuestos!$B$4+$B59/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>385870.281142466</v>
+        <v>396119.798525429</v>
       </c>
       <c r="AC59" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C59+$C59*((1+Supuestos!$B$4+$B59/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>410389.400451318</v>
+        <v>421688.160951063</v>
       </c>
       <c r="AD59" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C59+$C59*((1+Supuestos!$B$4+$B59/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>547479.107080349</v>
+        <v>559697.694084779</v>
       </c>
       <c r="AE59" s="0" t="n">
         <f aca="false">SUMPRODUCT(X59:AC59,R59:W59)</f>
-        <v>1265042.85196291</v>
+        <v>1177169.86591021</v>
       </c>
       <c r="AF59" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B59/10000)-1</f>
@@ -10075,19 +10075,19 @@
       </c>
       <c r="AG59" s="0" t="n">
         <f aca="false">AD59/(K59-AF59)</f>
-        <v>7095365.20893056</v>
+        <v>7253718.89953231</v>
       </c>
       <c r="AH59" s="0" t="n">
         <f aca="false">AG59*Q59</f>
-        <v>3903833.44950846</v>
+        <v>3990958.83573186</v>
       </c>
       <c r="AI59" s="0" t="n">
         <f aca="false">(AE59+AH59-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1749.90653035222</v>
+        <v>1749.56516056716</v>
       </c>
       <c r="AJ59" s="0" t="n">
         <f aca="false">AI59/AI$5-1</f>
-        <v>-0.0575747393867963</v>
+        <v>-0.0586920814955493</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10181,35 +10181,35 @@
       </c>
       <c r="X60" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C60+$C60*((1+Supuestos!$B$4+$B60/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113612.380453089</v>
+        <v>88659.4428768561</v>
       </c>
       <c r="Y60" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C60+$C60*((1+Supuestos!$B$4+$B60/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200757.136450528</v>
+        <v>150971.208372858</v>
       </c>
       <c r="Z60" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C60+$C60*((1+Supuestos!$B$4+$B60/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263129.921712237</v>
+        <v>216059.28410959</v>
       </c>
       <c r="AA60" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C60+$C60*((1+Supuestos!$B$4+$B60/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>382812.036131198</v>
+        <v>390583.429202461</v>
       </c>
       <c r="AB60" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C60+$C60*((1+Supuestos!$B$4+$B60/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>387142.360968947</v>
+        <v>397425.667438376</v>
       </c>
       <c r="AC60" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C60+$C60*((1+Supuestos!$B$4+$B60/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>412083.03050909</v>
+        <v>423428.41969948</v>
       </c>
       <c r="AD60" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C60+$C60*((1+Supuestos!$B$4+$B60/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>550194.346547259</v>
+        <v>562473.532009666</v>
       </c>
       <c r="AE60" s="0" t="n">
         <f aca="false">SUMPRODUCT(X60:AC60,R60:W60)</f>
-        <v>1267912.40465672</v>
+        <v>1180000.35165065</v>
       </c>
       <c r="AF60" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B60/10000)-1</f>
@@ -10217,19 +10217,19 @@
       </c>
       <c r="AG60" s="0" t="n">
         <f aca="false">AD60/(K60-AF60)</f>
-        <v>7220310.65922325</v>
+        <v>7381452.87058399</v>
       </c>
       <c r="AH60" s="0" t="n">
         <f aca="false">AG60*Q60</f>
-        <v>3971775.2607205</v>
+        <v>4060416.96586968</v>
       </c>
       <c r="AI60" s="0" t="n">
         <f aca="false">(AE60+AH60-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1782.24048647362</v>
+        <v>1782.57366096819</v>
       </c>
       <c r="AJ60" s="0" t="n">
         <f aca="false">AI60/AI$5-1</f>
-        <v>-0.0401610452861012</v>
+        <v>-0.0409327184802405</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10323,35 +10323,35 @@
       </c>
       <c r="X61" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C61+$C61*((1+Supuestos!$B$4+$B61/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113635.637592871</v>
+        <v>88677.591999758</v>
       </c>
       <c r="Y61" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C61+$C61*((1+Supuestos!$B$4+$B61/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200921.723223274</v>
+        <v>151094.979135895</v>
       </c>
       <c r="Z61" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C61+$C61*((1+Supuestos!$B$4+$B61/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263562.06959042</v>
+        <v>216414.126160932</v>
       </c>
       <c r="AA61" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C61+$C61*((1+Supuestos!$B$4+$B61/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>383756.627476272</v>
+        <v>391547.196513653</v>
       </c>
       <c r="AB61" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C61+$C61*((1+Supuestos!$B$4+$B61/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>388418.122644461</v>
+        <v>398735.315997925</v>
       </c>
       <c r="AC61" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C61+$C61*((1+Supuestos!$B$4+$B61/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>413783.199669932</v>
+        <v>425175.397584272</v>
       </c>
       <c r="AD61" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C61+$C61*((1+Supuestos!$B$4+$B61/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>552922.696750878</v>
+        <v>565262.773275448</v>
       </c>
       <c r="AE61" s="0" t="n">
         <f aca="false">SUMPRODUCT(X61:AC61,R61:W61)</f>
-        <v>1270795.2117631</v>
+        <v>1182844.13692958</v>
       </c>
       <c r="AF61" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B61/10000)-1</f>
@@ -10359,19 +10359,19 @@
       </c>
       <c r="AG61" s="0" t="n">
         <f aca="false">AD61/(K61-AF61)</f>
-        <v>7348799.58880476</v>
+        <v>7512809.40396059</v>
       </c>
       <c r="AH61" s="0" t="n">
         <f aca="false">AG61*Q61</f>
-        <v>4041676.03741865</v>
+        <v>4131877.78150032</v>
       </c>
       <c r="AI61" s="0" t="n">
         <f aca="false">(AE61+AH61-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1815.47499962637</v>
+        <v>1816.50270247941</v>
       </c>
       <c r="AJ61" s="0" t="n">
         <f aca="false">AI61/AI$5-1</f>
-        <v>-0.0222623494551681</v>
+        <v>-0.022678082321721</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10465,35 +10465,35 @@
       </c>
       <c r="X62" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C62+$C62*((1+Supuestos!$B$4+$B62/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113658.877950589</v>
+        <v>88695.7280264776</v>
       </c>
       <c r="Y62" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C62+$C62*((1+Supuestos!$B$4+$B62/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>201086.30999602</v>
+        <v>151218.749898933</v>
       </c>
       <c r="Z62" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C62+$C62*((1+Supuestos!$B$4+$B62/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263994.633595593</v>
+        <v>216769.309899371</v>
       </c>
       <c r="AA62" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C62+$C62*((1+Supuestos!$B$4+$B62/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>384703.038842644</v>
+        <v>392512.820794042</v>
       </c>
       <c r="AB62" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C62+$C62*((1+Supuestos!$B$4+$B62/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>389697.573266547</v>
+        <v>400048.751490141</v>
       </c>
       <c r="AC62" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C62+$C62*((1+Supuestos!$B$4+$B62/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>415489.926851194</v>
+        <v>426929.114043616</v>
       </c>
       <c r="AD62" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C62+$C62*((1+Supuestos!$B$4+$B62/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>555664.208287311</v>
+        <v>568065.469607425</v>
       </c>
       <c r="AE62" s="0" t="n">
         <f aca="false">SUMPRODUCT(X62:AC62,R62:W62)</f>
-        <v>1273691.34055792</v>
+        <v>1185701.28990184</v>
       </c>
       <c r="AF62" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B62/10000)-1</f>
@@ -10501,19 +10501,19 @@
       </c>
       <c r="AG62" s="0" t="n">
         <f aca="false">AD62/(K62-AF62)</f>
-        <v>7480979.98181372</v>
+        <v>7647939.78649677</v>
       </c>
       <c r="AH62" s="0" t="n">
         <f aca="false">AG62*Q62</f>
-        <v>4113617.98890922</v>
+        <v>4205425.3266696</v>
       </c>
       <c r="AI62" s="0" t="n">
         <f aca="false">(AE62+AH62-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1849.64763902609</v>
+        <v>1851.39069249837</v>
       </c>
       <c r="AJ62" s="0" t="n">
         <f aca="false">AI62/AI$5-1</f>
-        <v>-0.00385841871171311</v>
+        <v>-0.00390750892112202</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10607,35 +10607,35 @@
       </c>
       <c r="X63" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C63+$C63*((1+Supuestos!$B$4+$B63/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y63" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C63+$C63*((1+Supuestos!$B$4+$B63/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z63" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C63+$C63*((1+Supuestos!$B$4+$B63/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA63" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C63+$C63*((1+Supuestos!$B$4+$B63/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB63" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C63+$C63*((1+Supuestos!$B$4+$B63/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC63" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C63+$C63*((1+Supuestos!$B$4+$B63/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD63" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C63+$C63*((1+Supuestos!$B$4+$B63/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE63" s="0" t="n">
         <f aca="false">SUMPRODUCT(X63:AC63,R63:W63)</f>
-        <v>1245321.55173293</v>
+        <v>1157723.22568801</v>
       </c>
       <c r="AF63" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B63/10000)-1</f>
@@ -10643,19 +10643,19 @@
       </c>
       <c r="AG63" s="0" t="n">
         <f aca="false">AD63/(K63-AF63)</f>
-        <v>6309049.80175791</v>
+        <v>6449854.57936698</v>
       </c>
       <c r="AH63" s="0" t="n">
         <f aca="false">AG63*Q63</f>
-        <v>3477029.21557944</v>
+        <v>3554629.22522011</v>
       </c>
       <c r="AI63" s="0" t="n">
         <f aca="false">(AE63+AH63-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1546.01359238008</v>
+        <v>1541.4481510996</v>
       </c>
       <c r="AJ63" s="0" t="n">
         <f aca="false">AI63/AI$5-1</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10749,35 +10749,35 @@
       </c>
       <c r="X64" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C64+$C64*((1+Supuestos!$B$4+$B64/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113444.98011542</v>
+        <v>88528.8090443816</v>
       </c>
       <c r="Y64" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C64+$C64*((1+Supuestos!$B$4+$B64/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199575.984316705</v>
+        <v>150082.971132239</v>
       </c>
       <c r="Z64" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C64+$C64*((1+Supuestos!$B$4+$B64/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260040.864203777</v>
+        <v>213522.820185198</v>
       </c>
       <c r="AA64" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C64+$C64*((1+Supuestos!$B$4+$B64/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>376086.575891835</v>
+        <v>383721.436696157</v>
       </c>
       <c r="AB64" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C64+$C64*((1+Supuestos!$B$4+$B64/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>378094.752934642</v>
+        <v>388137.736113179</v>
       </c>
       <c r="AC64" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C64+$C64*((1+Supuestos!$B$4+$B64/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>400072.995369502</v>
+        <v>411087.726627485</v>
       </c>
       <c r="AD64" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C64+$C64*((1+Supuestos!$B$4+$B64/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>530996.968595156</v>
+        <v>542847.70878955</v>
       </c>
       <c r="AE64" s="0" t="n">
         <f aca="false">SUMPRODUCT(X64:AC64,R64:W64)</f>
-        <v>1247579.11286932</v>
+        <v>1159948.81241545</v>
       </c>
       <c r="AF64" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B64/10000)-1</f>
@@ -10785,19 +10785,19 @@
       </c>
       <c r="AG64" s="0" t="n">
         <f aca="false">AD64/(K64-AF64)</f>
-        <v>6407150.04467959</v>
+        <v>6550144.21424498</v>
       </c>
       <c r="AH64" s="0" t="n">
         <f aca="false">AG64*Q64</f>
-        <v>3530149.6711473</v>
+        <v>3608935.2180983</v>
       </c>
       <c r="AI64" s="0" t="n">
         <f aca="false">(AE64+AH64-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1571.30035799846</v>
+        <v>1567.26165776884</v>
       </c>
       <c r="AJ64" s="0" t="n">
         <f aca="false">AI64/AI$5-1</f>
-        <v>-0.153764430440606</v>
+        <v>-0.156775728005479</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10891,35 +10891,35 @@
       </c>
       <c r="X65" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C65+$C65*((1+Supuestos!$B$4+$B65/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113464.230453855</v>
+        <v>88543.8313885496</v>
       </c>
       <c r="Y65" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C65+$C65*((1+Supuestos!$B$4+$B65/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199711.526364848</v>
+        <v>150184.899995916</v>
       </c>
       <c r="Z65" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C65+$C65*((1+Supuestos!$B$4+$B65/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260394.351841991</v>
+        <v>213813.073325385</v>
       </c>
       <c r="AA65" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C65+$C65*((1+Supuestos!$B$4+$B65/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>376854.023151378</v>
+        <v>384504.463754015</v>
       </c>
       <c r="AB65" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C65+$C65*((1+Supuestos!$B$4+$B65/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>379124.27785051</v>
+        <v>389194.607352506</v>
       </c>
       <c r="AC65" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C65+$C65*((1+Supuestos!$B$4+$B65/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>401435.764154024</v>
+        <v>412488.014894956</v>
       </c>
       <c r="AD65" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C65+$C65*((1+Supuestos!$B$4+$B65/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>533169.133989455</v>
+        <v>545068.352365966</v>
       </c>
       <c r="AE65" s="0" t="n">
         <f aca="false">SUMPRODUCT(X65:AC65,R65:W65)</f>
-        <v>1249848.29193619</v>
+        <v>1162186.0340008</v>
       </c>
       <c r="AF65" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B65/10000)-1</f>
@@ -10927,19 +10927,19 @@
       </c>
       <c r="AG65" s="0" t="n">
         <f aca="false">AD65/(K65-AF65)</f>
-        <v>6507793.36468477</v>
+        <v>6653033.68236064</v>
       </c>
       <c r="AH65" s="0" t="n">
         <f aca="false">AG65*Q65</f>
-        <v>3584675.77037663</v>
+        <v>3664678.22566044</v>
       </c>
       <c r="AI65" s="0" t="n">
         <f aca="false">(AE65+AH65-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1597.23427502868</v>
+        <v>1593.73664824714</v>
       </c>
       <c r="AJ65" s="0" t="n">
         <f aca="false">AI65/AI$5-1</f>
-        <v>-0.1397975252991</v>
+        <v>-0.142531549656912</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11033,35 +11033,35 @@
       </c>
       <c r="X66" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C66+$C66*((1+Supuestos!$B$4+$B66/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113483.466807299</v>
+        <v>88558.8428192801</v>
       </c>
       <c r="Y66" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C66+$C66*((1+Supuestos!$B$4+$B66/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199847.068412992</v>
+        <v>150286.828859594</v>
       </c>
       <c r="Z66" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C66+$C66*((1+Supuestos!$B$4+$B66/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>260748.182173019</v>
+        <v>214103.607854946</v>
       </c>
       <c r="AA66" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C66+$C66*((1+Supuestos!$B$4+$B66/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>377622.959153925</v>
+        <v>385289.009777561</v>
       </c>
       <c r="AB66" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C66+$C66*((1+Supuestos!$B$4+$B66/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>380156.799925356</v>
+        <v>390254.555361588</v>
       </c>
       <c r="AC66" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C66+$C66*((1+Supuestos!$B$4+$B66/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>402803.825237037</v>
+        <v>413893.741167442</v>
       </c>
       <c r="AD66" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C66+$C66*((1+Supuestos!$B$4+$B66/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>535351.848973961</v>
+        <v>547299.780977347</v>
       </c>
       <c r="AE66" s="0" t="n">
         <f aca="false">SUMPRODUCT(X66:AC66,R66:W66)</f>
-        <v>1252129.14101855</v>
+        <v>1164434.94320583</v>
       </c>
       <c r="AF66" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B66/10000)-1</f>
@@ -11069,19 +11069,19 @@
       </c>
       <c r="AG66" s="0" t="n">
         <f aca="false">AD66/(K66-AF66)</f>
-        <v>6611076.5810751</v>
+        <v>6758621.96381965</v>
       </c>
       <c r="AH66" s="0" t="n">
         <f aca="false">AG66*Q66</f>
-        <v>3640661.28175442</v>
+        <v>3721913.21639354</v>
       </c>
       <c r="AI66" s="0" t="n">
         <f aca="false">(AE66+AH66-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1623.83991907442</v>
+        <v>1620.89824639241</v>
       </c>
       <c r="AJ66" s="0" t="n">
         <f aca="false">AI66/AI$5-1</f>
-        <v>-0.125468856545268</v>
+        <v>-0.127917959954951</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11175,35 +11175,35 @@
       </c>
       <c r="X67" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C67+$C67*((1+Supuestos!$B$4+$B67/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113502.689199434</v>
+        <v>88573.8433550547</v>
       </c>
       <c r="Y67" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C67+$C67*((1+Supuestos!$B$4+$B67/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199982.610461136</v>
+        <v>150388.757723272</v>
       </c>
       <c r="Z67" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C67+$C67*((1+Supuestos!$B$4+$B67/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261102.355196862</v>
+        <v>214394.423773883</v>
       </c>
       <c r="AA67" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C67+$C67*((1+Supuestos!$B$4+$B67/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>378393.385342058</v>
+        <v>386075.076238661</v>
       </c>
       <c r="AB67" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C67+$C67*((1+Supuestos!$B$4+$B67/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>381192.324970442</v>
+        <v>391317.586106047</v>
       </c>
       <c r="AC67" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C67+$C67*((1+Supuestos!$B$4+$B67/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>404177.194018037</v>
+        <v>415304.921268416</v>
       </c>
       <c r="AD67" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C67+$C67*((1+Supuestos!$B$4+$B67/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>537545.154498012</v>
+        <v>549542.036486934</v>
       </c>
       <c r="AE67" s="0" t="n">
         <f aca="false">SUMPRODUCT(X67:AC67,R67:W67)</f>
-        <v>1254421.71259226</v>
+        <v>1166695.59318939</v>
       </c>
       <c r="AF67" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B67/10000)-1</f>
@@ -11211,19 +11211,19 @@
       </c>
       <c r="AG67" s="0" t="n">
         <f aca="false">AD67/(K67-AF67)</f>
-        <v>6717101.47854792</v>
+        <v>6867013.1149406</v>
       </c>
       <c r="AH67" s="0" t="n">
         <f aca="false">AG67*Q67</f>
-        <v>3698162.73481744</v>
+        <v>3780697.98145522</v>
       </c>
       <c r="AI67" s="0" t="n">
         <f aca="false">(AE67+AH67-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1651.14312667109</v>
+        <v>1648.77286513452</v>
       </c>
       <c r="AJ67" s="0" t="n">
         <f aca="false">AI67/AI$5-1</f>
-        <v>-0.110764509719558</v>
+        <v>-0.112920748111328</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11317,35 +11317,35 @@
       </c>
       <c r="X68" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C68+$C68*((1+Supuestos!$B$4+$B68/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113521.89765388</v>
+        <v>88588.8330143061</v>
       </c>
       <c r="Y68" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C68+$C68*((1+Supuestos!$B$4+$B68/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200118.152509279</v>
+        <v>150490.686586949</v>
       </c>
       <c r="Z68" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C68+$C68*((1+Supuestos!$B$4+$B68/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261456.87091352</v>
+        <v>214685.521082194</v>
       </c>
       <c r="AA68" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C68+$C68*((1+Supuestos!$B$4+$B68/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379165.303158357</v>
+        <v>386862.664609183</v>
       </c>
       <c r="AB68" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C68+$C68*((1+Supuestos!$B$4+$B68/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>382230.858802656</v>
+        <v>392383.70555728</v>
       </c>
       <c r="AC68" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C68+$C68*((1+Supuestos!$B$4+$B68/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>405555.885926364</v>
+        <v>416721.571052015</v>
       </c>
       <c r="AD68" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C68+$C68*((1+Supuestos!$B$4+$B68/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>539749.09163004</v>
+        <v>551795.160879721</v>
       </c>
       <c r="AE68" s="0" t="n">
         <f aca="false">SUMPRODUCT(X68:AC68,R68:W68)</f>
-        <v>1256726.05952651</v>
+        <v>1168968.03751003</v>
       </c>
       <c r="AF68" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B68/10000)-1</f>
@@ -11353,19 +11353,19 @@
       </c>
       <c r="AG68" s="0" t="n">
         <f aca="false">AD68/(K68-AF68)</f>
-        <v>6825975.12960845</v>
+        <v>6978316.59786278</v>
       </c>
       <c r="AH68" s="0" t="n">
         <f aca="false">AG68*Q68</f>
-        <v>3757239.59945755</v>
+        <v>3841093.31798078</v>
       </c>
       <c r="AI68" s="0" t="n">
         <f aca="false">(AE68+AH68-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1679.17107716167</v>
+        <v>1677.38829017845</v>
       </c>
       <c r="AJ68" s="0" t="n">
         <f aca="false">AI68/AI$5-1</f>
-        <v>-0.0956698471833708</v>
+        <v>-0.0975249647519435</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11459,35 +11459,35 @@
       </c>
       <c r="X69" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C69+$C69*((1+Supuestos!$B$4+$B69/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113541.092194195</v>
+        <v>88603.8118154178</v>
       </c>
       <c r="Y69" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C69+$C69*((1+Supuestos!$B$4+$B69/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200253.694557423</v>
+        <v>150592.615450627</v>
       </c>
       <c r="Z69" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C69+$C69*((1+Supuestos!$B$4+$B69/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>261811.729322992</v>
+        <v>214976.89977988</v>
       </c>
       <c r="AA69" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C69+$C69*((1+Supuestos!$B$4+$B69/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>379938.714045403</v>
+        <v>387651.776360991</v>
       </c>
       <c r="AB69" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C69+$C69*((1+Supuestos!$B$4+$B69/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>383272.407244517</v>
+        <v>393452.919692462</v>
       </c>
       <c r="AC69" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C69+$C69*((1+Supuestos!$B$4+$B69/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>406939.916421232</v>
+        <v>418143.706403072</v>
       </c>
       <c r="AD69" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C69+$C69*((1+Supuestos!$B$4+$B69/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>541963.701557806</v>
+        <v>554059.196262694</v>
       </c>
       <c r="AE69" s="0" t="n">
         <f aca="false">SUMPRODUCT(X69:AC69,R69:W69)</f>
-        <v>1259042.23508645</v>
+        <v>1171252.33012862</v>
       </c>
       <c r="AF69" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B69/10000)-1</f>
@@ -11495,19 +11495,19 @@
       </c>
       <c r="AG69" s="0" t="n">
         <f aca="false">AD69/(K69-AF69)</f>
-        <v>6937810.24243445</v>
+        <v>7092647.63617442</v>
       </c>
       <c r="AH69" s="0" t="n">
         <f aca="false">AG69*Q69</f>
-        <v>3817954.47938242</v>
+        <v>3903163.22686151</v>
       </c>
       <c r="AI69" s="0" t="n">
         <f aca="false">(AE69+AH69-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1707.95238103602</v>
+        <v>1706.77377031513</v>
       </c>
       <c r="AJ69" s="0" t="n">
         <f aca="false">AI69/AI$5-1</f>
-        <v>-0.0801694605432303</v>
+        <v>-0.0817148733274294</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11601,35 +11601,35 @@
       </c>
       <c r="X70" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C70+$C70*((1+Supuestos!$B$4+$B70/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113560.272843875</v>
+        <v>88618.7797767247</v>
       </c>
       <c r="Y70" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C70+$C70*((1+Supuestos!$B$4+$B70/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200389.236605567</v>
+        <v>150694.544314305</v>
       </c>
       <c r="Z70" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C70+$C70*((1+Supuestos!$B$4+$B70/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>262166.930425278</v>
+        <v>215268.559866941</v>
       </c>
       <c r="AA70" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C70+$C70*((1+Supuestos!$B$4+$B70/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>380713.619445775</v>
+        <v>388442.412965952</v>
       </c>
       <c r="AB70" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C70+$C70*((1+Supuestos!$B$4+$B70/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>384316.97612417</v>
+        <v>394525.234494548</v>
       </c>
       <c r="AC70" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C70+$C70*((1+Supuestos!$B$4+$B70/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>408329.300991755</v>
+        <v>419571.343237145</v>
       </c>
       <c r="AD70" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C70+$C70*((1+Supuestos!$B$4+$B70/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>544189.025588628</v>
+        <v>556334.184865061</v>
       </c>
       <c r="AE70" s="0" t="n">
         <f aca="false">SUMPRODUCT(X70:AC70,R70:W70)</f>
-        <v>1261370.29293577</v>
+        <v>1173548.525411</v>
       </c>
       <c r="AF70" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B70/10000)-1</f>
@@ -11637,19 +11637,19 @@
       </c>
       <c r="AG70" s="0" t="n">
         <f aca="false">AD70/(K70-AF70)</f>
-        <v>7052725.53656863</v>
+        <v>7210127.59898977</v>
       </c>
       <c r="AH70" s="0" t="n">
         <f aca="false">AG70*Q70</f>
-        <v>3880373.32105262</v>
+        <v>3966975.12634488</v>
       </c>
       <c r="AI70" s="0" t="n">
         <f aca="false">(AE70+AH70-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1737.51717533716</v>
+        <v>1736.96011495702</v>
       </c>
       <c r="AJ70" s="0" t="n">
         <f aca="false">AI70/AI$5-1</f>
-        <v>-0.0642471192690213</v>
+        <v>-0.0654738976366995</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11743,35 +11743,35 @@
       </c>
       <c r="X71" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C71+$C71*((1+Supuestos!$B$4+$B71/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113579.439626352</v>
+        <v>88633.736916513</v>
       </c>
       <c r="Y71" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C71+$C71*((1+Supuestos!$B$4+$B71/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200524.77865371</v>
+        <v>150796.473177982</v>
       </c>
       <c r="Z71" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C71+$C71*((1+Supuestos!$B$4+$B71/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>262522.47422038</v>
+        <v>215560.501343377</v>
       </c>
       <c r="AA71" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C71+$C71*((1+Supuestos!$B$4+$B71/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>381490.020802054</v>
+        <v>389234.575895931</v>
       </c>
       <c r="AB71" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C71+$C71*((1+Supuestos!$B$4+$B71/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>385364.571275389</v>
+        <v>395600.655952268</v>
       </c>
       <c r="AC71" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C71+$C71*((1+Supuestos!$B$4+$B71/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>409724.055156978</v>
+        <v>421004.497500547</v>
       </c>
       <c r="AD71" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C71+$C71*((1+Supuestos!$B$4+$B71/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>546425.105149612</v>
+        <v>558620.169038498</v>
       </c>
       <c r="AE71" s="0" t="n">
         <f aca="false">SUMPRODUCT(X71:AC71,R71:W71)</f>
-        <v>1263710.28713932</v>
+        <v>1175856.67813069</v>
       </c>
       <c r="AF71" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B71/10000)-1</f>
@@ -11779,19 +11779,19 @@
       </c>
       <c r="AG71" s="0" t="n">
         <f aca="false">AD71/(K71-AF71)</f>
-        <v>7170846.14907079</v>
+        <v>7330884.41616568</v>
       </c>
       <c r="AH71" s="0" t="n">
         <f aca="false">AG71*Q71</f>
-        <v>3944565.63955881</v>
+        <v>4032600.08295275</v>
       </c>
       <c r="AI71" s="0" t="n">
         <f aca="false">(AE71+AH71-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1767.8972268028</v>
+        <v>1767.97979958148</v>
       </c>
       <c r="AJ71" s="0" t="n">
         <f aca="false">AI71/AI$5-1</f>
-        <v>-0.0478857151463799</v>
+        <v>-0.0487845650958934</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11885,35 +11885,35 @@
       </c>
       <c r="X72" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C72+$C72*((1+Supuestos!$B$4+$B72/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113598.592564996</v>
+        <v>88648.6832530204</v>
       </c>
       <c r="Y72" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C72+$C72*((1+Supuestos!$B$4+$B72/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200660.320701854</v>
+        <v>150898.40204166</v>
       </c>
       <c r="Z72" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C72+$C72*((1+Supuestos!$B$4+$B72/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>262878.360708295</v>
+        <v>215852.724209188</v>
       </c>
       <c r="AA72" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C72+$C72*((1+Supuestos!$B$4+$B72/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>382267.919556821</v>
+        <v>390028.266622795</v>
       </c>
       <c r="AB72" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C72+$C72*((1+Supuestos!$B$4+$B72/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>386415.198537577</v>
+        <v>396679.190060132</v>
       </c>
       <c r="AC72" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C72+$C72*((1+Supuestos!$B$4+$B72/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>411124.194465907</v>
+        <v>422443.185170376</v>
       </c>
       <c r="AD72" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C72+$C72*((1+Supuestos!$B$4+$B72/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>548671.981787887</v>
+        <v>560917.191257377</v>
       </c>
       <c r="AE72" s="0" t="n">
         <f aca="false">SUMPRODUCT(X72:AC72,R72:W72)</f>
-        <v>1266062.27216578</v>
+        <v>1178176.84347155</v>
       </c>
       <c r="AF72" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B72/10000)-1</f>
@@ -11921,19 +11921,19 @@
       </c>
       <c r="AG72" s="0" t="n">
         <f aca="false">AD72/(K72-AF72)</f>
-        <v>7292304.07405068</v>
+        <v>7455053.02764402</v>
       </c>
       <c r="AH72" s="0" t="n">
         <f aca="false">AG72*Q72</f>
-        <v>4010604.76306372</v>
+        <v>4100113.0613789</v>
       </c>
       <c r="AI72" s="0" t="n">
         <f aca="false">(AE72+AH72-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1799.12604348379</v>
+        <v>1799.86707984039</v>
       </c>
       <c r="AJ72" s="0" t="n">
         <f aca="false">AI72/AI$5-1</f>
-        <v>-0.0310672021636879</v>
+        <v>-0.0316284453446585</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12027,35 +12027,35 @@
       </c>
       <c r="X73" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C73+$C73*((1+Supuestos!$B$4+$B73/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113617.731683117</v>
+        <v>88663.6188044366</v>
       </c>
       <c r="Y73" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C73+$C73*((1+Supuestos!$B$4+$B73/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>200795.862749998</v>
+        <v>151000.330905338</v>
       </c>
       <c r="Z73" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C73+$C73*((1+Supuestos!$B$4+$B73/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>263234.589889026</v>
+        <v>216145.228464374</v>
       </c>
       <c r="AA73" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C73+$C73*((1+Supuestos!$B$4+$B73/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>383047.317152657</v>
+        <v>390823.48661841</v>
       </c>
       <c r="AB73" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C73+$C73*((1+Supuestos!$B$4+$B73/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>387468.863755766</v>
+        <v>397760.842818428</v>
       </c>
       <c r="AC73" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C73+$C73*((1+Supuestos!$B$4+$B73/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>412529.734497535</v>
+        <v>423887.422254541</v>
       </c>
       <c r="AD73" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C73+$C73*((1+Supuestos!$B$4+$B73/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>550929.697170832</v>
+        <v>563225.294119005</v>
       </c>
       <c r="AE73" s="0" t="n">
         <f aca="false">SUMPRODUCT(X73:AC73,R73:W73)</f>
-        <v>1268426.30289032</v>
+        <v>1180509.07703055</v>
       </c>
       <c r="AF73" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B73/10000)-1</f>
@@ -12063,19 +12063,19 @@
       </c>
       <c r="AG73" s="0" t="n">
         <f aca="false">AD73/(K73-AF73)</f>
-        <v>7417238.63882669</v>
+        <v>7582775.8702371</v>
       </c>
       <c r="AH73" s="0" t="n">
         <f aca="false">AG73*Q73</f>
-        <v>4078568.09761342</v>
+        <v>4169593.19521019</v>
       </c>
       <c r="AI73" s="0" t="n">
         <f aca="false">(AE73+AH73-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1831.23899566381</v>
+        <v>1832.65811517842</v>
       </c>
       <c r="AJ73" s="0" t="n">
         <f aca="false">AI73/AI$5-1</f>
-        <v>-0.0137725313899169</v>
+        <v>-0.0139860837365653</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12169,35 +12169,35 @@
       </c>
       <c r="X74" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C74+$C74*((1+Supuestos!$B$4+$B74/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y74" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C74+$C74*((1+Supuestos!$B$4+$B74/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z74" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C74+$C74*((1+Supuestos!$B$4+$B74/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA74" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C74+$C74*((1+Supuestos!$B$4+$B74/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB74" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C74+$C74*((1+Supuestos!$B$4+$B74/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC74" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C74+$C74*((1+Supuestos!$B$4+$B74/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD74" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C74+$C74*((1+Supuestos!$B$4+$B74/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE74" s="0" t="n">
         <f aca="false">SUMPRODUCT(X74:AC74,R74:W74)</f>
-        <v>1310631.05293323</v>
+        <v>1222146.56553767</v>
       </c>
       <c r="AF74" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B74/10000)-1</f>
@@ -12205,19 +12205,19 @@
       </c>
       <c r="AG74" s="0" t="n">
         <f aca="false">AD74/(K74-AF74)</f>
-        <v>8204590.23273713</v>
+        <v>8387699.50265796</v>
       </c>
       <c r="AH74" s="0" t="n">
         <f aca="false">AG74*Q74</f>
-        <v>4982471.04885489</v>
+        <v>5093669.36714715</v>
       </c>
       <c r="AI74" s="0" t="n">
         <f aca="false">(AE74+AH74-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2263.25164465211</v>
+        <v>2273.62325693371</v>
       </c>
       <c r="AJ74" s="0" t="n">
         <f aca="false">AI74/AI$5-1</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12311,35 +12311,35 @@
       </c>
       <c r="X75" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C75+$C75*((1+Supuestos!$B$4+$B75/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113398.175225783</v>
+        <v>88492.2840158372</v>
       </c>
       <c r="Y75" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C75+$C75*((1+Supuestos!$B$4+$B75/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199246.810771213</v>
+        <v>149835.429606164</v>
       </c>
       <c r="Z75" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C75+$C75*((1+Supuestos!$B$4+$B75/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259183.7160404</v>
+        <v>212819.005060905</v>
       </c>
       <c r="AA75" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C75+$C75*((1+Supuestos!$B$4+$B75/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>374228.510073755</v>
+        <v>381825.650643441</v>
       </c>
       <c r="AB75" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C75+$C75*((1+Supuestos!$B$4+$B75/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>375606.007930436</v>
+        <v>385582.884864389</v>
       </c>
       <c r="AC75" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C75+$C75*((1+Supuestos!$B$4+$B75/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>396783.745989796</v>
+        <v>407707.918278847</v>
       </c>
       <c r="AD75" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C75+$C75*((1+Supuestos!$B$4+$B75/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>525762.185408225</v>
+        <v>537496.09620586</v>
       </c>
       <c r="AE75" s="0" t="n">
         <f aca="false">SUMPRODUCT(X75:AC75,R75:W75)</f>
-        <v>1307060.99634076</v>
+        <v>1218622.07340236</v>
       </c>
       <c r="AF75" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B75/10000)-1</f>
@@ -12347,19 +12347,19 @@
       </c>
       <c r="AG75" s="0" t="n">
         <f aca="false">AD75/(K75-AF75)</f>
-        <v>8036846.18938639</v>
+        <v>8216211.76359053</v>
       </c>
       <c r="AH75" s="0" t="n">
         <f aca="false">AG75*Q75</f>
-        <v>4881514.97038144</v>
+        <v>4990460.16044927</v>
       </c>
       <c r="AI75" s="0" t="n">
         <f aca="false">(AE75+AH75-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2215.52281585489</v>
+        <v>2224.88640815143</v>
       </c>
       <c r="AJ75" s="0" t="n">
         <f aca="false">AI75/AI$5-1</f>
-        <v>0.193186396479287</v>
+        <v>0.197042122790646</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12453,35 +12453,35 @@
       </c>
       <c r="X76" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C76+$C76*((1+Supuestos!$B$4+$B76/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113370.614602719</v>
+        <v>88470.7765931733</v>
       </c>
       <c r="Y76" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C76+$C76*((1+Supuestos!$B$4+$B76/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199053.179273865</v>
+        <v>149689.816943768</v>
       </c>
       <c r="Z76" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C76+$C76*((1+Supuestos!$B$4+$B76/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>258680.202383585</v>
+        <v>212405.563672245</v>
       </c>
       <c r="AA76" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C76+$C76*((1+Supuestos!$B$4+$B76/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>373138.524808026</v>
+        <v>380713.537797745</v>
       </c>
       <c r="AB76" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C76+$C76*((1+Supuestos!$B$4+$B76/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>374148.053287273</v>
+        <v>384086.203912959</v>
       </c>
       <c r="AC76" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C76+$C76*((1+Supuestos!$B$4+$B76/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>394859.483149769</v>
+        <v>405730.677011638</v>
       </c>
       <c r="AD76" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C76+$C76*((1+Supuestos!$B$4+$B76/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>522703.955219387</v>
+        <v>534369.612724505</v>
       </c>
       <c r="AE76" s="0" t="n">
         <f aca="false">SUMPRODUCT(X76:AC76,R76:W76)</f>
-        <v>1303506.31838201</v>
+        <v>1215113.03963557</v>
       </c>
       <c r="AF76" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B76/10000)-1</f>
@@ -12489,19 +12489,19 @@
       </c>
       <c r="AG76" s="0" t="n">
         <f aca="false">AD76/(K76-AF76)</f>
-        <v>7874416.18346294</v>
+        <v>8050156.6601358</v>
       </c>
       <c r="AH76" s="0" t="n">
         <f aca="false">AG76*Q76</f>
-        <v>4783794.82703902</v>
+        <v>4890559.10817704</v>
       </c>
       <c r="AI76" s="0" t="n">
         <f aca="false">(AE76+AH76-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2169.27860521508</v>
+        <v>2177.66719078201</v>
       </c>
       <c r="AJ76" s="0" t="n">
         <f aca="false">AI76/AI$5-1</f>
-        <v>0.168281230684348</v>
+        <v>0.171637054024299</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12595,35 +12595,35 @@
       </c>
       <c r="X77" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C77+$C77*((1+Supuestos!$B$4+$B77/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113343.033864854</v>
+        <v>88449.2534735676</v>
       </c>
       <c r="Y77" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C77+$C77*((1+Supuestos!$B$4+$B77/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198859.547776517</v>
+        <v>149544.204281371</v>
       </c>
       <c r="Z77" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C77+$C77*((1+Supuestos!$B$4+$B77/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>258177.178287935</v>
+        <v>211992.524268406</v>
       </c>
       <c r="AA77" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C77+$C77*((1+Supuestos!$B$4+$B77/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>372050.658074703</v>
+        <v>379603.586492371</v>
       </c>
       <c r="AB77" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C77+$C77*((1+Supuestos!$B$4+$B77/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>372694.347172994</v>
+        <v>382593.884340178</v>
       </c>
       <c r="AC77" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C77+$C77*((1+Supuestos!$B$4+$B77/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>392942.693164553</v>
+        <v>403761.114340414</v>
       </c>
       <c r="AD77" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C77+$C77*((1+Supuestos!$B$4+$B77/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>519660.563572289</v>
+        <v>531258.298950065</v>
       </c>
       <c r="AE77" s="0" t="n">
         <f aca="false">SUMPRODUCT(X77:AC77,R77:W77)</f>
-        <v>1299966.93423208</v>
+        <v>1211619.37828569</v>
       </c>
       <c r="AF77" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B77/10000)-1</f>
@@ -12631,19 +12631,19 @@
       </c>
       <c r="AG77" s="0" t="n">
         <f aca="false">AD77/(K77-AF77)</f>
-        <v>7717058.2265732</v>
+        <v>7889286.80322607</v>
       </c>
       <c r="AH77" s="0" t="n">
         <f aca="false">AG77*Q77</f>
-        <v>4689162.68295431</v>
+        <v>4793814.9728383</v>
       </c>
       <c r="AI77" s="0" t="n">
         <f aca="false">(AE77+AH77-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2124.45142337278</v>
+        <v>2131.89650736255</v>
       </c>
       <c r="AJ77" s="0" t="n">
         <f aca="false">AI77/AI$5-1</f>
-        <v>0.144139216355283</v>
+        <v>0.147011331182325</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12737,35 +12737,35 @@
       </c>
       <c r="X78" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C78+$C78*((1+Supuestos!$B$4+$B78/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113315.432977903</v>
+        <v>88427.7146302629</v>
       </c>
       <c r="Y78" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C78+$C78*((1+Supuestos!$B$4+$B78/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198665.916279169</v>
+        <v>149398.591618974</v>
       </c>
       <c r="Z78" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C78+$C78*((1+Supuestos!$B$4+$B78/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257674.643753447</v>
+        <v>211579.886849388</v>
       </c>
       <c r="AA78" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C78+$C78*((1+Supuestos!$B$4+$B78/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370964.907812954</v>
+        <v>378495.794624652</v>
       </c>
       <c r="AB78" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C78+$C78*((1+Supuestos!$B$4+$B78/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>371244.881325999</v>
+        <v>381105.917665002</v>
       </c>
       <c r="AC78" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C78+$C78*((1+Supuestos!$B$4+$B78/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>391033.354247421</v>
+        <v>401799.207878618</v>
       </c>
       <c r="AD78" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C78+$C78*((1+Supuestos!$B$4+$B78/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>516631.952813636</v>
+        <v>528162.095942542</v>
       </c>
       <c r="AE78" s="0" t="n">
         <f aca="false">SUMPRODUCT(X78:AC78,R78:W78)</f>
-        <v>1296442.759623</v>
+        <v>1208141.00396804</v>
       </c>
       <c r="AF78" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B78/10000)-1</f>
@@ -12773,19 +12773,19 @@
       </c>
       <c r="AG78" s="0" t="n">
         <f aca="false">AD78/(K78-AF78)</f>
-        <v>7564544.77815036</v>
+        <v>7733369.57406567</v>
       </c>
       <c r="AH78" s="0" t="n">
         <f aca="false">AG78*Q78</f>
-        <v>4597479.4405229</v>
+        <v>4700085.55246145</v>
       </c>
       <c r="AI78" s="0" t="n">
         <f aca="false">(AE78+AH78-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2080.9777169616</v>
+        <v>2087.50938649748</v>
       </c>
       <c r="AJ78" s="0" t="n">
         <f aca="false">AI78/AI$5-1</f>
-        <v>0.120726126350907</v>
+        <v>0.123129998099332</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12879,35 +12879,35 @@
       </c>
       <c r="X79" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C79+$C79*((1+Supuestos!$B$4+$B79/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113287.811907483</v>
+        <v>88406.1600364302</v>
       </c>
       <c r="Y79" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C79+$C79*((1+Supuestos!$B$4+$B79/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198472.28478182</v>
+        <v>149252.978956578</v>
       </c>
       <c r="Z79" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C79+$C79*((1+Supuestos!$B$4+$B79/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257172.598780124</v>
+        <v>211167.651415192</v>
       </c>
       <c r="AA79" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C79+$C79*((1+Supuestos!$B$4+$B79/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>369881.271961953</v>
+        <v>377390.160091923</v>
       </c>
       <c r="AB79" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C79+$C79*((1+Supuestos!$B$4+$B79/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>369799.647492731</v>
+        <v>379622.29541464</v>
       </c>
       <c r="AC79" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C79+$C79*((1+Supuestos!$B$4+$B79/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>389131.444654032</v>
+        <v>399844.93528325</v>
       </c>
       <c r="AD79" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C79+$C79*((1+Supuestos!$B$4+$B79/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>513618.065458298</v>
+        <v>525080.944933858</v>
       </c>
       <c r="AE79" s="0" t="n">
         <f aca="false">SUMPRODUCT(X79:AC79,R79:W79)</f>
-        <v>1292933.71083957</v>
+        <v>1204677.83186058</v>
       </c>
       <c r="AF79" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B79/10000)-1</f>
@@ -12915,19 +12915,19 @@
       </c>
       <c r="AG79" s="0" t="n">
         <f aca="false">AD79/(K79-AF79)</f>
-        <v>7416661.68312057</v>
+        <v>7582186.03808802</v>
       </c>
       <c r="AH79" s="0" t="n">
         <f aca="false">AG79*Q79</f>
-        <v>4508614.19048782</v>
+        <v>4609237.01616909</v>
       </c>
       <c r="AI79" s="0" t="n">
         <f aca="false">(AE79+AH79-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2038.79767183899</v>
+        <v>2044.4446794656</v>
       </c>
       <c r="AJ79" s="0" t="n">
         <f aca="false">AI79/AI$5-1</f>
-        <v>0.0980097473170249</v>
+        <v>0.0999601553001979</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13021,35 +13021,35 @@
       </c>
       <c r="X80" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C80+$C80*((1+Supuestos!$B$4+$B80/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113260.170619125</v>
+        <v>88384.5896651686</v>
       </c>
       <c r="Y80" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C80+$C80*((1+Supuestos!$B$4+$B80/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198278.653284472</v>
+        <v>149107.366294181</v>
       </c>
       <c r="Z80" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C80+$C80*((1+Supuestos!$B$4+$B80/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>256671.043367964</v>
+        <v>210755.817965816</v>
       </c>
       <c r="AA80" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C80+$C80*((1+Supuestos!$B$4+$B80/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>368799.748460868</v>
+        <v>376286.680791518</v>
       </c>
       <c r="AB80" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C80+$C80*((1+Supuestos!$B$4+$B80/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>368358.63742767</v>
+        <v>378143.009124556</v>
       </c>
       <c r="AC80" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C80+$C80*((1+Supuestos!$B$4+$B80/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>387236.942682388</v>
+        <v>397898.274254817</v>
       </c>
       <c r="AD80" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C80+$C80*((1+Supuestos!$B$4+$B80/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>510618.844188984</v>
+        <v>522014.787327521</v>
       </c>
       <c r="AE80" s="0" t="n">
         <f aca="false">SUMPRODUCT(X80:AC80,R80:W80)</f>
-        <v>1289439.70471513</v>
+        <v>1201229.77769964</v>
       </c>
       <c r="AF80" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B80/10000)-1</f>
@@ -13057,19 +13057,19 @@
       </c>
       <c r="AG80" s="0" t="n">
         <f aca="false">AD80/(K80-AF80)</f>
-        <v>7273207.20194534</v>
+        <v>7435529.95335067</v>
       </c>
       <c r="AH80" s="0" t="n">
         <f aca="false">AG80*Q80</f>
-        <v>4422443.61853327</v>
+        <v>4521143.29752815</v>
       </c>
       <c r="AI80" s="0" t="n">
         <f aca="false">(AE80+AH80-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1997.85494212256</v>
+        <v>2002.64478320904</v>
       </c>
       <c r="AJ80" s="0" t="n">
         <f aca="false">AI80/AI$5-1</f>
-        <v>0.0759597337568947</v>
+        <v>0.0774708109615088</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13163,35 +13163,35 @@
       </c>
       <c r="X81" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C81+$C81*((1+Supuestos!$B$4+$B81/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113232.509078261</v>
+        <v>88363.0034895046</v>
       </c>
       <c r="Y81" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C81+$C81*((1+Supuestos!$B$4+$B81/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198085.021787124</v>
+        <v>148961.753631784</v>
       </c>
       <c r="Z81" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C81+$C81*((1+Supuestos!$B$4+$B81/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>256169.977516968</v>
+        <v>210344.386501263</v>
       </c>
       <c r="AA81" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C81+$C81*((1+Supuestos!$B$4+$B81/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>367720.335248872</v>
+        <v>375185.354620772</v>
       </c>
       <c r="AB81" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C81+$C81*((1+Supuestos!$B$4+$B81/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>366921.842893341</v>
+        <v>376668.050338469</v>
       </c>
       <c r="AC81" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C81+$C81*((1+Supuestos!$B$4+$B81/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>385349.826672798</v>
+        <v>395959.202537297</v>
       </c>
       <c r="AD81" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C81+$C81*((1+Supuestos!$B$4+$B81/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>507634.231855919</v>
+        <v>518963.564698292</v>
       </c>
       <c r="AE81" s="0" t="n">
         <f aca="false">SUMPRODUCT(X81:AC81,R81:W81)</f>
-        <v>1285960.65862741</v>
+        <v>1197796.75777565</v>
       </c>
       <c r="AF81" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B81/10000)-1</f>
@@ -13199,19 +13199,19 @@
       </c>
       <c r="AG81" s="0" t="n">
         <f aca="false">AD81/(K81-AF81)</f>
-        <v>7133991.12380244</v>
+        <v>7293206.86392422</v>
       </c>
       <c r="AH81" s="0" t="n">
         <f aca="false">AG81*Q81</f>
-        <v>4338851.46274164</v>
+        <v>4435685.53989853</v>
       </c>
       <c r="AI81" s="0" t="n">
         <f aca="false">(AE81+AH81-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1958.09640245162</v>
+        <v>1962.05538706584</v>
       </c>
       <c r="AJ81" s="0" t="n">
         <f aca="false">AI81/AI$5-1</f>
-        <v>0.0545474746098629</v>
+        <v>0.0556327446476352</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13305,35 +13305,35 @@
       </c>
       <c r="X82" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C82+$C82*((1+Supuestos!$B$4+$B82/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113204.827250236</v>
+        <v>88341.4014823927</v>
       </c>
       <c r="Y82" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C82+$C82*((1+Supuestos!$B$4+$B82/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197891.390289776</v>
+        <v>148816.140969388</v>
       </c>
       <c r="Z82" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C82+$C82*((1+Supuestos!$B$4+$B82/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255669.401227135</v>
+        <v>209933.35702153</v>
       </c>
       <c r="AA82" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C82+$C82*((1+Supuestos!$B$4+$B82/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366643.030265134</v>
+        <v>374086.179477018</v>
       </c>
       <c r="AB82" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C82+$C82*((1+Supuestos!$B$4+$B82/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>365489.255660306</v>
+        <v>375197.410608351</v>
       </c>
       <c r="AC82" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C82+$C82*((1+Supuestos!$B$4+$B82/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>383470.075007833</v>
+        <v>394027.697918093</v>
       </c>
       <c r="AD82" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C82+$C82*((1+Supuestos!$B$4+$B82/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>504664.171476508</v>
+        <v>515927.218791845</v>
       </c>
       <c r="AE82" s="0" t="n">
         <f aca="false">SUMPRODUCT(X82:AC82,R82:W82)</f>
-        <v>1282496.4904944</v>
+        <v>1194378.68892896</v>
       </c>
       <c r="AF82" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B82/10000)-1</f>
@@ -13341,19 +13341,19 @@
       </c>
       <c r="AG82" s="0" t="n">
         <f aca="false">AD82/(K82-AF82)</f>
-        <v>6998833.95470904</v>
+        <v>7155033.2698961</v>
       </c>
       <c r="AH82" s="0" t="n">
         <f aca="false">AG82*Q82</f>
-        <v>4257728.01689965</v>
+        <v>4352751.58865405</v>
       </c>
       <c r="AI82" s="0" t="n">
         <f aca="false">(AE82+AH82-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1919.4719211845</v>
+        <v>1922.62524090548</v>
       </c>
       <c r="AJ82" s="0" t="n">
         <f aca="false">AI82/AI$5-1</f>
-        <v>0.0337459711050507</v>
+        <v>0.034418382562089</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13447,35 +13447,35 @@
       </c>
       <c r="X83" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C83+$C83*((1+Supuestos!$B$4+$B83/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113177.125100297</v>
+        <v>88319.783616714</v>
       </c>
       <c r="Y83" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C83+$C83*((1+Supuestos!$B$4+$B83/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197697.758792428</v>
+        <v>148670.528306991</v>
       </c>
       <c r="Z83" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C83+$C83*((1+Supuestos!$B$4+$B83/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255169.314498466</v>
+        <v>209522.729526619</v>
       </c>
       <c r="AA83" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C83+$C83*((1+Supuestos!$B$4+$B83/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>365567.831448826</v>
+        <v>372989.153257591</v>
       </c>
       <c r="AB83" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C83+$C83*((1+Supuestos!$B$4+$B83/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364060.867507168</v>
+        <v>373731.081494427</v>
       </c>
       <c r="AC83" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C83+$C83*((1+Supuestos!$B$4+$B83/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>381597.666112284</v>
+        <v>392103.738227994</v>
       </c>
       <c r="AD83" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C83+$C83*((1+Supuestos!$B$4+$B83/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>501708.606235023</v>
+        <v>512905.691524442</v>
       </c>
       <c r="AE83" s="0" t="n">
         <f aca="false">SUMPRODUCT(X83:AC83,R83:W83)</f>
-        <v>1279047.11877032</v>
+        <v>1190975.48854565</v>
       </c>
       <c r="AF83" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B83/10000)-1</f>
@@ -13483,19 +13483,19 @@
       </c>
       <c r="AG83" s="0" t="n">
         <f aca="false">AD83/(K83-AF83)</f>
-        <v>6867566.17330084</v>
+        <v>7020835.86654018</v>
       </c>
       <c r="AH83" s="0" t="n">
         <f aca="false">AG83*Q83</f>
-        <v>4178969.6751958</v>
+        <v>4272235.52571849</v>
       </c>
       <c r="AI83" s="0" t="n">
         <f aca="false">(AE83+AH83-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1881.93415249594</v>
+        <v>1884.30594258636</v>
       </c>
       <c r="AJ83" s="0" t="n">
         <f aca="false">AI83/AI$5-1</f>
-        <v>0.0135297247938668</v>
+        <v>0.0138016831945562</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13589,35 +13589,35 @@
       </c>
       <c r="X84" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C84+$C84*((1+Supuestos!$B$4+$B84/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113149.4025936</v>
+        <v>88298.149865277</v>
       </c>
       <c r="Y84" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C84+$C84*((1+Supuestos!$B$4+$B84/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197504.12729508</v>
+        <v>148524.915644594</v>
       </c>
       <c r="Z84" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C84+$C84*((1+Supuestos!$B$4+$B84/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>254669.717330961</v>
+        <v>209112.504016529</v>
       </c>
       <c r="AA84" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C84+$C84*((1+Supuestos!$B$4+$B84/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>364494.736739118</v>
+        <v>371894.273859826</v>
       </c>
       <c r="AB84" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C84+$C84*((1+Supuestos!$B$4+$B84/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>362636.670220572</v>
+        <v>372269.054565179</v>
       </c>
       <c r="AC84" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C84+$C84*((1+Supuestos!$B$4+$B84/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>379732.578453125</v>
+        <v>390187.301341129</v>
       </c>
       <c r="AD84" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C84+$C84*((1+Supuestos!$B$4+$B84/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>498767.479482262</v>
+        <v>509898.924982592</v>
       </c>
       <c r="AE84" s="0" t="n">
         <f aca="false">SUMPRODUCT(X84:AC84,R84:W84)</f>
-        <v>1275612.4624415</v>
+        <v>1187587.07455343</v>
       </c>
       <c r="AF84" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B84/10000)-1</f>
@@ -13625,19 +13625,19 @@
       </c>
       <c r="AG84" s="0" t="n">
         <f aca="false">AD84/(K84-AF84)</f>
-        <v>6740027.54777928</v>
+        <v>6890450.84601979</v>
       </c>
       <c r="AH84" s="0" t="n">
         <f aca="false">AG84*Q84</f>
-        <v>4102478.51433996</v>
+        <v>4194037.24235898</v>
       </c>
       <c r="AI84" s="0" t="n">
         <f aca="false">(AE84+AH84-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1845.43834556231</v>
+        <v>1847.05174288238</v>
       </c>
       <c r="AJ84" s="0" t="n">
         <f aca="false">AI84/AI$5-1</f>
-        <v>-0.00612536521473805</v>
+        <v>-0.00624196763325058</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13731,35 +13731,35 @@
       </c>
       <c r="X85" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C85+$C85*((1+Supuestos!$B$4+$B85/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y85" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C85+$C85*((1+Supuestos!$B$4+$B85/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z85" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C85+$C85*((1+Supuestos!$B$4+$B85/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA85" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C85+$C85*((1+Supuestos!$B$4+$B85/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB85" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C85+$C85*((1+Supuestos!$B$4+$B85/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC85" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C85+$C85*((1+Supuestos!$B$4+$B85/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD85" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C85+$C85*((1+Supuestos!$B$4+$B85/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE85" s="0" t="n">
         <f aca="false">SUMPRODUCT(X85:AC85,R85:W85)</f>
-        <v>1310631.05293323</v>
+        <v>1222146.56553767</v>
       </c>
       <c r="AF85" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B85/10000)-1</f>
@@ -13767,19 +13767,19 @@
       </c>
       <c r="AG85" s="0" t="n">
         <f aca="false">AD85/(K85-AF85)</f>
-        <v>8204590.23273713</v>
+        <v>8387699.50265796</v>
       </c>
       <c r="AH85" s="0" t="n">
         <f aca="false">AG85*Q85</f>
-        <v>4982471.04885489</v>
+        <v>5093669.36714715</v>
       </c>
       <c r="AI85" s="0" t="n">
         <f aca="false">(AE85+AH85-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2263.25164465211</v>
+        <v>2273.62325693371</v>
       </c>
       <c r="AJ85" s="0" t="n">
         <f aca="false">AI85/AI$5-1</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13873,35 +13873,35 @@
       </c>
       <c r="X86" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C86+$C86*((1+Supuestos!$B$4+$B86/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113402.306307153</v>
+        <v>88495.5077786984</v>
       </c>
       <c r="Y86" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C86+$C86*((1+Supuestos!$B$4+$B86/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199275.855495815</v>
+        <v>149857.271505524</v>
       </c>
       <c r="Z86" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C86+$C86*((1+Supuestos!$B$4+$B86/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259259.316523097</v>
+        <v>212881.081566927</v>
       </c>
       <c r="AA86" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C86+$C86*((1+Supuestos!$B$4+$B86/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>374392.325952599</v>
+        <v>381992.792116743</v>
       </c>
       <c r="AB86" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C86+$C86*((1+Supuestos!$B$4+$B86/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>375825.339646688</v>
+        <v>385808.042487296</v>
       </c>
       <c r="AC86" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C86+$C86*((1+Supuestos!$B$4+$B86/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>397073.509618395</v>
+        <v>408005.659622849</v>
       </c>
       <c r="AD86" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C86+$C86*((1+Supuestos!$B$4+$B86/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>526223.154391081</v>
+        <v>537967.353050938</v>
       </c>
       <c r="AE86" s="0" t="n">
         <f aca="false">SUMPRODUCT(X86:AC86,R86:W86)</f>
-        <v>1307615.95244325</v>
+        <v>1219169.94622033</v>
       </c>
       <c r="AF86" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B86/10000)-1</f>
@@ -13909,19 +13909,19 @@
       </c>
       <c r="AG86" s="0" t="n">
         <f aca="false">AD86/(K86-AF86)</f>
-        <v>8043892.60108375</v>
+        <v>8223415.43643864</v>
       </c>
       <c r="AH86" s="0" t="n">
         <f aca="false">AG86*Q86</f>
-        <v>4885794.90350167</v>
+        <v>4994835.61271265</v>
       </c>
       <c r="AI86" s="0" t="n">
         <f aca="false">(AE86+AH86-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2217.73052782873</v>
+        <v>2227.13450179588</v>
       </c>
       <c r="AJ86" s="0" t="n">
         <f aca="false">AI86/AI$5-1</f>
-        <v>0.194375376288335</v>
+        <v>0.198251650961849</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14015,35 +14015,35 @@
       </c>
       <c r="X87" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C87+$C87*((1+Supuestos!$B$4+$B87/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113378.879777548</v>
+        <v>88477.2264694341</v>
       </c>
       <c r="Y87" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C87+$C87*((1+Supuestos!$B$4+$B87/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199111.268723069</v>
+        <v>149733.500742487</v>
       </c>
       <c r="Z87" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C87+$C87*((1+Supuestos!$B$4+$B87/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>258831.329914804</v>
+        <v>212529.656386566</v>
       </c>
       <c r="AA87" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C87+$C87*((1+Supuestos!$B$4+$B87/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>373465.83847673</v>
+        <v>381047.496197902</v>
       </c>
       <c r="AB87" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C87+$C87*((1+Supuestos!$B$4+$B87/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>374586.0782</v>
+        <v>384535.86367858</v>
       </c>
       <c r="AC87" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C87+$C87*((1+Supuestos!$B$4+$B87/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>395437.886204372</v>
+        <v>406325.004545721</v>
       </c>
       <c r="AD87" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C87+$C87*((1+Supuestos!$B$4+$B87/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>523623.658730568</v>
+        <v>535309.842091787</v>
       </c>
       <c r="AE87" s="0" t="n">
         <f aca="false">SUMPRODUCT(X87:AC87,R87:W87)</f>
-        <v>1304614.91850703</v>
+        <v>1216207.44852181</v>
       </c>
       <c r="AF87" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B87/10000)-1</f>
@@ -14051,19 +14051,19 @@
       </c>
       <c r="AG87" s="0" t="n">
         <f aca="false">AD87/(K87-AF87)</f>
-        <v>7888271.30764962</v>
+        <v>8064321.00167551</v>
       </c>
       <c r="AH87" s="0" t="n">
         <f aca="false">AG87*Q87</f>
-        <v>4792211.96805214</v>
+        <v>4899164.10214832</v>
       </c>
       <c r="AI87" s="0" t="n">
         <f aca="false">(AE87+AH87-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2173.62825870282</v>
+        <v>2182.09614185851</v>
       </c>
       <c r="AJ87" s="0" t="n">
         <f aca="false">AI87/AI$5-1</f>
-        <v>0.170623769128919</v>
+        <v>0.174019935675659</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14157,35 +14157,35 @@
       </c>
       <c r="X88" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C88+$C88*((1+Supuestos!$B$4+$B88/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113355.436150363</v>
+        <v>88458.9318177692</v>
       </c>
       <c r="Y88" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C88+$C88*((1+Supuestos!$B$4+$B88/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198946.681950323</v>
+        <v>149609.72997945</v>
       </c>
       <c r="Z88" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C88+$C88*((1+Supuestos!$B$4+$B88/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>258403.759433501</v>
+        <v>212178.572893303</v>
       </c>
       <c r="AA88" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C88+$C88*((1+Supuestos!$B$4+$B88/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>372541.151753405</v>
+        <v>380104.037588334</v>
       </c>
       <c r="AB88" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C88+$C88*((1+Supuestos!$B$4+$B88/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>373350.428002863</v>
+        <v>383267.392041717</v>
       </c>
       <c r="AC88" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C88+$C88*((1+Supuestos!$B$4+$B88/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>393808.614716939</v>
+        <v>404650.87627518</v>
       </c>
       <c r="AD88" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C88+$C88*((1+Supuestos!$B$4+$B88/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>521036.775830535</v>
+        <v>532665.225383513</v>
       </c>
       <c r="AE88" s="0" t="n">
         <f aca="false">SUMPRODUCT(X88:AC88,R88:W88)</f>
-        <v>1301627.87952417</v>
+        <v>1213258.99988644</v>
       </c>
       <c r="AF88" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B88/10000)-1</f>
@@ -14193,19 +14193,19 @@
       </c>
       <c r="AG88" s="0" t="n">
         <f aca="false">AD88/(K88-AF88)</f>
-        <v>7737495.24041161</v>
+        <v>7910179.92840913</v>
       </c>
       <c r="AH88" s="0" t="n">
         <f aca="false">AG88*Q88</f>
-        <v>4701580.94906407</v>
+        <v>4806510.38863825</v>
       </c>
       <c r="AI88" s="0" t="n">
         <f aca="false">(AE88+AH88-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2130.8802870266</v>
+        <v>2138.44218654095</v>
       </c>
       <c r="AJ88" s="0" t="n">
         <f aca="false">AI88/AI$5-1</f>
-        <v>0.147601528998447</v>
+        <v>0.150533063199794</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14299,35 +14299,35 @@
       </c>
       <c r="X89" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C89+$C89*((1+Supuestos!$B$4+$B89/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113331.975396454</v>
+        <v>88440.6238009603</v>
       </c>
       <c r="Y89" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C89+$C89*((1+Supuestos!$B$4+$B89/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198782.095177577</v>
+        <v>149485.959216412</v>
       </c>
       <c r="Z89" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C89+$C89*((1+Supuestos!$B$4+$B89/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257976.605079187</v>
+        <v>211827.831087138</v>
       </c>
       <c r="AA89" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C89+$C89*((1+Supuestos!$B$4+$B89/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>371618.264030919</v>
+        <v>379162.414500773</v>
       </c>
       <c r="AB89" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C89+$C89*((1+Supuestos!$B$4+$B89/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>372118.382032917</v>
+        <v>382002.620367816</v>
       </c>
       <c r="AC89" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C89+$C89*((1+Supuestos!$B$4+$B89/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>392185.676637377</v>
+        <v>402983.255782655</v>
       </c>
       <c r="AD89" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C89+$C89*((1+Supuestos!$B$4+$B89/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>518462.45668568</v>
+        <v>530033.452827117</v>
       </c>
       <c r="AE89" s="0" t="n">
         <f aca="false">SUMPRODUCT(X89:AC89,R89:W89)</f>
-        <v>1298654.76439217</v>
+        <v>1210324.52826502</v>
       </c>
       <c r="AF89" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B89/10000)-1</f>
@@ -14335,19 +14335,19 @@
       </c>
       <c r="AG89" s="0" t="n">
         <f aca="false">AD89/(K89-AF89)</f>
-        <v>7591347.08573362</v>
+        <v>7760770.05301819</v>
       </c>
       <c r="AH89" s="0" t="n">
         <f aca="false">AG89*Q89</f>
-        <v>4613768.9941823</v>
+        <v>4716738.65484093</v>
       </c>
       <c r="AI89" s="0" t="n">
         <f aca="false">(AE89+AH89-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2089.42591715729</v>
+        <v>2096.11058589313</v>
       </c>
       <c r="AJ89" s="0" t="n">
         <f aca="false">AI89/AI$5-1</f>
-        <v>0.125275967804174</v>
+        <v>0.127757649176433</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14441,35 +14441,35 @@
       </c>
       <c r="X90" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C90+$C90*((1+Supuestos!$B$4+$B90/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113308.497486598</v>
+        <v>88422.3023962025</v>
       </c>
       <c r="Y90" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C90+$C90*((1+Supuestos!$B$4+$B90/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198617.508404832</v>
+        <v>149362.188453375</v>
       </c>
       <c r="Z90" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C90+$C90*((1+Supuestos!$B$4+$B90/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257549.866851862</v>
+        <v>211477.430968071</v>
       </c>
       <c r="AA90" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C90+$C90*((1+Supuestos!$B$4+$B90/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370697.173557567</v>
+        <v>378222.625147953</v>
       </c>
       <c r="AB90" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C90+$C90*((1+Supuestos!$B$4+$B90/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370889.933274639</v>
+        <v>380741.541455009</v>
       </c>
       <c r="AC90" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C90+$C90*((1+Supuestos!$B$4+$B90/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390569.053482996</v>
+        <v>401322.124076592</v>
       </c>
       <c r="AD90" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C90+$C90*((1+Supuestos!$B$4+$B90/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>515900.652433643</v>
+        <v>527414.474469736</v>
       </c>
       <c r="AE90" s="0" t="n">
         <f aca="false">SUMPRODUCT(X90:AC90,R90:W90)</f>
-        <v>1295695.50250287</v>
+        <v>1207403.96211123</v>
       </c>
       <c r="AF90" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B90/10000)-1</f>
@@ -14477,19 +14477,19 @@
       </c>
       <c r="AG90" s="0" t="n">
         <f aca="false">AD90/(K90-AF90)</f>
-        <v>7449622.31378554</v>
+        <v>7615882.28099516</v>
       </c>
       <c r="AH90" s="0" t="n">
         <f aca="false">AG90*Q90</f>
-        <v>4528651.0714314</v>
+        <v>4629721.07832916</v>
       </c>
       <c r="AI90" s="0" t="n">
         <f aca="false">(AE90+AH90-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2049.20802462752</v>
+        <v>2055.04294084036</v>
       </c>
       <c r="AJ90" s="0" t="n">
         <f aca="false">AI90/AI$5-1</f>
-        <v>0.103616320736594</v>
+        <v>0.105662273506075</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14583,35 +14583,35 @@
       </c>
       <c r="X91" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C91+$C91*((1+Supuestos!$B$4+$B91/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113285.002391493</v>
+        <v>88403.9675806301</v>
       </c>
       <c r="Y91" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C91+$C91*((1+Supuestos!$B$4+$B91/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198452.921632086</v>
+        <v>149238.417690338</v>
       </c>
       <c r="Z91" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C91+$C91*((1+Supuestos!$B$4+$B91/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257123.544751526</v>
+        <v>211127.372536102</v>
       </c>
       <c r="AA91" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C91+$C91*((1+Supuestos!$B$4+$B91/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>369777.878581645</v>
+        <v>377284.667742609</v>
       </c>
       <c r="AB91" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C91+$C91*((1+Supuestos!$B$4+$B91/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>369665.074719338</v>
+        <v>379484.148108437</v>
       </c>
       <c r="AC91" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C91+$C91*((1+Supuestos!$B$4+$B91/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>388958.726807098</v>
+        <v>399667.462202423</v>
       </c>
       <c r="AD91" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C91+$C91*((1+Supuestos!$B$4+$B91/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>513351.314354726</v>
+        <v>524808.24050435</v>
       </c>
       <c r="AE91" s="0" t="n">
         <f aca="false">SUMPRODUCT(X91:AC91,R91:W91)</f>
-        <v>1292750.0237389</v>
+        <v>1204497.230378</v>
       </c>
       <c r="AF91" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B91/10000)-1</f>
@@ -14619,19 +14619,19 @@
       </c>
       <c r="AG91" s="0" t="n">
         <f aca="false">AD91/(K91-AF91)</f>
-        <v>7312128.25218613</v>
+        <v>7475319.63991478</v>
       </c>
       <c r="AH91" s="0" t="n">
         <f aca="false">AG91*Q91</f>
-        <v>4446109.40248316</v>
+        <v>4545337.25220908</v>
       </c>
       <c r="AI91" s="0" t="n">
         <f aca="false">(AE91+AH91-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2010.17279736167</v>
+        <v>2015.18423862424</v>
       </c>
       <c r="AJ91" s="0" t="n">
         <f aca="false">AI91/AI$5-1</f>
-        <v>0.0825936068995816</v>
+        <v>0.084217338008399</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14725,35 +14725,35 @@
       </c>
       <c r="X92" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C92+$C92*((1+Supuestos!$B$4+$B92/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113261.490081759</v>
+        <v>88385.6193313157</v>
       </c>
       <c r="Y92" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C92+$C92*((1+Supuestos!$B$4+$B92/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198288.33485934</v>
+        <v>149114.646927301</v>
       </c>
       <c r="Z92" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C92+$C92*((1+Supuestos!$B$4+$B92/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>256697.638778179</v>
+        <v>210777.655791231</v>
       </c>
       <c r="AA92" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C92+$C92*((1+Supuestos!$B$4+$B92/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>368860.377351449</v>
+        <v>376348.540497474</v>
       </c>
       <c r="AB92" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C92+$C92*((1+Supuestos!$B$4+$B92/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>368443.799365158</v>
+        <v>378230.433140264</v>
       </c>
       <c r="AC92" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C92+$C92*((1+Supuestos!$B$4+$B92/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>387354.678198947</v>
+        <v>398019.251242531</v>
       </c>
       <c r="AD92" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C92+$C92*((1+Supuestos!$B$4+$B92/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>510814.39387162</v>
+        <v>522214.701269505</v>
       </c>
       <c r="AE92" s="0" t="n">
         <f aca="false">SUMPRODUCT(X92:AC92,R92:W92)</f>
-        <v>1289818.25847021</v>
+        <v>1201604.26251395</v>
       </c>
       <c r="AF92" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B92/10000)-1</f>
@@ -14761,19 +14761,19 @@
       </c>
       <c r="AG92" s="0" t="n">
         <f aca="false">AD92/(K92-AF92)</f>
-        <v>7178683.23904715</v>
+        <v>7338896.41357596</v>
       </c>
       <c r="AH92" s="0" t="n">
         <f aca="false">AG92*Q92</f>
-        <v>4366032.94450093</v>
+        <v>4463473.65540053</v>
       </c>
       <c r="AI92" s="0" t="n">
         <f aca="false">(AE92+AH92-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1972.26949907358</v>
+        <v>1976.48261091986</v>
       </c>
       <c r="AJ92" s="0" t="n">
         <f aca="false">AI92/AI$5-1</f>
-        <v>0.0621805018864448</v>
+        <v>0.06339493628354</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14867,35 +14867,35 @@
       </c>
       <c r="X93" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C93+$C93*((1+Supuestos!$B$4+$B93/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113237.960527937</v>
+        <v>88367.2576252705</v>
       </c>
       <c r="Y93" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C93+$C93*((1+Supuestos!$B$4+$B93/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198123.748086594</v>
+        <v>148990.876164264</v>
       </c>
       <c r="Z93" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C93+$C93*((1+Supuestos!$B$4+$B93/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>256272.148931822</v>
+        <v>210428.280733458</v>
       </c>
       <c r="AA93" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C93+$C93*((1+Supuestos!$B$4+$B93/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>367944.668115271</v>
+        <v>375414.241625283</v>
       </c>
       <c r="AB93" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C93+$C93*((1+Supuestos!$B$4+$B93/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>367226.100217078</v>
+        <v>376980.389369663</v>
       </c>
       <c r="AC93" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C93+$C93*((1+Supuestos!$B$4+$B93/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>385756.889283726</v>
+        <v>396377.472316208</v>
       </c>
       <c r="AD93" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C93+$C93*((1+Supuestos!$B$4+$B93/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>508289.842549121</v>
+        <v>519633.807249025</v>
       </c>
       <c r="AE93" s="0" t="n">
         <f aca="false">SUMPRODUCT(X93:AC93,R93:W93)</f>
-        <v>1286900.13755056</v>
+        <v>1198724.98845984</v>
       </c>
       <c r="AF93" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B93/10000)-1</f>
@@ -14903,19 +14903,19 @@
       </c>
       <c r="AG93" s="0" t="n">
         <f aca="false">AD93/(K93-AF93)</f>
-        <v>7049115.84759113</v>
+        <v>7206437.34931459</v>
       </c>
       <c r="AH93" s="0" t="n">
         <f aca="false">AG93*Q93</f>
-        <v>4288316.91577226</v>
+        <v>4384023.1676827</v>
       </c>
       <c r="AI93" s="0" t="n">
         <f aca="false">(AE93+AH93-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1935.45025265882</v>
+        <v>1938.88911239385</v>
       </c>
       <c r="AJ93" s="0" t="n">
         <f aca="false">AI93/AI$5-1</f>
-        <v>0.0423512211242185</v>
+        <v>0.0431687345710288</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15009,35 +15009,35 @@
       </c>
       <c r="X94" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C94+$C94*((1+Supuestos!$B$4+$B94/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113214.413700489</v>
+        <v>88348.8824394437</v>
       </c>
       <c r="Y94" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C94+$C94*((1+Supuestos!$B$4+$B94/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197959.161313848</v>
+        <v>148867.105401227</v>
       </c>
       <c r="Z94" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C94+$C94*((1+Supuestos!$B$4+$B94/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255847.075212453</v>
+        <v>210079.247362784</v>
       </c>
       <c r="AA94" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C94+$C94*((1+Supuestos!$B$4+$B94/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>367030.74912141</v>
+        <v>374481.769338771</v>
       </c>
       <c r="AB94" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C94+$C94*((1+Supuestos!$B$4+$B94/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>366011.970286911</v>
+        <v>375734.009622828</v>
       </c>
       <c r="AC94" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C94+$C94*((1+Supuestos!$B$4+$B94/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>384165.34172251</v>
+        <v>394742.106579624</v>
       </c>
       <c r="AD94" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C94+$C94*((1+Supuestos!$B$4+$B94/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>505777.612093858</v>
+        <v>517065.509071733</v>
       </c>
       <c r="AE94" s="0" t="n">
         <f aca="false">SUMPRODUCT(X94:AC94,R94:W94)</f>
-        <v>1283995.5923141</v>
+        <v>1195859.33864504</v>
       </c>
       <c r="AF94" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B94/10000)-1</f>
@@ -15045,19 +15045,19 @@
       </c>
       <c r="AG94" s="0" t="n">
         <f aca="false">AD94/(K94-AF94)</f>
-        <v>6923264.17538378</v>
+        <v>7077776.93137313</v>
       </c>
       <c r="AH94" s="0" t="n">
         <f aca="false">AG94*Q94</f>
-        <v>4212862.3608722</v>
+        <v>4306884.62515278</v>
       </c>
       <c r="AI94" s="0" t="n">
         <f aca="false">(AE94+AH94-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1899.66984163758</v>
+        <v>1902.3575177159</v>
       </c>
       <c r="AJ94" s="0" t="n">
         <f aca="false">AI94/AI$5-1</f>
-        <v>0.0230814129392316</v>
+        <v>0.0235138625371079</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15151,35 +15151,35 @@
       </c>
       <c r="X95" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C95+$C95*((1+Supuestos!$B$4+$B95/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113190.849569797</v>
+        <v>88330.4937507222</v>
       </c>
       <c r="Y95" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C95+$C95*((1+Supuestos!$B$4+$B95/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>197794.574541102</v>
+        <v>148743.334638189</v>
       </c>
       <c r="Z95" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C95+$C95*((1+Supuestos!$B$4+$B95/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>255422.417620074</v>
+        <v>209730.555679207</v>
       </c>
       <c r="AA95" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C95+$C95*((1+Supuestos!$B$4+$B95/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>366118.618618158</v>
+        <v>373551.12185067</v>
       </c>
       <c r="AB95" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C95+$C95*((1+Supuestos!$B$4+$B95/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>364801.402593305</v>
+        <v>374491.286732967</v>
       </c>
       <c r="AC95" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C95+$C95*((1+Supuestos!$B$4+$B95/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>382580.017212225</v>
+        <v>393113.135225789</v>
       </c>
       <c r="AD95" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C95+$C95*((1+Supuestos!$B$4+$B95/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>503277.654354012</v>
+        <v>514509.75751116</v>
       </c>
       <c r="AE95" s="0" t="n">
         <f aca="false">SUMPRODUCT(X95:AC95,R95:W95)</f>
-        <v>1281104.55457198</v>
+        <v>1193007.2439841</v>
       </c>
       <c r="AF95" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B95/10000)-1</f>
@@ -15187,19 +15187,19 @@
       </c>
       <c r="AG95" s="0" t="n">
         <f aca="false">AD95/(K95-AF95)</f>
-        <v>6800975.19198506</v>
+        <v>6952758.71399267</v>
       </c>
       <c r="AH95" s="0" t="n">
         <f aca="false">AG95*Q95</f>
-        <v>4139575.75156657</v>
+        <v>4231962.41222232</v>
       </c>
       <c r="AI95" s="0" t="n">
         <f aca="false">(AE95+AH95-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1864.88552791714</v>
+        <v>1866.84413525407</v>
       </c>
       <c r="AJ95" s="0" t="n">
         <f aca="false">AI95/AI$5-1</f>
-        <v>0.00434806041174873</v>
+        <v>0.00440681303838719</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15293,35 +15293,35 @@
       </c>
       <c r="X96" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C96+$C96*((1+Supuestos!$B$4+$B96/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y96" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C96+$C96*((1+Supuestos!$B$4+$B96/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z96" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C96+$C96*((1+Supuestos!$B$4+$B96/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA96" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C96+$C96*((1+Supuestos!$B$4+$B96/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB96" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C96+$C96*((1+Supuestos!$B$4+$B96/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC96" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C96+$C96*((1+Supuestos!$B$4+$B96/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD96" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C96+$C96*((1+Supuestos!$B$4+$B96/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE96" s="0" t="n">
         <f aca="false">SUMPRODUCT(X96:AC96,R96:W96)</f>
-        <v>1310631.05293323</v>
+        <v>1222146.56553767</v>
       </c>
       <c r="AF96" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B96/10000)-1</f>
@@ -15329,19 +15329,19 @@
       </c>
       <c r="AG96" s="0" t="n">
         <f aca="false">AD96/(K96-AF96)</f>
-        <v>8204590.23273713</v>
+        <v>8387699.50265796</v>
       </c>
       <c r="AH96" s="0" t="n">
         <f aca="false">AG96*Q96</f>
-        <v>4982471.04885489</v>
+        <v>5093669.36714715</v>
       </c>
       <c r="AI96" s="0" t="n">
         <f aca="false">(AE96+AH96-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2263.25164465211</v>
+        <v>2273.62325693371</v>
       </c>
       <c r="AJ96" s="0" t="n">
         <f aca="false">AI96/AI$5-1</f>
-        <v>0.218891114495815</v>
+        <v>0.223263713569719</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15435,35 +15435,35 @@
       </c>
       <c r="X97" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C97+$C97*((1+Supuestos!$B$4+$B97/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113406.437388522</v>
+        <v>88498.7315415596</v>
       </c>
       <c r="Y97" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C97+$C97*((1+Supuestos!$B$4+$B97/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199304.900220417</v>
+        <v>149879.113404883</v>
       </c>
       <c r="Z97" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C97+$C97*((1+Supuestos!$B$4+$B97/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259334.917005793</v>
+        <v>212943.158072949</v>
       </c>
       <c r="AA97" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C97+$C97*((1+Supuestos!$B$4+$B97/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>374556.141831443</v>
+        <v>382159.933590045</v>
       </c>
       <c r="AB97" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C97+$C97*((1+Supuestos!$B$4+$B97/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>376044.671362941</v>
+        <v>386033.200110202</v>
       </c>
       <c r="AC97" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C97+$C97*((1+Supuestos!$B$4+$B97/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>397363.273246995</v>
+        <v>408303.400966851</v>
       </c>
       <c r="AD97" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C97+$C97*((1+Supuestos!$B$4+$B97/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>526684.123373936</v>
+        <v>538438.609896016</v>
       </c>
       <c r="AE97" s="0" t="n">
         <f aca="false">SUMPRODUCT(X97:AC97,R97:W97)</f>
-        <v>1308170.90854575</v>
+        <v>1219717.8190383</v>
       </c>
       <c r="AF97" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B97/10000)-1</f>
@@ -15471,19 +15471,19 @@
       </c>
       <c r="AG97" s="0" t="n">
         <f aca="false">AD97/(K97-AF97)</f>
-        <v>8050939.0127811</v>
+        <v>8230619.10928675</v>
       </c>
       <c r="AH97" s="0" t="n">
         <f aca="false">AG97*Q97</f>
-        <v>4890074.83662189</v>
+        <v>4999211.06497603</v>
       </c>
       <c r="AI97" s="0" t="n">
         <f aca="false">(AE97+AH97-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2219.93823980258</v>
+        <v>2229.38259544033</v>
       </c>
       <c r="AJ97" s="0" t="n">
         <f aca="false">AI97/AI$5-1</f>
-        <v>0.195564356097383</v>
+        <v>0.199461179133052</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15577,35 +15577,35 @@
       </c>
       <c r="X98" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C98+$C98*((1+Supuestos!$B$4+$B98/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113387.144952377</v>
+        <v>88483.6763456948</v>
       </c>
       <c r="Y98" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C98+$C98*((1+Supuestos!$B$4+$B98/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199169.358172274</v>
+        <v>149777.184541206</v>
       </c>
       <c r="Z98" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C98+$C98*((1+Supuestos!$B$4+$B98/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>258982.457446023</v>
+        <v>212653.749100887</v>
       </c>
       <c r="AA98" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C98+$C98*((1+Supuestos!$B$4+$B98/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>373793.152145433</v>
+        <v>381381.454598058</v>
       </c>
       <c r="AB98" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C98+$C98*((1+Supuestos!$B$4+$B98/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>375024.103112727</v>
+        <v>384985.523444201</v>
       </c>
       <c r="AC98" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C98+$C98*((1+Supuestos!$B$4+$B98/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>396016.289258975</v>
+        <v>406919.332079804</v>
       </c>
       <c r="AD98" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C98+$C98*((1+Supuestos!$B$4+$B98/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>524543.362241749</v>
+        <v>536250.071459068</v>
       </c>
       <c r="AE98" s="0" t="n">
         <f aca="false">SUMPRODUCT(X98:AC98,R98:W98)</f>
-        <v>1305723.51863205</v>
+        <v>1217301.85740806</v>
       </c>
       <c r="AF98" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B98/10000)-1</f>
@@ -15613,19 +15613,19 @@
       </c>
       <c r="AG98" s="0" t="n">
         <f aca="false">AD98/(K98-AF98)</f>
-        <v>7902126.4318363</v>
+        <v>8078485.34321523</v>
       </c>
       <c r="AH98" s="0" t="n">
         <f aca="false">AG98*Q98</f>
-        <v>4800629.10906526</v>
+        <v>4907769.09611961</v>
       </c>
       <c r="AI98" s="0" t="n">
         <f aca="false">(AE98+AH98-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2177.97791219056</v>
+        <v>2186.52509293501</v>
       </c>
       <c r="AJ98" s="0" t="n">
         <f aca="false">AI98/AI$5-1</f>
-        <v>0.172966307573491</v>
+        <v>0.17640281732702</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15719,35 +15719,35 @@
       </c>
       <c r="X99" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C99+$C99*((1+Supuestos!$B$4+$B99/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113367.838435872</v>
+        <v>88468.6101619709</v>
       </c>
       <c r="Y99" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C99+$C99*((1+Supuestos!$B$4+$B99/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199033.81612413</v>
+        <v>149675.255677528</v>
       </c>
       <c r="Z99" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C99+$C99*((1+Supuestos!$B$4+$B99/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>258630.340579068</v>
+        <v>212364.6215182</v>
       </c>
       <c r="AA99" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C99+$C99*((1+Supuestos!$B$4+$B99/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>373031.645432107</v>
+        <v>380604.488684296</v>
       </c>
       <c r="AB99" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C99+$C99*((1+Supuestos!$B$4+$B99/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>374006.508832732</v>
+        <v>383940.899743255</v>
       </c>
       <c r="AC99" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C99+$C99*((1+Supuestos!$B$4+$B99/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>394674.536269325</v>
+        <v>405540.638209947</v>
       </c>
       <c r="AD99" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C99+$C99*((1+Supuestos!$B$4+$B99/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>522412.988088781</v>
+        <v>534072.15181696</v>
       </c>
       <c r="AE99" s="0" t="n">
         <f aca="false">SUMPRODUCT(X99:AC99,R99:W99)</f>
-        <v>1303288.82481626</v>
+        <v>1214898.62148719</v>
       </c>
       <c r="AF99" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B99/10000)-1</f>
@@ -15755,19 +15755,19 @@
       </c>
       <c r="AG99" s="0" t="n">
         <f aca="false">AD99/(K99-AF99)</f>
-        <v>7757932.25425003</v>
+        <v>7931073.0535922</v>
       </c>
       <c r="AH99" s="0" t="n">
         <f aca="false">AG99*Q99</f>
-        <v>4713999.21517384</v>
+        <v>4819205.80443819</v>
       </c>
       <c r="AI99" s="0" t="n">
         <f aca="false">(AE99+AH99-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2137.30915068041</v>
+        <v>2144.98786571935</v>
       </c>
       <c r="AJ99" s="0" t="n">
         <f aca="false">AI99/AI$5-1</f>
-        <v>0.15106384164161</v>
+        <v>0.154054795217262</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15861,35 +15861,35 @@
       </c>
       <c r="X100" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C100+$C100*((1+Supuestos!$B$4+$B100/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113348.517815005</v>
+        <v>88453.5329716576</v>
       </c>
       <c r="Y100" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C100+$C100*((1+Supuestos!$B$4+$B100/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198898.274075986</v>
+        <v>149573.32681385</v>
       </c>
       <c r="Z100" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C100+$C100*((1+Supuestos!$B$4+$B100/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>258278.566404927</v>
+        <v>212075.775324887</v>
       </c>
       <c r="AA100" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C100+$C100*((1+Supuestos!$B$4+$B100/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>372271.620248883</v>
+        <v>379829.034376893</v>
       </c>
       <c r="AB100" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C100+$C100*((1+Supuestos!$B$4+$B100/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>372991.882739836</v>
+        <v>382899.323070631</v>
       </c>
       <c r="AC100" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C100+$C100*((1+Supuestos!$B$4+$B100/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>393337.999027332</v>
+        <v>404167.303686691</v>
       </c>
       <c r="AD100" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C100+$C100*((1+Supuestos!$B$4+$B100/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>520292.960557724</v>
+        <v>531904.809711693</v>
       </c>
       <c r="AE100" s="0" t="n">
         <f aca="false">SUMPRODUCT(X100:AC100,R100:W100)</f>
-        <v>1300866.76916133</v>
+        <v>1212508.052562</v>
       </c>
       <c r="AF100" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B100/10000)-1</f>
@@ -15897,19 +15897,19 @@
       </c>
       <c r="AG100" s="0" t="n">
         <f aca="false">AD100/(K100-AF100)</f>
-        <v>7618149.39331689</v>
+        <v>7788170.53197072</v>
       </c>
       <c r="AH100" s="0" t="n">
         <f aca="false">AG100*Q100</f>
-        <v>4630058.5478417</v>
+        <v>4733391.75722042</v>
       </c>
       <c r="AI100" s="0" t="n">
         <f aca="false">(AE100+AH100-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2097.87411735298</v>
+        <v>2104.71178528877</v>
       </c>
       <c r="AJ100" s="0" t="n">
         <f aca="false">AI100/AI$5-1</f>
-        <v>0.12982580925744</v>
+        <v>0.132385300253534</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16003,35 +16003,35 @@
       </c>
       <c r="X101" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C101+$C101*((1+Supuestos!$B$4+$B101/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113329.183065712</v>
+        <v>88438.4447559747</v>
       </c>
       <c r="Y101" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C101+$C101*((1+Supuestos!$B$4+$B101/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198762.732027843</v>
+        <v>149471.397950173</v>
       </c>
       <c r="Z101" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C101+$C101*((1+Supuestos!$B$4+$B101/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257927.1349236</v>
+        <v>211787.21052095</v>
       </c>
       <c r="AA101" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C101+$C101*((1+Supuestos!$B$4+$B101/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>371513.075153182</v>
+        <v>379055.090203983</v>
       </c>
       <c r="AB101" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C101+$C101*((1+Supuestos!$B$4+$B101/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>371980.219056548</v>
+        <v>381860.787495378</v>
       </c>
       <c r="AC101" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C101+$C101*((1+Supuestos!$B$4+$B101/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>392006.662311959</v>
+        <v>402799.312869933</v>
       </c>
       <c r="AD101" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C101+$C101*((1+Supuestos!$B$4+$B101/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>518183.239408987</v>
+        <v>529748.004005615</v>
       </c>
       <c r="AE101" s="0" t="n">
         <f aca="false">SUMPRODUCT(X101:AC101,R101:W101)</f>
-        <v>1298457.29416616</v>
+        <v>1210130.09236187</v>
       </c>
       <c r="AF101" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B101/10000)-1</f>
@@ -16039,19 +16039,19 @@
       </c>
       <c r="AG101" s="0" t="n">
         <f aca="false">AD101/(K101-AF101)</f>
-        <v>7482582.94445052</v>
+        <v>7649578.5239023</v>
       </c>
       <c r="AH101" s="0" t="n">
         <f aca="false">AG101*Q101</f>
-        <v>4548687.95237498</v>
+        <v>4650205.14048923</v>
       </c>
       <c r="AI101" s="0" t="n">
         <f aca="false">(AE101+AH101-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2059.61837741605</v>
+        <v>2065.64120221512</v>
       </c>
       <c r="AJ101" s="0" t="n">
         <f aca="false">AI101/AI$5-1</f>
-        <v>0.109222894156163</v>
+        <v>0.111364391711952</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16145,35 +16145,35 @@
       </c>
       <c r="X102" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C102+$C102*((1+Supuestos!$B$4+$B102/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113309.834163861</v>
+        <v>88423.3454960915</v>
       </c>
       <c r="Y102" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C102+$C102*((1+Supuestos!$B$4+$B102/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198627.189979699</v>
+        <v>149369.469086495</v>
       </c>
       <c r="Z102" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C102+$C102*((1+Supuestos!$B$4+$B102/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257576.046135088</v>
+        <v>211498.927106387</v>
       </c>
       <c r="AA102" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C102+$C102*((1+Supuestos!$B$4+$B102/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370756.008702423</v>
+        <v>378282.654693699</v>
       </c>
       <c r="AB102" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C102+$C102*((1+Supuestos!$B$4+$B102/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>370971.512011005</v>
+        <v>380825.287092319</v>
       </c>
       <c r="AC102" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C102+$C102*((1+Supuestos!$B$4+$B102/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>390680.510931809</v>
+        <v>401436.65015003</v>
       </c>
       <c r="AD102" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C102+$C102*((1+Supuestos!$B$4+$B102/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>516083.784520467</v>
+        <v>527601.693681179</v>
       </c>
       <c r="AE102" s="0" t="n">
         <f aca="false">SUMPRODUCT(X102:AC102,R102:W102)</f>
-        <v>1296060.34276267</v>
+        <v>1207764.68305636</v>
       </c>
       <c r="AF102" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B102/10000)-1</f>
@@ -16181,19 +16181,19 @@
       </c>
       <c r="AG102" s="0" t="n">
         <f aca="false">AD102/(K102-AF102)</f>
-        <v>7351049.30242692</v>
+        <v>7515109.32647889</v>
       </c>
       <c r="AH102" s="0" t="n">
         <f aca="false">AG102*Q102</f>
-        <v>4469775.18643304</v>
+        <v>4569531.20689001</v>
       </c>
       <c r="AI102" s="0" t="n">
         <f aca="false">(AE102+AH102-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>2022.49065260078</v>
+        <v>2027.72369403944</v>
       </c>
       <c r="AJ102" s="0" t="n">
         <f aca="false">AI102/AI$5-1</f>
-        <v>0.0892274800422681</v>
+        <v>0.0909638650552891</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16287,35 +16287,35 @@
       </c>
       <c r="X103" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C103+$C103*((1+Supuestos!$B$4+$B103/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113290.471085256</v>
+        <v>88408.2351731268</v>
       </c>
       <c r="Y103" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C103+$C103*((1+Supuestos!$B$4+$B103/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198491.647931555</v>
+        <v>149267.540222817</v>
       </c>
       <c r="Z103" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C103+$C103*((1+Supuestos!$B$4+$B103/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>257225.300039391</v>
+        <v>211210.9250812</v>
       </c>
       <c r="AA103" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C103+$C103*((1+Supuestos!$B$4+$B103/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>370000.419454025</v>
+        <v>377511.726374177</v>
       </c>
       <c r="AB103" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C103+$C103*((1+Supuestos!$B$4+$B103/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>369965.755836975</v>
+        <v>379792.815942058</v>
       </c>
       <c r="AC103" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C103+$C103*((1+Supuestos!$B$4+$B103/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>389359.529725096</v>
+        <v>400079.299947766</v>
       </c>
       <c r="AD103" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C103+$C103*((1+Supuestos!$B$4+$B103/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>513994.555887322</v>
+        <v>525465.837840718</v>
       </c>
       <c r="AE103" s="0" t="n">
         <f aca="false">SUMPRODUCT(X103:AC103,R103:W103)</f>
-        <v>1293675.85831302</v>
+        <v>1205411.76725226</v>
       </c>
       <c r="AF103" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B103/10000)-1</f>
@@ -16323,19 +16323,19 @@
       </c>
       <c r="AG103" s="0" t="n">
         <f aca="false">AD103/(K103-AF103)</f>
-        <v>7223375.35429187</v>
+        <v>7384585.9632277</v>
       </c>
       <c r="AH103" s="0" t="n">
         <f aca="false">AG103*Q103</f>
-        <v>4393214.42626021</v>
+        <v>4491261.77090253</v>
       </c>
       <c r="AI103" s="0" t="n">
         <f aca="false">(AE103+AH103-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1986.44259569554</v>
+        <v>1990.90983477388</v>
       </c>
       <c r="AJ103" s="0" t="n">
         <f aca="false">AI103/AI$5-1</f>
-        <v>0.0698135291630264</v>
+        <v>0.0711571279194452</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16429,35 +16429,35 @@
       </c>
       <c r="X104" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C104+$C104*((1+Supuestos!$B$4+$B104/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113271.093805638</v>
+        <v>88393.1137681484</v>
       </c>
       <c r="Y104" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C104+$C104*((1+Supuestos!$B$4+$B104/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198356.105883412</v>
+        <v>149165.61135914</v>
       </c>
       <c r="Z104" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C104+$C104*((1+Supuestos!$B$4+$B104/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>256874.896636508</v>
+        <v>210923.204445387</v>
       </c>
       <c r="AA104" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C104+$C104*((1+Supuestos!$B$4+$B104/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>369246.305965409</v>
+        <v>376742.303773549</v>
       </c>
       <c r="AB104" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C104+$C104*((1+Supuestos!$B$4+$B104/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>368962.94477385</v>
+        <v>378763.368130975</v>
       </c>
       <c r="AC104" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C104+$C104*((1+Supuestos!$B$4+$B104/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>388043.70355962</v>
+        <v>398727.246714323</v>
       </c>
       <c r="AD104" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C104+$C104*((1+Supuestos!$B$4+$B104/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>511915.513621734</v>
+        <v>523340.395706205</v>
       </c>
       <c r="AE104" s="0" t="n">
         <f aca="false">SUMPRODUCT(X104:AC104,R104:W104)</f>
-        <v>1291303.78460672</v>
+        <v>1203071.28799072</v>
       </c>
       <c r="AF104" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B104/10000)-1</f>
@@ -16465,19 +16465,19 @@
       </c>
       <c r="AG104" s="0" t="n">
         <f aca="false">AD104/(K104-AF104)</f>
-        <v>7099397.74047322</v>
+        <v>7257841.42873308</v>
       </c>
       <c r="AH104" s="0" t="n">
         <f aca="false">AG104*Q104</f>
-        <v>4318905.81464488</v>
+        <v>4415294.74671134</v>
       </c>
       <c r="AI104" s="0" t="n">
         <f aca="false">(AE104+AH104-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1951.42858413315</v>
+        <v>1955.15298388222</v>
       </c>
       <c r="AJ104" s="0" t="n">
         <f aca="false">AI104/AI$5-1</f>
-        <v>0.0509564711433863</v>
+        <v>0.0519190865799686</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16571,35 +16571,35 @@
       </c>
       <c r="X105" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C105+$C105*((1+Supuestos!$B$4+$B105/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113251.702300681</v>
+        <v>88377.9812621733</v>
       </c>
       <c r="Y105" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C105+$C105*((1+Supuestos!$B$4+$B105/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198220.563835268</v>
+        <v>149063.682495462</v>
       </c>
       <c r="Z105" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C105+$C105*((1+Supuestos!$B$4+$B105/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>256524.83592644</v>
+        <v>210635.765198949</v>
       </c>
       <c r="AA105" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C105+$C105*((1+Supuestos!$B$4+$B105/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>368493.666793993</v>
+        <v>375974.385419951</v>
       </c>
       <c r="AB105" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C105+$C105*((1+Supuestos!$B$4+$B105/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>367963.073066654</v>
+        <v>377736.937751229</v>
       </c>
       <c r="AC105" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C105+$C105*((1+Supuestos!$B$4+$B105/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>386733.017332736</v>
+        <v>397380.474931254</v>
       </c>
       <c r="AD105" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C105+$C105*((1+Supuestos!$B$4+$B105/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>509846.617952694</v>
+        <v>521225.326619023</v>
       </c>
       <c r="AE105" s="0" t="n">
         <f aca="false">SUMPRODUCT(X105:AC105,R105:W105)</f>
-        <v>1288944.06585789</v>
+        <v>1200743.18874443</v>
       </c>
       <c r="AF105" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B105/10000)-1</f>
@@ -16607,19 +16607,19 @@
       </c>
       <c r="AG105" s="0" t="n">
         <f aca="false">AD105/(K105-AF105)</f>
-        <v>6978962.17746671</v>
+        <v>7134717.99620608</v>
       </c>
       <c r="AH105" s="0" t="n">
         <f aca="false">AG105*Q105</f>
-        <v>4246755.0465486</v>
+        <v>4341533.72458706</v>
       </c>
       <c r="AI105" s="0" t="n">
         <f aca="false">(AE105+AH105-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1917.40553077922</v>
+        <v>1920.40909284543</v>
       </c>
       <c r="AJ105" s="0" t="n">
         <f aca="false">AI105/AI$5-1</f>
-        <v>0.0326331010845964</v>
+        <v>0.0332260418796599</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16713,35 +16713,35 @@
       </c>
       <c r="X106" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C106+$C106*((1+Supuestos!$B$4+$B106/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113232.296545994</v>
+        <v>88362.8376361675</v>
       </c>
       <c r="Y106" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C106+$C106*((1+Supuestos!$B$4+$B106/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>198085.021787124</v>
+        <v>148961.753631784</v>
       </c>
       <c r="Z106" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C106+$C106*((1+Supuestos!$B$4+$B106/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>256175.117909186</v>
+        <v>210348.607341886</v>
       </c>
       <c r="AA106" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C106+$C106*((1+Supuestos!$B$4+$B106/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>367742.500497198</v>
+        <v>375207.969841515</v>
       </c>
       <c r="AB106" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C106+$C106*((1+Supuestos!$B$4+$B106/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>366966.134966037</v>
+        <v>376713.518900755</v>
       </c>
       <c r="AC106" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C106+$C106*((1+Supuestos!$B$4+$B106/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>385427.455971325</v>
+        <v>396038.969110448</v>
       </c>
       <c r="AD106" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C106+$C106*((1+Supuestos!$B$4+$B106/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>507787.829225762</v>
+        <v>519120.590039728</v>
       </c>
       <c r="AE106" s="0" t="n">
         <f aca="false">SUMPRODUCT(X106:AC106,R106:W106)</f>
-        <v>1286596.64670246</v>
+        <v>1198427.41341477</v>
       </c>
       <c r="AF106" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B106/10000)-1</f>
@@ -16749,19 +16749,19 @@
       </c>
       <c r="AG106" s="0" t="n">
         <f aca="false">AD106/(K106-AF106)</f>
-        <v>6861922.83619084</v>
+        <v>7015066.58196555</v>
       </c>
       <c r="AH106" s="0" t="n">
         <f aca="false">AG106*Q106</f>
-        <v>4176672.98879317</v>
+        <v>4269887.58208565</v>
       </c>
       <c r="AI106" s="0" t="n">
         <f aca="false">(AE106+AH106-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1884.33271027198</v>
+        <v>1886.63652762576</v>
       </c>
       <c r="AJ106" s="0" t="n">
         <f aca="false">AI106/AI$5-1</f>
-        <v>0.0148214860382356</v>
+        <v>0.0150555937100247</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16858,35 +16858,35 @@
       </c>
       <c r="X107" s="0" t="n">
         <f aca="false">Supuestos!C$23*(1-$C107+$C107*((1+Supuestos!$B$4+$B107/10000)/(1+Supuestos!$B$4))^Supuestos!C$25)</f>
-        <v>113425.715768245</v>
+        <v>88513.7757682451</v>
       </c>
       <c r="Y107" s="0" t="n">
         <f aca="false">Supuestos!D$23*(1-$C107+$C107*((1+Supuestos!$B$4+$B107/10000)/(1+Supuestos!$B$4))^Supuestos!D$25)</f>
-        <v>199440.442268561</v>
+        <v>149981.042268561</v>
       </c>
       <c r="Z107" s="0" t="n">
         <f aca="false">Supuestos!E$23*(1-$C107+$C107*((1+Supuestos!$B$4+$B107/10000)/(1+Supuestos!$B$4))^Supuestos!E$25)</f>
-        <v>259687.719258378</v>
+        <v>213232.848434386</v>
       </c>
       <c r="AA107" s="0" t="n">
         <f aca="false">Supuestos!F$23*(1-$C107+$C107*((1+Supuestos!$B$4+$B107/10000)/(1+Supuestos!$B$4))^Supuestos!F$25)</f>
-        <v>375320.615932717</v>
+        <v>382939.927132123</v>
       </c>
       <c r="AB107" s="0" t="n">
         <f aca="false">Supuestos!G$23*(1-$C107+$C107*((1+Supuestos!$B$4+$B107/10000)/(1+Supuestos!$B$4))^Supuestos!G$25)</f>
-        <v>377068.219372121</v>
+        <v>387083.935683766</v>
       </c>
       <c r="AC107" s="0" t="n">
         <f aca="false">Supuestos!H$23*(1-$C107+$C107*((1+Supuestos!$B$4+$B107/10000)/(1+Supuestos!$B$4))^Supuestos!H$25)</f>
-        <v>398715.503513791</v>
+        <v>409692.860572193</v>
       </c>
       <c r="AD107" s="0" t="n">
         <f aca="false">Supuestos!I$23*(1-$C107+$C107*((1+Supuestos!$B$4+$B107/10000)/(1+Supuestos!$B$4))^Supuestos!I$25)</f>
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="AE107" s="0" t="n">
         <f aca="false">SUMPRODUCT(X107:AC107,R107:W107)</f>
-        <v>1245321.55173293</v>
+        <v>1157723.22568801</v>
       </c>
       <c r="AF107" s="0" t="n">
         <f aca="false">(1+Supuestos!$B$5)/(1+Supuestos!$B$4)*(1+Supuestos!$B$4+$B107/10000)-1</f>
@@ -16894,19 +16894,19 @@
       </c>
       <c r="AG107" s="0" t="n">
         <f aca="false">AD107/(K107-AF107)</f>
-        <v>6309049.80175791</v>
+        <v>6449854.57936698</v>
       </c>
       <c r="AH107" s="0" t="n">
         <f aca="false">AG107*Q107</f>
-        <v>3477029.21557944</v>
+        <v>3554629.22522011</v>
       </c>
       <c r="AI107" s="0" t="n">
         <f aca="false">(AE107+AH107-Supuestos!$B$7-Supuestos!$B$8)/Supuestos!$B$9</f>
-        <v>1546.01359238008</v>
+        <v>1541.4481510996</v>
       </c>
       <c r="AJ107" s="0" t="n">
         <f aca="false">AI107/AI$5-1</f>
-        <v>-0.167382807345096</v>
+        <v>-0.170664012237341</v>
       </c>
     </row>
   </sheetData>
